--- a/12620994.xlsx
+++ b/12620994.xlsx
@@ -3004,47 +3004,91 @@
       <c r="N47" s="19"/>
     </row>
     <row r="48">
-      <c r="A48" s="20"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="17" t="str">
+      <c r="A48" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B48" s="16">
+        <v>360</v>
+      </c>
+      <c r="C48" s="16">
+        <v>0</v>
+      </c>
+      <c r="D48" s="16">
+        <v>90</v>
+      </c>
+      <c r="E48" s="16">
+        <v>90</v>
+      </c>
+      <c r="F48" s="16">
+        <v>350</v>
+      </c>
+      <c r="G48" s="16">
+        <v>7</v>
+      </c>
+      <c r="H48" s="16">
+        <v>210</v>
+      </c>
+      <c r="I48" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="17" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J48" s="17">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="18"/>
-      <c r="L48" s="18"/>
-      <c r="M48" s="18"/>
+        <v>340</v>
+      </c>
+      <c r="K48" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="L48" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="M48" s="18" t="s">
+        <v>53</v>
+      </c>
       <c r="N48" s="19"/>
     </row>
     <row r="49">
-      <c r="A49" s="20"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="16"/>
-      <c r="I49" s="17" t="str">
+      <c r="A49" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B49" s="16">
+        <v>400</v>
+      </c>
+      <c r="C49" s="16">
+        <v>0</v>
+      </c>
+      <c r="D49" s="16">
+        <v>95</v>
+      </c>
+      <c r="E49" s="16">
+        <v>45</v>
+      </c>
+      <c r="F49" s="16">
+        <v>150</v>
+      </c>
+      <c r="G49" s="16">
+        <v>3</v>
+      </c>
+      <c r="H49" s="16">
+        <v>190</v>
+      </c>
+      <c r="I49" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="17" t="str">
+        <v>880</v>
+      </c>
+      <c r="J49" s="17">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="18"/>
-      <c r="L49" s="18"/>
-      <c r="M49" s="18"/>
+        <v>560</v>
+      </c>
+      <c r="K49" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="L49" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="M49" s="18" t="s">
+        <v>53</v>
+      </c>
       <c r="N49" s="19"/>
     </row>
     <row r="50">
@@ -10808,7 +10852,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="lessThan" id="{76ABA876-F716-404A-8ED8-A0623CAC24F4}">
+          <x14:cfRule type="cellIs" priority="2" operator="lessThan" id="{1C8F9663-0315-490F-93C4-CA52D4BEA06A}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -10829,7 +10873,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3" disablePrompts="0">
-        <x14:dataValidation xr:uid="{6AAF6B38-0449-4A93-90EA-06BCC030C4F5}" type="list" allowBlank="1" error="Please choose a value from the dropdown list." errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's overall feeling" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{B0B51877-F7D1-4EBF-A430-7348FB18D483}" type="list" allowBlank="1" error="Please choose a value from the dropdown list." errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's overall feeling" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Excellent,Good,Neutral,Low,Stressed"</xm:f>
           </x14:formula1>
@@ -10838,7 +10882,7 @@
           </x14:formula2>
           <xm:sqref>K6:K401</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{DF2FAD40-264E-49A7-BC5E-B7BA94582D10}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's satisfaction level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{1717D493-EA88-4074-87F7-103096DDF9B8}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's satisfaction level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</xm:f>
           </x14:formula1>
@@ -10847,7 +10891,7 @@
           </x14:formula2>
           <xm:sqref>L6:L401</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{143EE11C-C0D9-408A-B7C4-D947005A3CD4}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's energy level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{D53152B9-F2A7-4B89-82C4-30101151E42A}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's energy level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"High,Medium,Low"</xm:f>
           </x14:formula1>

--- a/12620994.xlsx
+++ b/12620994.xlsx
@@ -3092,25 +3092,47 @@
       <c r="N49" s="19"/>
     </row>
     <row r="50">
-      <c r="A50" s="20"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
-      <c r="I50" s="17" t="str">
+      <c r="A50" s="11">
+        <v>46289</v>
+      </c>
+      <c r="B50" s="16">
+        <v>350</v>
+      </c>
+      <c r="C50" s="16">
+        <v>0</v>
+      </c>
+      <c r="D50" s="16">
+        <v>120</v>
+      </c>
+      <c r="E50" s="16">
+        <v>56</v>
+      </c>
+      <c r="F50" s="16">
+        <v>150</v>
+      </c>
+      <c r="G50" s="16">
+        <v>3</v>
+      </c>
+      <c r="H50" s="16">
+        <v>200</v>
+      </c>
+      <c r="I50" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="17" t="str">
+        <v>876</v>
+      </c>
+      <c r="J50" s="17">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="18"/>
-      <c r="L50" s="18"/>
-      <c r="M50" s="18"/>
+        <v>564</v>
+      </c>
+      <c r="K50" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="L50" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="M50" s="18" t="s">
+        <v>53</v>
+      </c>
       <c r="N50" s="19"/>
     </row>
     <row r="51">
@@ -10852,7 +10874,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="lessThan" id="{1C8F9663-0315-490F-93C4-CA52D4BEA06A}">
+          <x14:cfRule type="cellIs" priority="2" operator="lessThan" id="{C85CB251-8038-4DE2-B670-AF8456B19F1A}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -10873,7 +10895,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3" disablePrompts="0">
-        <x14:dataValidation xr:uid="{B0B51877-F7D1-4EBF-A430-7348FB18D483}" type="list" allowBlank="1" error="Please choose a value from the dropdown list." errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's overall feeling" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{C0792ABE-4EF7-430E-9EC4-24F57842DF4C}" type="list" allowBlank="1" error="Please choose a value from the dropdown list." errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's overall feeling" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Excellent,Good,Neutral,Low,Stressed"</xm:f>
           </x14:formula1>
@@ -10882,7 +10904,7 @@
           </x14:formula2>
           <xm:sqref>K6:K401</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{1717D493-EA88-4074-87F7-103096DDF9B8}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's satisfaction level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{8A0609D0-6B20-46AC-8491-D4C4F760B683}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's satisfaction level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</xm:f>
           </x14:formula1>
@@ -10891,7 +10913,7 @@
           </x14:formula2>
           <xm:sqref>L6:L401</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{D53152B9-F2A7-4B89-82C4-30101151E42A}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's energy level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{9E68DF9E-3195-42E1-B0A0-F28B852CAADA}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's energy level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"High,Medium,Low"</xm:f>
           </x14:formula1>

--- a/12620994.xlsx
+++ b/12620994.xlsx
@@ -3136,25 +3136,47 @@
       <c r="N50" s="19"/>
     </row>
     <row r="51">
-      <c r="A51" s="20"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
-      <c r="H51" s="16"/>
-      <c r="I51" s="17" t="str">
+      <c r="A51" s="11">
+        <v>46290</v>
+      </c>
+      <c r="B51" s="16">
+        <v>400</v>
+      </c>
+      <c r="C51" s="16">
+        <v>0</v>
+      </c>
+      <c r="D51" s="16">
+        <v>60</v>
+      </c>
+      <c r="E51" s="16">
+        <v>79</v>
+      </c>
+      <c r="F51" s="16">
+        <v>250</v>
+      </c>
+      <c r="G51" s="16">
+        <v>5</v>
+      </c>
+      <c r="H51" s="16">
+        <v>100</v>
+      </c>
+      <c r="I51" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="17" t="str">
+        <v>889</v>
+      </c>
+      <c r="J51" s="17">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="18"/>
-      <c r="L51" s="18"/>
-      <c r="M51" s="18"/>
+        <v>551</v>
+      </c>
+      <c r="K51" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="L51" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="M51" s="18" t="s">
+        <v>53</v>
+      </c>
       <c r="N51" s="19"/>
     </row>
     <row r="52">
@@ -10874,7 +10896,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="lessThan" id="{C85CB251-8038-4DE2-B670-AF8456B19F1A}">
+          <x14:cfRule type="cellIs" priority="2" operator="lessThan" id="{0A2C7CCA-C66E-4608-BFE4-CA77F28D0127}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -10895,7 +10917,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3" disablePrompts="0">
-        <x14:dataValidation xr:uid="{C0792ABE-4EF7-430E-9EC4-24F57842DF4C}" type="list" allowBlank="1" error="Please choose a value from the dropdown list." errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's overall feeling" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{5104895D-034F-4B7E-9562-CC528460866C}" type="list" allowBlank="1" error="Please choose a value from the dropdown list." errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's overall feeling" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Excellent,Good,Neutral,Low,Stressed"</xm:f>
           </x14:formula1>
@@ -10904,7 +10926,7 @@
           </x14:formula2>
           <xm:sqref>K6:K401</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{8A0609D0-6B20-46AC-8491-D4C4F760B683}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's satisfaction level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{16B90CE1-E07F-4A40-B96B-85397697717F}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's satisfaction level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</xm:f>
           </x14:formula1>
@@ -10913,7 +10935,7 @@
           </x14:formula2>
           <xm:sqref>L6:L401</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{9E68DF9E-3195-42E1-B0A0-F28B852CAADA}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's energy level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{602249B5-4D63-4F3A-8E9A-C800E794B315}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's energy level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"High,Medium,Low"</xm:f>
           </x14:formula1>

--- a/12620994.xlsx
+++ b/12620994.xlsx
@@ -324,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
@@ -364,6 +364,9 @@
     </xf>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3180,29 +3183,51 @@
       <c r="N51" s="19"/>
     </row>
     <row r="52">
-      <c r="A52" s="20"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="17" t="str">
+      <c r="A52" s="11">
+        <v>46291</v>
+      </c>
+      <c r="B52" s="16">
+        <v>500</v>
+      </c>
+      <c r="C52" s="16">
+        <v>0</v>
+      </c>
+      <c r="D52" s="16">
+        <v>70</v>
+      </c>
+      <c r="E52" s="16">
+        <v>68</v>
+      </c>
+      <c r="F52" s="16">
+        <v>0</v>
+      </c>
+      <c r="G52" s="16">
+        <v>0</v>
+      </c>
+      <c r="H52" s="16">
+        <v>100</v>
+      </c>
+      <c r="I52" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="17" t="str">
+        <v>738</v>
+      </c>
+      <c r="J52" s="17">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="18"/>
-      <c r="L52" s="18"/>
-      <c r="M52" s="18"/>
+        <v>702</v>
+      </c>
+      <c r="K52" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="L52" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="M52" s="20" t="s">
+        <v>53</v>
+      </c>
       <c r="N52" s="19"/>
     </row>
     <row r="53">
-      <c r="A53" s="20"/>
+      <c r="A53" s="21"/>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
@@ -3219,12 +3244,11 @@
         <v/>
       </c>
       <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
       <c r="M53" s="18"/>
       <c r="N53" s="19"/>
     </row>
     <row r="54">
-      <c r="A54" s="20"/>
+      <c r="A54" s="21"/>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
       <c r="D54" s="16"/>
@@ -3246,7 +3270,7 @@
       <c r="N54" s="19"/>
     </row>
     <row r="55">
-      <c r="A55" s="20"/>
+      <c r="A55" s="21"/>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
@@ -3268,7 +3292,7 @@
       <c r="N55" s="19"/>
     </row>
     <row r="56">
-      <c r="A56" s="20"/>
+      <c r="A56" s="21"/>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
       <c r="D56" s="16"/>
@@ -3290,7 +3314,7 @@
       <c r="N56" s="19"/>
     </row>
     <row r="57">
-      <c r="A57" s="20"/>
+      <c r="A57" s="21"/>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
       <c r="D57" s="16"/>
@@ -3312,7 +3336,7 @@
       <c r="N57" s="19"/>
     </row>
     <row r="58">
-      <c r="A58" s="20"/>
+      <c r="A58" s="21"/>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
       <c r="D58" s="16"/>
@@ -3334,7 +3358,7 @@
       <c r="N58" s="19"/>
     </row>
     <row r="59">
-      <c r="A59" s="20"/>
+      <c r="A59" s="21"/>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
       <c r="D59" s="16"/>
@@ -3356,7 +3380,7 @@
       <c r="N59" s="19"/>
     </row>
     <row r="60">
-      <c r="A60" s="20"/>
+      <c r="A60" s="21"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
       <c r="D60" s="16"/>
@@ -3378,7 +3402,7 @@
       <c r="N60" s="19"/>
     </row>
     <row r="61">
-      <c r="A61" s="20"/>
+      <c r="A61" s="21"/>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
       <c r="D61" s="16"/>
@@ -3400,7 +3424,7 @@
       <c r="N61" s="19"/>
     </row>
     <row r="62">
-      <c r="A62" s="20"/>
+      <c r="A62" s="21"/>
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
       <c r="D62" s="16"/>
@@ -3422,7 +3446,7 @@
       <c r="N62" s="19"/>
     </row>
     <row r="63">
-      <c r="A63" s="20"/>
+      <c r="A63" s="21"/>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
       <c r="D63" s="16"/>
@@ -3444,7 +3468,7 @@
       <c r="N63" s="19"/>
     </row>
     <row r="64">
-      <c r="A64" s="20"/>
+      <c r="A64" s="21"/>
       <c r="B64" s="16"/>
       <c r="C64" s="16"/>
       <c r="D64" s="16"/>
@@ -3466,7 +3490,7 @@
       <c r="N64" s="19"/>
     </row>
     <row r="65">
-      <c r="A65" s="20"/>
+      <c r="A65" s="21"/>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
       <c r="D65" s="16"/>
@@ -3488,7 +3512,7 @@
       <c r="N65" s="19"/>
     </row>
     <row r="66">
-      <c r="A66" s="20"/>
+      <c r="A66" s="21"/>
       <c r="B66" s="16"/>
       <c r="C66" s="16"/>
       <c r="D66" s="16"/>
@@ -3510,7 +3534,7 @@
       <c r="N66" s="19"/>
     </row>
     <row r="67">
-      <c r="A67" s="20"/>
+      <c r="A67" s="21"/>
       <c r="B67" s="16"/>
       <c r="C67" s="16"/>
       <c r="D67" s="16"/>
@@ -3532,7 +3556,7 @@
       <c r="N67" s="19"/>
     </row>
     <row r="68">
-      <c r="A68" s="20"/>
+      <c r="A68" s="21"/>
       <c r="B68" s="16"/>
       <c r="C68" s="16"/>
       <c r="D68" s="16"/>
@@ -3554,7 +3578,7 @@
       <c r="N68" s="19"/>
     </row>
     <row r="69">
-      <c r="A69" s="20"/>
+      <c r="A69" s="21"/>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
       <c r="D69" s="16"/>
@@ -3576,7 +3600,7 @@
       <c r="N69" s="19"/>
     </row>
     <row r="70">
-      <c r="A70" s="20"/>
+      <c r="A70" s="21"/>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
       <c r="D70" s="16"/>
@@ -3598,7 +3622,7 @@
       <c r="N70" s="19"/>
     </row>
     <row r="71">
-      <c r="A71" s="20"/>
+      <c r="A71" s="21"/>
       <c r="B71" s="16"/>
       <c r="C71" s="16"/>
       <c r="D71" s="16"/>
@@ -3620,7 +3644,7 @@
       <c r="N71" s="19"/>
     </row>
     <row r="72">
-      <c r="A72" s="20"/>
+      <c r="A72" s="21"/>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
       <c r="D72" s="16"/>
@@ -3642,7 +3666,7 @@
       <c r="N72" s="19"/>
     </row>
     <row r="73">
-      <c r="A73" s="20"/>
+      <c r="A73" s="21"/>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
       <c r="D73" s="16"/>
@@ -3664,7 +3688,7 @@
       <c r="N73" s="19"/>
     </row>
     <row r="74">
-      <c r="A74" s="20"/>
+      <c r="A74" s="21"/>
       <c r="B74" s="16"/>
       <c r="C74" s="16"/>
       <c r="D74" s="16"/>
@@ -3686,7 +3710,7 @@
       <c r="N74" s="19"/>
     </row>
     <row r="75">
-      <c r="A75" s="20"/>
+      <c r="A75" s="21"/>
       <c r="B75" s="16"/>
       <c r="C75" s="16"/>
       <c r="D75" s="16"/>
@@ -3708,7 +3732,7 @@
       <c r="N75" s="19"/>
     </row>
     <row r="76">
-      <c r="A76" s="20"/>
+      <c r="A76" s="21"/>
       <c r="B76" s="16"/>
       <c r="C76" s="16"/>
       <c r="D76" s="16"/>
@@ -3730,7 +3754,7 @@
       <c r="N76" s="19"/>
     </row>
     <row r="77">
-      <c r="A77" s="20"/>
+      <c r="A77" s="21"/>
       <c r="B77" s="16"/>
       <c r="C77" s="16"/>
       <c r="D77" s="16"/>
@@ -3752,7 +3776,7 @@
       <c r="N77" s="19"/>
     </row>
     <row r="78">
-      <c r="A78" s="20"/>
+      <c r="A78" s="21"/>
       <c r="B78" s="16"/>
       <c r="C78" s="16"/>
       <c r="D78" s="16"/>
@@ -3774,7 +3798,7 @@
       <c r="N78" s="19"/>
     </row>
     <row r="79">
-      <c r="A79" s="20"/>
+      <c r="A79" s="21"/>
       <c r="B79" s="16"/>
       <c r="C79" s="16"/>
       <c r="D79" s="16"/>
@@ -3796,7 +3820,7 @@
       <c r="N79" s="19"/>
     </row>
     <row r="80">
-      <c r="A80" s="20"/>
+      <c r="A80" s="21"/>
       <c r="B80" s="16"/>
       <c r="C80" s="16"/>
       <c r="D80" s="16"/>
@@ -3818,7 +3842,7 @@
       <c r="N80" s="19"/>
     </row>
     <row r="81">
-      <c r="A81" s="20"/>
+      <c r="A81" s="21"/>
       <c r="B81" s="16"/>
       <c r="C81" s="16"/>
       <c r="D81" s="16"/>
@@ -3840,7 +3864,7 @@
       <c r="N81" s="19"/>
     </row>
     <row r="82">
-      <c r="A82" s="20"/>
+      <c r="A82" s="21"/>
       <c r="B82" s="16"/>
       <c r="C82" s="16"/>
       <c r="D82" s="16"/>
@@ -3862,7 +3886,7 @@
       <c r="N82" s="19"/>
     </row>
     <row r="83">
-      <c r="A83" s="20"/>
+      <c r="A83" s="21"/>
       <c r="B83" s="16"/>
       <c r="C83" s="16"/>
       <c r="D83" s="16"/>
@@ -3884,7 +3908,7 @@
       <c r="N83" s="19"/>
     </row>
     <row r="84">
-      <c r="A84" s="20"/>
+      <c r="A84" s="21"/>
       <c r="B84" s="16"/>
       <c r="C84" s="16"/>
       <c r="D84" s="16"/>
@@ -3906,7 +3930,7 @@
       <c r="N84" s="19"/>
     </row>
     <row r="85">
-      <c r="A85" s="20"/>
+      <c r="A85" s="21"/>
       <c r="B85" s="16"/>
       <c r="C85" s="16"/>
       <c r="D85" s="16"/>
@@ -3928,7 +3952,7 @@
       <c r="N85" s="19"/>
     </row>
     <row r="86">
-      <c r="A86" s="20"/>
+      <c r="A86" s="21"/>
       <c r="B86" s="16"/>
       <c r="C86" s="16"/>
       <c r="D86" s="16"/>
@@ -3950,7 +3974,7 @@
       <c r="N86" s="19"/>
     </row>
     <row r="87">
-      <c r="A87" s="20"/>
+      <c r="A87" s="21"/>
       <c r="B87" s="16"/>
       <c r="C87" s="16"/>
       <c r="D87" s="16"/>
@@ -3972,7 +3996,7 @@
       <c r="N87" s="19"/>
     </row>
     <row r="88">
-      <c r="A88" s="20"/>
+      <c r="A88" s="21"/>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
       <c r="D88" s="16"/>
@@ -3994,7 +4018,7 @@
       <c r="N88" s="19"/>
     </row>
     <row r="89">
-      <c r="A89" s="20"/>
+      <c r="A89" s="21"/>
       <c r="B89" s="16"/>
       <c r="C89" s="16"/>
       <c r="D89" s="16"/>
@@ -4016,7 +4040,7 @@
       <c r="N89" s="19"/>
     </row>
     <row r="90">
-      <c r="A90" s="20"/>
+      <c r="A90" s="21"/>
       <c r="B90" s="16"/>
       <c r="C90" s="16"/>
       <c r="D90" s="16"/>
@@ -4038,7 +4062,7 @@
       <c r="N90" s="19"/>
     </row>
     <row r="91">
-      <c r="A91" s="20"/>
+      <c r="A91" s="21"/>
       <c r="B91" s="16"/>
       <c r="C91" s="16"/>
       <c r="D91" s="16"/>
@@ -4060,7 +4084,7 @@
       <c r="N91" s="19"/>
     </row>
     <row r="92">
-      <c r="A92" s="20"/>
+      <c r="A92" s="21"/>
       <c r="B92" s="16"/>
       <c r="C92" s="16"/>
       <c r="D92" s="16"/>
@@ -4082,7 +4106,7 @@
       <c r="N92" s="19"/>
     </row>
     <row r="93">
-      <c r="A93" s="20"/>
+      <c r="A93" s="21"/>
       <c r="B93" s="16"/>
       <c r="C93" s="16"/>
       <c r="D93" s="16"/>
@@ -4104,7 +4128,7 @@
       <c r="N93" s="19"/>
     </row>
     <row r="94">
-      <c r="A94" s="20"/>
+      <c r="A94" s="21"/>
       <c r="B94" s="16"/>
       <c r="C94" s="16"/>
       <c r="D94" s="16"/>
@@ -4126,7 +4150,7 @@
       <c r="N94" s="19"/>
     </row>
     <row r="95">
-      <c r="A95" s="20"/>
+      <c r="A95" s="21"/>
       <c r="B95" s="16"/>
       <c r="C95" s="16"/>
       <c r="D95" s="16"/>
@@ -4148,7 +4172,7 @@
       <c r="N95" s="19"/>
     </row>
     <row r="96">
-      <c r="A96" s="20"/>
+      <c r="A96" s="21"/>
       <c r="B96" s="16"/>
       <c r="C96" s="16"/>
       <c r="D96" s="16"/>
@@ -4170,7 +4194,7 @@
       <c r="N96" s="19"/>
     </row>
     <row r="97">
-      <c r="A97" s="20"/>
+      <c r="A97" s="21"/>
       <c r="B97" s="16"/>
       <c r="C97" s="16"/>
       <c r="D97" s="16"/>
@@ -4192,7 +4216,7 @@
       <c r="N97" s="19"/>
     </row>
     <row r="98">
-      <c r="A98" s="20"/>
+      <c r="A98" s="21"/>
       <c r="B98" s="16"/>
       <c r="C98" s="16"/>
       <c r="D98" s="16"/>
@@ -4214,7 +4238,7 @@
       <c r="N98" s="19"/>
     </row>
     <row r="99">
-      <c r="A99" s="20"/>
+      <c r="A99" s="21"/>
       <c r="B99" s="16"/>
       <c r="C99" s="16"/>
       <c r="D99" s="16"/>
@@ -4236,7 +4260,7 @@
       <c r="N99" s="19"/>
     </row>
     <row r="100">
-      <c r="A100" s="20"/>
+      <c r="A100" s="21"/>
       <c r="B100" s="16"/>
       <c r="C100" s="16"/>
       <c r="D100" s="16"/>
@@ -4258,7 +4282,7 @@
       <c r="N100" s="19"/>
     </row>
     <row r="101">
-      <c r="A101" s="20"/>
+      <c r="A101" s="21"/>
       <c r="B101" s="16"/>
       <c r="C101" s="16"/>
       <c r="D101" s="16"/>
@@ -4280,7 +4304,7 @@
       <c r="N101" s="19"/>
     </row>
     <row r="102">
-      <c r="A102" s="20"/>
+      <c r="A102" s="21"/>
       <c r="B102" s="16"/>
       <c r="C102" s="16"/>
       <c r="D102" s="16"/>
@@ -4302,7 +4326,7 @@
       <c r="N102" s="19"/>
     </row>
     <row r="103">
-      <c r="A103" s="20"/>
+      <c r="A103" s="21"/>
       <c r="B103" s="16"/>
       <c r="C103" s="16"/>
       <c r="D103" s="16"/>
@@ -4324,7 +4348,7 @@
       <c r="N103" s="19"/>
     </row>
     <row r="104">
-      <c r="A104" s="20"/>
+      <c r="A104" s="21"/>
       <c r="B104" s="16"/>
       <c r="C104" s="16"/>
       <c r="D104" s="16"/>
@@ -4346,7 +4370,7 @@
       <c r="N104" s="19"/>
     </row>
     <row r="105">
-      <c r="A105" s="20"/>
+      <c r="A105" s="21"/>
       <c r="B105" s="16"/>
       <c r="C105" s="16"/>
       <c r="D105" s="16"/>
@@ -4368,7 +4392,7 @@
       <c r="N105" s="19"/>
     </row>
     <row r="106">
-      <c r="A106" s="20"/>
+      <c r="A106" s="21"/>
       <c r="B106" s="16"/>
       <c r="C106" s="16"/>
       <c r="D106" s="16"/>
@@ -4390,7 +4414,7 @@
       <c r="N106" s="19"/>
     </row>
     <row r="107">
-      <c r="A107" s="20"/>
+      <c r="A107" s="21"/>
       <c r="B107" s="16"/>
       <c r="C107" s="16"/>
       <c r="D107" s="16"/>
@@ -4412,7 +4436,7 @@
       <c r="N107" s="19"/>
     </row>
     <row r="108">
-      <c r="A108" s="20"/>
+      <c r="A108" s="21"/>
       <c r="B108" s="16"/>
       <c r="C108" s="16"/>
       <c r="D108" s="16"/>
@@ -4434,7 +4458,7 @@
       <c r="N108" s="19"/>
     </row>
     <row r="109">
-      <c r="A109" s="20"/>
+      <c r="A109" s="21"/>
       <c r="B109" s="16"/>
       <c r="C109" s="16"/>
       <c r="D109" s="16"/>
@@ -4456,7 +4480,7 @@
       <c r="N109" s="19"/>
     </row>
     <row r="110">
-      <c r="A110" s="20"/>
+      <c r="A110" s="21"/>
       <c r="B110" s="16"/>
       <c r="C110" s="16"/>
       <c r="D110" s="16"/>
@@ -4478,7 +4502,7 @@
       <c r="N110" s="19"/>
     </row>
     <row r="111">
-      <c r="A111" s="20"/>
+      <c r="A111" s="21"/>
       <c r="B111" s="16"/>
       <c r="C111" s="16"/>
       <c r="D111" s="16"/>
@@ -4500,7 +4524,7 @@
       <c r="N111" s="19"/>
     </row>
     <row r="112">
-      <c r="A112" s="20"/>
+      <c r="A112" s="21"/>
       <c r="B112" s="16"/>
       <c r="C112" s="16"/>
       <c r="D112" s="16"/>
@@ -4522,7 +4546,7 @@
       <c r="N112" s="19"/>
     </row>
     <row r="113">
-      <c r="A113" s="20"/>
+      <c r="A113" s="21"/>
       <c r="B113" s="16"/>
       <c r="C113" s="16"/>
       <c r="D113" s="16"/>
@@ -4544,7 +4568,7 @@
       <c r="N113" s="19"/>
     </row>
     <row r="114">
-      <c r="A114" s="20"/>
+      <c r="A114" s="21"/>
       <c r="B114" s="16"/>
       <c r="C114" s="16"/>
       <c r="D114" s="16"/>
@@ -4566,7 +4590,7 @@
       <c r="N114" s="19"/>
     </row>
     <row r="115">
-      <c r="A115" s="20"/>
+      <c r="A115" s="21"/>
       <c r="B115" s="16"/>
       <c r="C115" s="16"/>
       <c r="D115" s="16"/>
@@ -4588,7 +4612,7 @@
       <c r="N115" s="19"/>
     </row>
     <row r="116">
-      <c r="A116" s="20"/>
+      <c r="A116" s="21"/>
       <c r="B116" s="16"/>
       <c r="C116" s="16"/>
       <c r="D116" s="16"/>
@@ -4610,7 +4634,7 @@
       <c r="N116" s="19"/>
     </row>
     <row r="117">
-      <c r="A117" s="20"/>
+      <c r="A117" s="21"/>
       <c r="B117" s="16"/>
       <c r="C117" s="16"/>
       <c r="D117" s="16"/>
@@ -4632,7 +4656,7 @@
       <c r="N117" s="19"/>
     </row>
     <row r="118">
-      <c r="A118" s="20"/>
+      <c r="A118" s="21"/>
       <c r="B118" s="16"/>
       <c r="C118" s="16"/>
       <c r="D118" s="16"/>
@@ -4654,7 +4678,7 @@
       <c r="N118" s="19"/>
     </row>
     <row r="119">
-      <c r="A119" s="20"/>
+      <c r="A119" s="21"/>
       <c r="B119" s="16"/>
       <c r="C119" s="16"/>
       <c r="D119" s="16"/>
@@ -4676,7 +4700,7 @@
       <c r="N119" s="19"/>
     </row>
     <row r="120">
-      <c r="A120" s="20"/>
+      <c r="A120" s="21"/>
       <c r="B120" s="16"/>
       <c r="C120" s="16"/>
       <c r="D120" s="16"/>
@@ -4698,7 +4722,7 @@
       <c r="N120" s="19"/>
     </row>
     <row r="121">
-      <c r="A121" s="20"/>
+      <c r="A121" s="21"/>
       <c r="B121" s="16"/>
       <c r="C121" s="16"/>
       <c r="D121" s="16"/>
@@ -4720,7 +4744,7 @@
       <c r="N121" s="19"/>
     </row>
     <row r="122">
-      <c r="A122" s="20"/>
+      <c r="A122" s="21"/>
       <c r="B122" s="16"/>
       <c r="C122" s="16"/>
       <c r="D122" s="16"/>
@@ -4742,7 +4766,7 @@
       <c r="N122" s="19"/>
     </row>
     <row r="123">
-      <c r="A123" s="20"/>
+      <c r="A123" s="21"/>
       <c r="B123" s="16"/>
       <c r="C123" s="16"/>
       <c r="D123" s="16"/>
@@ -4764,7 +4788,7 @@
       <c r="N123" s="19"/>
     </row>
     <row r="124">
-      <c r="A124" s="20"/>
+      <c r="A124" s="21"/>
       <c r="B124" s="16"/>
       <c r="C124" s="16"/>
       <c r="D124" s="16"/>
@@ -4786,7 +4810,7 @@
       <c r="N124" s="19"/>
     </row>
     <row r="125">
-      <c r="A125" s="20"/>
+      <c r="A125" s="21"/>
       <c r="B125" s="16"/>
       <c r="C125" s="16"/>
       <c r="D125" s="16"/>
@@ -4808,7 +4832,7 @@
       <c r="N125" s="19"/>
     </row>
     <row r="126">
-      <c r="A126" s="20"/>
+      <c r="A126" s="21"/>
       <c r="B126" s="16"/>
       <c r="C126" s="16"/>
       <c r="D126" s="16"/>
@@ -4830,7 +4854,7 @@
       <c r="N126" s="19"/>
     </row>
     <row r="127">
-      <c r="A127" s="20"/>
+      <c r="A127" s="21"/>
       <c r="B127" s="16"/>
       <c r="C127" s="16"/>
       <c r="D127" s="16"/>
@@ -4852,7 +4876,7 @@
       <c r="N127" s="19"/>
     </row>
     <row r="128">
-      <c r="A128" s="20"/>
+      <c r="A128" s="21"/>
       <c r="B128" s="16"/>
       <c r="C128" s="16"/>
       <c r="D128" s="16"/>
@@ -4874,7 +4898,7 @@
       <c r="N128" s="19"/>
     </row>
     <row r="129">
-      <c r="A129" s="20"/>
+      <c r="A129" s="21"/>
       <c r="B129" s="16"/>
       <c r="C129" s="16"/>
       <c r="D129" s="16"/>
@@ -4896,7 +4920,7 @@
       <c r="N129" s="19"/>
     </row>
     <row r="130">
-      <c r="A130" s="20"/>
+      <c r="A130" s="21"/>
       <c r="B130" s="16"/>
       <c r="C130" s="16"/>
       <c r="D130" s="16"/>
@@ -4918,7 +4942,7 @@
       <c r="N130" s="19"/>
     </row>
     <row r="131">
-      <c r="A131" s="20"/>
+      <c r="A131" s="21"/>
       <c r="B131" s="16"/>
       <c r="C131" s="16"/>
       <c r="D131" s="16"/>
@@ -4940,7 +4964,7 @@
       <c r="N131" s="19"/>
     </row>
     <row r="132">
-      <c r="A132" s="20"/>
+      <c r="A132" s="21"/>
       <c r="B132" s="16"/>
       <c r="C132" s="16"/>
       <c r="D132" s="16"/>
@@ -4962,7 +4986,7 @@
       <c r="N132" s="19"/>
     </row>
     <row r="133">
-      <c r="A133" s="20"/>
+      <c r="A133" s="21"/>
       <c r="B133" s="16"/>
       <c r="C133" s="16"/>
       <c r="D133" s="16"/>
@@ -4984,7 +5008,7 @@
       <c r="N133" s="19"/>
     </row>
     <row r="134">
-      <c r="A134" s="20"/>
+      <c r="A134" s="21"/>
       <c r="B134" s="16"/>
       <c r="C134" s="16"/>
       <c r="D134" s="16"/>
@@ -5006,7 +5030,7 @@
       <c r="N134" s="19"/>
     </row>
     <row r="135">
-      <c r="A135" s="20"/>
+      <c r="A135" s="21"/>
       <c r="B135" s="16"/>
       <c r="C135" s="16"/>
       <c r="D135" s="16"/>
@@ -5028,7 +5052,7 @@
       <c r="N135" s="19"/>
     </row>
     <row r="136">
-      <c r="A136" s="20"/>
+      <c r="A136" s="21"/>
       <c r="B136" s="16"/>
       <c r="C136" s="16"/>
       <c r="D136" s="16"/>
@@ -5050,7 +5074,7 @@
       <c r="N136" s="19"/>
     </row>
     <row r="137">
-      <c r="A137" s="20"/>
+      <c r="A137" s="21"/>
       <c r="B137" s="16"/>
       <c r="C137" s="16"/>
       <c r="D137" s="16"/>
@@ -5072,7 +5096,7 @@
       <c r="N137" s="19"/>
     </row>
     <row r="138">
-      <c r="A138" s="20"/>
+      <c r="A138" s="21"/>
       <c r="B138" s="16"/>
       <c r="C138" s="16"/>
       <c r="D138" s="16"/>
@@ -5094,7 +5118,7 @@
       <c r="N138" s="19"/>
     </row>
     <row r="139">
-      <c r="A139" s="20"/>
+      <c r="A139" s="21"/>
       <c r="B139" s="16"/>
       <c r="C139" s="16"/>
       <c r="D139" s="16"/>
@@ -5116,7 +5140,7 @@
       <c r="N139" s="19"/>
     </row>
     <row r="140">
-      <c r="A140" s="20"/>
+      <c r="A140" s="21"/>
       <c r="B140" s="16"/>
       <c r="C140" s="16"/>
       <c r="D140" s="16"/>
@@ -5138,7 +5162,7 @@
       <c r="N140" s="19"/>
     </row>
     <row r="141">
-      <c r="A141" s="20"/>
+      <c r="A141" s="21"/>
       <c r="B141" s="16"/>
       <c r="C141" s="16"/>
       <c r="D141" s="16"/>
@@ -5160,7 +5184,7 @@
       <c r="N141" s="19"/>
     </row>
     <row r="142">
-      <c r="A142" s="20"/>
+      <c r="A142" s="21"/>
       <c r="B142" s="16"/>
       <c r="C142" s="16"/>
       <c r="D142" s="16"/>
@@ -5182,7 +5206,7 @@
       <c r="N142" s="19"/>
     </row>
     <row r="143">
-      <c r="A143" s="20"/>
+      <c r="A143" s="21"/>
       <c r="B143" s="16"/>
       <c r="C143" s="16"/>
       <c r="D143" s="16"/>
@@ -5204,7 +5228,7 @@
       <c r="N143" s="19"/>
     </row>
     <row r="144">
-      <c r="A144" s="20"/>
+      <c r="A144" s="21"/>
       <c r="B144" s="16"/>
       <c r="C144" s="16"/>
       <c r="D144" s="16"/>
@@ -5226,7 +5250,7 @@
       <c r="N144" s="19"/>
     </row>
     <row r="145">
-      <c r="A145" s="20"/>
+      <c r="A145" s="21"/>
       <c r="B145" s="16"/>
       <c r="C145" s="16"/>
       <c r="D145" s="16"/>
@@ -5248,7 +5272,7 @@
       <c r="N145" s="19"/>
     </row>
     <row r="146">
-      <c r="A146" s="20"/>
+      <c r="A146" s="21"/>
       <c r="B146" s="16"/>
       <c r="C146" s="16"/>
       <c r="D146" s="16"/>
@@ -5270,7 +5294,7 @@
       <c r="N146" s="19"/>
     </row>
     <row r="147">
-      <c r="A147" s="20"/>
+      <c r="A147" s="21"/>
       <c r="B147" s="16"/>
       <c r="C147" s="16"/>
       <c r="D147" s="16"/>
@@ -5292,7 +5316,7 @@
       <c r="N147" s="19"/>
     </row>
     <row r="148">
-      <c r="A148" s="20"/>
+      <c r="A148" s="21"/>
       <c r="B148" s="16"/>
       <c r="C148" s="16"/>
       <c r="D148" s="16"/>
@@ -5314,7 +5338,7 @@
       <c r="N148" s="19"/>
     </row>
     <row r="149">
-      <c r="A149" s="20"/>
+      <c r="A149" s="21"/>
       <c r="B149" s="16"/>
       <c r="C149" s="16"/>
       <c r="D149" s="16"/>
@@ -5336,7 +5360,7 @@
       <c r="N149" s="19"/>
     </row>
     <row r="150">
-      <c r="A150" s="20"/>
+      <c r="A150" s="21"/>
       <c r="B150" s="16"/>
       <c r="C150" s="16"/>
       <c r="D150" s="16"/>
@@ -5358,7 +5382,7 @@
       <c r="N150" s="19"/>
     </row>
     <row r="151">
-      <c r="A151" s="20"/>
+      <c r="A151" s="21"/>
       <c r="B151" s="16"/>
       <c r="C151" s="16"/>
       <c r="D151" s="16"/>
@@ -5380,7 +5404,7 @@
       <c r="N151" s="19"/>
     </row>
     <row r="152">
-      <c r="A152" s="20"/>
+      <c r="A152" s="21"/>
       <c r="B152" s="16"/>
       <c r="C152" s="16"/>
       <c r="D152" s="16"/>
@@ -5402,7 +5426,7 @@
       <c r="N152" s="19"/>
     </row>
     <row r="153">
-      <c r="A153" s="20"/>
+      <c r="A153" s="21"/>
       <c r="B153" s="16"/>
       <c r="C153" s="16"/>
       <c r="D153" s="16"/>
@@ -5424,7 +5448,7 @@
       <c r="N153" s="19"/>
     </row>
     <row r="154">
-      <c r="A154" s="20"/>
+      <c r="A154" s="21"/>
       <c r="B154" s="16"/>
       <c r="C154" s="16"/>
       <c r="D154" s="16"/>
@@ -5446,7 +5470,7 @@
       <c r="N154" s="19"/>
     </row>
     <row r="155">
-      <c r="A155" s="20"/>
+      <c r="A155" s="21"/>
       <c r="B155" s="16"/>
       <c r="C155" s="16"/>
       <c r="D155" s="16"/>
@@ -5468,7 +5492,7 @@
       <c r="N155" s="19"/>
     </row>
     <row r="156">
-      <c r="A156" s="20"/>
+      <c r="A156" s="21"/>
       <c r="B156" s="16"/>
       <c r="C156" s="16"/>
       <c r="D156" s="16"/>
@@ -5490,7 +5514,7 @@
       <c r="N156" s="19"/>
     </row>
     <row r="157">
-      <c r="A157" s="20"/>
+      <c r="A157" s="21"/>
       <c r="B157" s="16"/>
       <c r="C157" s="16"/>
       <c r="D157" s="16"/>
@@ -5512,7 +5536,7 @@
       <c r="N157" s="19"/>
     </row>
     <row r="158">
-      <c r="A158" s="20"/>
+      <c r="A158" s="21"/>
       <c r="B158" s="16"/>
       <c r="C158" s="16"/>
       <c r="D158" s="16"/>
@@ -5534,7 +5558,7 @@
       <c r="N158" s="19"/>
     </row>
     <row r="159">
-      <c r="A159" s="20"/>
+      <c r="A159" s="21"/>
       <c r="B159" s="16"/>
       <c r="C159" s="16"/>
       <c r="D159" s="16"/>
@@ -5556,7 +5580,7 @@
       <c r="N159" s="19"/>
     </row>
     <row r="160">
-      <c r="A160" s="20"/>
+      <c r="A160" s="21"/>
       <c r="B160" s="16"/>
       <c r="C160" s="16"/>
       <c r="D160" s="16"/>
@@ -5578,7 +5602,7 @@
       <c r="N160" s="19"/>
     </row>
     <row r="161">
-      <c r="A161" s="20"/>
+      <c r="A161" s="21"/>
       <c r="B161" s="16"/>
       <c r="C161" s="16"/>
       <c r="D161" s="16"/>
@@ -5600,7 +5624,7 @@
       <c r="N161" s="19"/>
     </row>
     <row r="162">
-      <c r="A162" s="20"/>
+      <c r="A162" s="21"/>
       <c r="B162" s="16"/>
       <c r="C162" s="16"/>
       <c r="D162" s="16"/>
@@ -5622,7 +5646,7 @@
       <c r="N162" s="19"/>
     </row>
     <row r="163">
-      <c r="A163" s="20"/>
+      <c r="A163" s="21"/>
       <c r="B163" s="16"/>
       <c r="C163" s="16"/>
       <c r="D163" s="16"/>
@@ -5644,7 +5668,7 @@
       <c r="N163" s="19"/>
     </row>
     <row r="164">
-      <c r="A164" s="20"/>
+      <c r="A164" s="21"/>
       <c r="B164" s="16"/>
       <c r="C164" s="16"/>
       <c r="D164" s="16"/>
@@ -5666,7 +5690,7 @@
       <c r="N164" s="19"/>
     </row>
     <row r="165">
-      <c r="A165" s="20"/>
+      <c r="A165" s="21"/>
       <c r="B165" s="16"/>
       <c r="C165" s="16"/>
       <c r="D165" s="16"/>
@@ -5688,7 +5712,7 @@
       <c r="N165" s="19"/>
     </row>
     <row r="166">
-      <c r="A166" s="20"/>
+      <c r="A166" s="21"/>
       <c r="B166" s="16"/>
       <c r="C166" s="16"/>
       <c r="D166" s="16"/>
@@ -5710,7 +5734,7 @@
       <c r="N166" s="19"/>
     </row>
     <row r="167">
-      <c r="A167" s="20"/>
+      <c r="A167" s="21"/>
       <c r="B167" s="16"/>
       <c r="C167" s="16"/>
       <c r="D167" s="16"/>
@@ -5732,7 +5756,7 @@
       <c r="N167" s="19"/>
     </row>
     <row r="168">
-      <c r="A168" s="20"/>
+      <c r="A168" s="21"/>
       <c r="B168" s="16"/>
       <c r="C168" s="16"/>
       <c r="D168" s="16"/>
@@ -5754,7 +5778,7 @@
       <c r="N168" s="19"/>
     </row>
     <row r="169">
-      <c r="A169" s="20"/>
+      <c r="A169" s="21"/>
       <c r="B169" s="16"/>
       <c r="C169" s="16"/>
       <c r="D169" s="16"/>
@@ -5776,7 +5800,7 @@
       <c r="N169" s="19"/>
     </row>
     <row r="170">
-      <c r="A170" s="20"/>
+      <c r="A170" s="21"/>
       <c r="B170" s="16"/>
       <c r="C170" s="16"/>
       <c r="D170" s="16"/>
@@ -5798,7 +5822,7 @@
       <c r="N170" s="19"/>
     </row>
     <row r="171">
-      <c r="A171" s="20"/>
+      <c r="A171" s="21"/>
       <c r="B171" s="16"/>
       <c r="C171" s="16"/>
       <c r="D171" s="16"/>
@@ -5820,7 +5844,7 @@
       <c r="N171" s="19"/>
     </row>
     <row r="172">
-      <c r="A172" s="20"/>
+      <c r="A172" s="21"/>
       <c r="B172" s="16"/>
       <c r="C172" s="16"/>
       <c r="D172" s="16"/>
@@ -5842,7 +5866,7 @@
       <c r="N172" s="19"/>
     </row>
     <row r="173">
-      <c r="A173" s="20"/>
+      <c r="A173" s="21"/>
       <c r="B173" s="16"/>
       <c r="C173" s="16"/>
       <c r="D173" s="16"/>
@@ -5864,7 +5888,7 @@
       <c r="N173" s="19"/>
     </row>
     <row r="174">
-      <c r="A174" s="20"/>
+      <c r="A174" s="21"/>
       <c r="B174" s="16"/>
       <c r="C174" s="16"/>
       <c r="D174" s="16"/>
@@ -5886,7 +5910,7 @@
       <c r="N174" s="19"/>
     </row>
     <row r="175">
-      <c r="A175" s="20"/>
+      <c r="A175" s="21"/>
       <c r="B175" s="16"/>
       <c r="C175" s="16"/>
       <c r="D175" s="16"/>
@@ -5908,7 +5932,7 @@
       <c r="N175" s="19"/>
     </row>
     <row r="176">
-      <c r="A176" s="20"/>
+      <c r="A176" s="21"/>
       <c r="B176" s="16"/>
       <c r="C176" s="16"/>
       <c r="D176" s="16"/>
@@ -5930,7 +5954,7 @@
       <c r="N176" s="19"/>
     </row>
     <row r="177">
-      <c r="A177" s="20"/>
+      <c r="A177" s="21"/>
       <c r="B177" s="16"/>
       <c r="C177" s="16"/>
       <c r="D177" s="16"/>
@@ -5952,7 +5976,7 @@
       <c r="N177" s="19"/>
     </row>
     <row r="178">
-      <c r="A178" s="20"/>
+      <c r="A178" s="21"/>
       <c r="B178" s="16"/>
       <c r="C178" s="16"/>
       <c r="D178" s="16"/>
@@ -5974,7 +5998,7 @@
       <c r="N178" s="19"/>
     </row>
     <row r="179">
-      <c r="A179" s="20"/>
+      <c r="A179" s="21"/>
       <c r="B179" s="16"/>
       <c r="C179" s="16"/>
       <c r="D179" s="16"/>
@@ -5996,7 +6020,7 @@
       <c r="N179" s="19"/>
     </row>
     <row r="180">
-      <c r="A180" s="20"/>
+      <c r="A180" s="21"/>
       <c r="B180" s="16"/>
       <c r="C180" s="16"/>
       <c r="D180" s="16"/>
@@ -6018,7 +6042,7 @@
       <c r="N180" s="19"/>
     </row>
     <row r="181">
-      <c r="A181" s="20"/>
+      <c r="A181" s="21"/>
       <c r="B181" s="16"/>
       <c r="C181" s="16"/>
       <c r="D181" s="16"/>
@@ -6040,7 +6064,7 @@
       <c r="N181" s="19"/>
     </row>
     <row r="182">
-      <c r="A182" s="20"/>
+      <c r="A182" s="21"/>
       <c r="B182" s="16"/>
       <c r="C182" s="16"/>
       <c r="D182" s="16"/>
@@ -6062,7 +6086,7 @@
       <c r="N182" s="19"/>
     </row>
     <row r="183">
-      <c r="A183" s="20"/>
+      <c r="A183" s="21"/>
       <c r="B183" s="16"/>
       <c r="C183" s="16"/>
       <c r="D183" s="16"/>
@@ -6084,7 +6108,7 @@
       <c r="N183" s="19"/>
     </row>
     <row r="184">
-      <c r="A184" s="20"/>
+      <c r="A184" s="21"/>
       <c r="B184" s="16"/>
       <c r="C184" s="16"/>
       <c r="D184" s="16"/>
@@ -6106,7 +6130,7 @@
       <c r="N184" s="19"/>
     </row>
     <row r="185">
-      <c r="A185" s="20"/>
+      <c r="A185" s="21"/>
       <c r="B185" s="16"/>
       <c r="C185" s="16"/>
       <c r="D185" s="16"/>
@@ -6128,7 +6152,7 @@
       <c r="N185" s="19"/>
     </row>
     <row r="186">
-      <c r="A186" s="20"/>
+      <c r="A186" s="21"/>
       <c r="B186" s="16"/>
       <c r="C186" s="16"/>
       <c r="D186" s="16"/>
@@ -6150,7 +6174,7 @@
       <c r="N186" s="19"/>
     </row>
     <row r="187">
-      <c r="A187" s="20"/>
+      <c r="A187" s="21"/>
       <c r="B187" s="16"/>
       <c r="C187" s="16"/>
       <c r="D187" s="16"/>
@@ -6172,7 +6196,7 @@
       <c r="N187" s="19"/>
     </row>
     <row r="188">
-      <c r="A188" s="20"/>
+      <c r="A188" s="21"/>
       <c r="B188" s="16"/>
       <c r="C188" s="16"/>
       <c r="D188" s="16"/>
@@ -6194,7 +6218,7 @@
       <c r="N188" s="19"/>
     </row>
     <row r="189">
-      <c r="A189" s="20"/>
+      <c r="A189" s="21"/>
       <c r="B189" s="16"/>
       <c r="C189" s="16"/>
       <c r="D189" s="16"/>
@@ -6216,7 +6240,7 @@
       <c r="N189" s="19"/>
     </row>
     <row r="190">
-      <c r="A190" s="20"/>
+      <c r="A190" s="21"/>
       <c r="B190" s="16"/>
       <c r="C190" s="16"/>
       <c r="D190" s="16"/>
@@ -6238,7 +6262,7 @@
       <c r="N190" s="19"/>
     </row>
     <row r="191">
-      <c r="A191" s="20"/>
+      <c r="A191" s="21"/>
       <c r="B191" s="16"/>
       <c r="C191" s="16"/>
       <c r="D191" s="16"/>
@@ -6260,7 +6284,7 @@
       <c r="N191" s="19"/>
     </row>
     <row r="192">
-      <c r="A192" s="20"/>
+      <c r="A192" s="21"/>
       <c r="B192" s="16"/>
       <c r="C192" s="16"/>
       <c r="D192" s="16"/>
@@ -6282,7 +6306,7 @@
       <c r="N192" s="19"/>
     </row>
     <row r="193">
-      <c r="A193" s="20"/>
+      <c r="A193" s="21"/>
       <c r="B193" s="16"/>
       <c r="C193" s="16"/>
       <c r="D193" s="16"/>
@@ -6304,7 +6328,7 @@
       <c r="N193" s="19"/>
     </row>
     <row r="194">
-      <c r="A194" s="20"/>
+      <c r="A194" s="21"/>
       <c r="B194" s="16"/>
       <c r="C194" s="16"/>
       <c r="D194" s="16"/>
@@ -6326,7 +6350,7 @@
       <c r="N194" s="19"/>
     </row>
     <row r="195">
-      <c r="A195" s="20"/>
+      <c r="A195" s="21"/>
       <c r="B195" s="16"/>
       <c r="C195" s="16"/>
       <c r="D195" s="16"/>
@@ -6348,7 +6372,7 @@
       <c r="N195" s="19"/>
     </row>
     <row r="196">
-      <c r="A196" s="20"/>
+      <c r="A196" s="21"/>
       <c r="B196" s="16"/>
       <c r="C196" s="16"/>
       <c r="D196" s="16"/>
@@ -6370,7 +6394,7 @@
       <c r="N196" s="19"/>
     </row>
     <row r="197">
-      <c r="A197" s="20"/>
+      <c r="A197" s="21"/>
       <c r="B197" s="16"/>
       <c r="C197" s="16"/>
       <c r="D197" s="16"/>
@@ -6392,7 +6416,7 @@
       <c r="N197" s="19"/>
     </row>
     <row r="198">
-      <c r="A198" s="20"/>
+      <c r="A198" s="21"/>
       <c r="B198" s="16"/>
       <c r="C198" s="16"/>
       <c r="D198" s="16"/>
@@ -6414,7 +6438,7 @@
       <c r="N198" s="19"/>
     </row>
     <row r="199">
-      <c r="A199" s="20"/>
+      <c r="A199" s="21"/>
       <c r="B199" s="16"/>
       <c r="C199" s="16"/>
       <c r="D199" s="16"/>
@@ -6436,7 +6460,7 @@
       <c r="N199" s="19"/>
     </row>
     <row r="200">
-      <c r="A200" s="20"/>
+      <c r="A200" s="21"/>
       <c r="B200" s="16"/>
       <c r="C200" s="16"/>
       <c r="D200" s="16"/>
@@ -6458,7 +6482,7 @@
       <c r="N200" s="19"/>
     </row>
     <row r="201">
-      <c r="A201" s="20"/>
+      <c r="A201" s="21"/>
       <c r="B201" s="16"/>
       <c r="C201" s="16"/>
       <c r="D201" s="16"/>
@@ -6480,7 +6504,7 @@
       <c r="N201" s="19"/>
     </row>
     <row r="202">
-      <c r="A202" s="20"/>
+      <c r="A202" s="21"/>
       <c r="B202" s="16"/>
       <c r="C202" s="16"/>
       <c r="D202" s="16"/>
@@ -6502,7 +6526,7 @@
       <c r="N202" s="19"/>
     </row>
     <row r="203">
-      <c r="A203" s="20"/>
+      <c r="A203" s="21"/>
       <c r="B203" s="16"/>
       <c r="C203" s="16"/>
       <c r="D203" s="16"/>
@@ -6524,7 +6548,7 @@
       <c r="N203" s="19"/>
     </row>
     <row r="204">
-      <c r="A204" s="20"/>
+      <c r="A204" s="21"/>
       <c r="B204" s="16"/>
       <c r="C204" s="16"/>
       <c r="D204" s="16"/>
@@ -6546,7 +6570,7 @@
       <c r="N204" s="19"/>
     </row>
     <row r="205">
-      <c r="A205" s="20"/>
+      <c r="A205" s="21"/>
       <c r="B205" s="16"/>
       <c r="C205" s="16"/>
       <c r="D205" s="16"/>
@@ -6568,7 +6592,7 @@
       <c r="N205" s="19"/>
     </row>
     <row r="206">
-      <c r="A206" s="20"/>
+      <c r="A206" s="21"/>
       <c r="B206" s="16"/>
       <c r="C206" s="16"/>
       <c r="D206" s="16"/>
@@ -6590,7 +6614,7 @@
       <c r="N206" s="19"/>
     </row>
     <row r="207">
-      <c r="A207" s="20"/>
+      <c r="A207" s="21"/>
       <c r="B207" s="16"/>
       <c r="C207" s="16"/>
       <c r="D207" s="16"/>
@@ -6612,7 +6636,7 @@
       <c r="N207" s="19"/>
     </row>
     <row r="208">
-      <c r="A208" s="20"/>
+      <c r="A208" s="21"/>
       <c r="B208" s="16"/>
       <c r="C208" s="16"/>
       <c r="D208" s="16"/>
@@ -6634,7 +6658,7 @@
       <c r="N208" s="19"/>
     </row>
     <row r="209">
-      <c r="A209" s="20"/>
+      <c r="A209" s="21"/>
       <c r="B209" s="16"/>
       <c r="C209" s="16"/>
       <c r="D209" s="16"/>
@@ -6656,7 +6680,7 @@
       <c r="N209" s="19"/>
     </row>
     <row r="210">
-      <c r="A210" s="20"/>
+      <c r="A210" s="21"/>
       <c r="B210" s="16"/>
       <c r="C210" s="16"/>
       <c r="D210" s="16"/>
@@ -6678,7 +6702,7 @@
       <c r="N210" s="19"/>
     </row>
     <row r="211">
-      <c r="A211" s="20"/>
+      <c r="A211" s="21"/>
       <c r="B211" s="16"/>
       <c r="C211" s="16"/>
       <c r="D211" s="16"/>
@@ -6700,7 +6724,7 @@
       <c r="N211" s="19"/>
     </row>
     <row r="212">
-      <c r="A212" s="20"/>
+      <c r="A212" s="21"/>
       <c r="B212" s="16"/>
       <c r="C212" s="16"/>
       <c r="D212" s="16"/>
@@ -6722,7 +6746,7 @@
       <c r="N212" s="19"/>
     </row>
     <row r="213">
-      <c r="A213" s="20"/>
+      <c r="A213" s="21"/>
       <c r="B213" s="16"/>
       <c r="C213" s="16"/>
       <c r="D213" s="16"/>
@@ -6744,7 +6768,7 @@
       <c r="N213" s="19"/>
     </row>
     <row r="214">
-      <c r="A214" s="20"/>
+      <c r="A214" s="21"/>
       <c r="B214" s="16"/>
       <c r="C214" s="16"/>
       <c r="D214" s="16"/>
@@ -6766,7 +6790,7 @@
       <c r="N214" s="19"/>
     </row>
     <row r="215">
-      <c r="A215" s="20"/>
+      <c r="A215" s="21"/>
       <c r="B215" s="16"/>
       <c r="C215" s="16"/>
       <c r="D215" s="16"/>
@@ -6788,7 +6812,7 @@
       <c r="N215" s="19"/>
     </row>
     <row r="216">
-      <c r="A216" s="20"/>
+      <c r="A216" s="21"/>
       <c r="B216" s="16"/>
       <c r="C216" s="16"/>
       <c r="D216" s="16"/>
@@ -6810,7 +6834,7 @@
       <c r="N216" s="19"/>
     </row>
     <row r="217">
-      <c r="A217" s="20"/>
+      <c r="A217" s="21"/>
       <c r="B217" s="16"/>
       <c r="C217" s="16"/>
       <c r="D217" s="16"/>
@@ -6832,7 +6856,7 @@
       <c r="N217" s="19"/>
     </row>
     <row r="218">
-      <c r="A218" s="20"/>
+      <c r="A218" s="21"/>
       <c r="B218" s="16"/>
       <c r="C218" s="16"/>
       <c r="D218" s="16"/>
@@ -6854,7 +6878,7 @@
       <c r="N218" s="19"/>
     </row>
     <row r="219">
-      <c r="A219" s="20"/>
+      <c r="A219" s="21"/>
       <c r="B219" s="16"/>
       <c r="C219" s="16"/>
       <c r="D219" s="16"/>
@@ -6876,7 +6900,7 @@
       <c r="N219" s="19"/>
     </row>
     <row r="220">
-      <c r="A220" s="20"/>
+      <c r="A220" s="21"/>
       <c r="B220" s="16"/>
       <c r="C220" s="16"/>
       <c r="D220" s="16"/>
@@ -6898,7 +6922,7 @@
       <c r="N220" s="19"/>
     </row>
     <row r="221">
-      <c r="A221" s="20"/>
+      <c r="A221" s="21"/>
       <c r="B221" s="16"/>
       <c r="C221" s="16"/>
       <c r="D221" s="16"/>
@@ -6920,7 +6944,7 @@
       <c r="N221" s="19"/>
     </row>
     <row r="222">
-      <c r="A222" s="20"/>
+      <c r="A222" s="21"/>
       <c r="B222" s="16"/>
       <c r="C222" s="16"/>
       <c r="D222" s="16"/>
@@ -6942,7 +6966,7 @@
       <c r="N222" s="19"/>
     </row>
     <row r="223">
-      <c r="A223" s="20"/>
+      <c r="A223" s="21"/>
       <c r="B223" s="16"/>
       <c r="C223" s="16"/>
       <c r="D223" s="16"/>
@@ -6964,7 +6988,7 @@
       <c r="N223" s="19"/>
     </row>
     <row r="224">
-      <c r="A224" s="20"/>
+      <c r="A224" s="21"/>
       <c r="B224" s="16"/>
       <c r="C224" s="16"/>
       <c r="D224" s="16"/>
@@ -6986,7 +7010,7 @@
       <c r="N224" s="19"/>
     </row>
     <row r="225">
-      <c r="A225" s="20"/>
+      <c r="A225" s="21"/>
       <c r="B225" s="16"/>
       <c r="C225" s="16"/>
       <c r="D225" s="16"/>
@@ -7008,7 +7032,7 @@
       <c r="N225" s="19"/>
     </row>
     <row r="226">
-      <c r="A226" s="20"/>
+      <c r="A226" s="21"/>
       <c r="B226" s="16"/>
       <c r="C226" s="16"/>
       <c r="D226" s="16"/>
@@ -7030,7 +7054,7 @@
       <c r="N226" s="19"/>
     </row>
     <row r="227">
-      <c r="A227" s="20"/>
+      <c r="A227" s="21"/>
       <c r="B227" s="16"/>
       <c r="C227" s="16"/>
       <c r="D227" s="16"/>
@@ -7052,7 +7076,7 @@
       <c r="N227" s="19"/>
     </row>
     <row r="228">
-      <c r="A228" s="20"/>
+      <c r="A228" s="21"/>
       <c r="B228" s="16"/>
       <c r="C228" s="16"/>
       <c r="D228" s="16"/>
@@ -7074,7 +7098,7 @@
       <c r="N228" s="19"/>
     </row>
     <row r="229">
-      <c r="A229" s="20"/>
+      <c r="A229" s="21"/>
       <c r="B229" s="16"/>
       <c r="C229" s="16"/>
       <c r="D229" s="16"/>
@@ -7096,7 +7120,7 @@
       <c r="N229" s="19"/>
     </row>
     <row r="230">
-      <c r="A230" s="20"/>
+      <c r="A230" s="21"/>
       <c r="B230" s="16"/>
       <c r="C230" s="16"/>
       <c r="D230" s="16"/>
@@ -7118,7 +7142,7 @@
       <c r="N230" s="19"/>
     </row>
     <row r="231">
-      <c r="A231" s="20"/>
+      <c r="A231" s="21"/>
       <c r="B231" s="16"/>
       <c r="C231" s="16"/>
       <c r="D231" s="16"/>
@@ -7140,7 +7164,7 @@
       <c r="N231" s="19"/>
     </row>
     <row r="232">
-      <c r="A232" s="20"/>
+      <c r="A232" s="21"/>
       <c r="B232" s="16"/>
       <c r="C232" s="16"/>
       <c r="D232" s="16"/>
@@ -7162,7 +7186,7 @@
       <c r="N232" s="19"/>
     </row>
     <row r="233">
-      <c r="A233" s="20"/>
+      <c r="A233" s="21"/>
       <c r="B233" s="16"/>
       <c r="C233" s="16"/>
       <c r="D233" s="16"/>
@@ -7184,7 +7208,7 @@
       <c r="N233" s="19"/>
     </row>
     <row r="234">
-      <c r="A234" s="20"/>
+      <c r="A234" s="21"/>
       <c r="B234" s="16"/>
       <c r="C234" s="16"/>
       <c r="D234" s="16"/>
@@ -7206,7 +7230,7 @@
       <c r="N234" s="19"/>
     </row>
     <row r="235">
-      <c r="A235" s="20"/>
+      <c r="A235" s="21"/>
       <c r="B235" s="16"/>
       <c r="C235" s="16"/>
       <c r="D235" s="16"/>
@@ -7228,7 +7252,7 @@
       <c r="N235" s="19"/>
     </row>
     <row r="236">
-      <c r="A236" s="20"/>
+      <c r="A236" s="21"/>
       <c r="B236" s="16"/>
       <c r="C236" s="16"/>
       <c r="D236" s="16"/>
@@ -7250,7 +7274,7 @@
       <c r="N236" s="19"/>
     </row>
     <row r="237">
-      <c r="A237" s="20"/>
+      <c r="A237" s="21"/>
       <c r="B237" s="16"/>
       <c r="C237" s="16"/>
       <c r="D237" s="16"/>
@@ -7272,7 +7296,7 @@
       <c r="N237" s="19"/>
     </row>
     <row r="238">
-      <c r="A238" s="20"/>
+      <c r="A238" s="21"/>
       <c r="B238" s="16"/>
       <c r="C238" s="16"/>
       <c r="D238" s="16"/>
@@ -7294,7 +7318,7 @@
       <c r="N238" s="19"/>
     </row>
     <row r="239">
-      <c r="A239" s="20"/>
+      <c r="A239" s="21"/>
       <c r="B239" s="16"/>
       <c r="C239" s="16"/>
       <c r="D239" s="16"/>
@@ -7316,7 +7340,7 @@
       <c r="N239" s="19"/>
     </row>
     <row r="240">
-      <c r="A240" s="20"/>
+      <c r="A240" s="21"/>
       <c r="B240" s="16"/>
       <c r="C240" s="16"/>
       <c r="D240" s="16"/>
@@ -7338,7 +7362,7 @@
       <c r="N240" s="19"/>
     </row>
     <row r="241">
-      <c r="A241" s="20"/>
+      <c r="A241" s="21"/>
       <c r="B241" s="16"/>
       <c r="C241" s="16"/>
       <c r="D241" s="16"/>
@@ -7360,7 +7384,7 @@
       <c r="N241" s="19"/>
     </row>
     <row r="242">
-      <c r="A242" s="20"/>
+      <c r="A242" s="21"/>
       <c r="B242" s="16"/>
       <c r="C242" s="16"/>
       <c r="D242" s="16"/>
@@ -7382,7 +7406,7 @@
       <c r="N242" s="19"/>
     </row>
     <row r="243">
-      <c r="A243" s="20"/>
+      <c r="A243" s="21"/>
       <c r="B243" s="16"/>
       <c r="C243" s="16"/>
       <c r="D243" s="16"/>
@@ -7404,7 +7428,7 @@
       <c r="N243" s="19"/>
     </row>
     <row r="244">
-      <c r="A244" s="20"/>
+      <c r="A244" s="21"/>
       <c r="B244" s="16"/>
       <c r="C244" s="16"/>
       <c r="D244" s="16"/>
@@ -7426,7 +7450,7 @@
       <c r="N244" s="19"/>
     </row>
     <row r="245">
-      <c r="A245" s="20"/>
+      <c r="A245" s="21"/>
       <c r="B245" s="16"/>
       <c r="C245" s="16"/>
       <c r="D245" s="16"/>
@@ -7448,7 +7472,7 @@
       <c r="N245" s="19"/>
     </row>
     <row r="246">
-      <c r="A246" s="20"/>
+      <c r="A246" s="21"/>
       <c r="B246" s="16"/>
       <c r="C246" s="16"/>
       <c r="D246" s="16"/>
@@ -7470,7 +7494,7 @@
       <c r="N246" s="19"/>
     </row>
     <row r="247">
-      <c r="A247" s="20"/>
+      <c r="A247" s="21"/>
       <c r="B247" s="16"/>
       <c r="C247" s="16"/>
       <c r="D247" s="16"/>
@@ -7492,7 +7516,7 @@
       <c r="N247" s="19"/>
     </row>
     <row r="248">
-      <c r="A248" s="20"/>
+      <c r="A248" s="21"/>
       <c r="B248" s="16"/>
       <c r="C248" s="16"/>
       <c r="D248" s="16"/>
@@ -7514,7 +7538,7 @@
       <c r="N248" s="19"/>
     </row>
     <row r="249">
-      <c r="A249" s="20"/>
+      <c r="A249" s="21"/>
       <c r="B249" s="16"/>
       <c r="C249" s="16"/>
       <c r="D249" s="16"/>
@@ -7536,7 +7560,7 @@
       <c r="N249" s="19"/>
     </row>
     <row r="250">
-      <c r="A250" s="20"/>
+      <c r="A250" s="21"/>
       <c r="B250" s="16"/>
       <c r="C250" s="16"/>
       <c r="D250" s="16"/>
@@ -7558,7 +7582,7 @@
       <c r="N250" s="19"/>
     </row>
     <row r="251">
-      <c r="A251" s="20"/>
+      <c r="A251" s="21"/>
       <c r="B251" s="16"/>
       <c r="C251" s="16"/>
       <c r="D251" s="16"/>
@@ -7580,7 +7604,7 @@
       <c r="N251" s="19"/>
     </row>
     <row r="252">
-      <c r="A252" s="20"/>
+      <c r="A252" s="21"/>
       <c r="B252" s="16"/>
       <c r="C252" s="16"/>
       <c r="D252" s="16"/>
@@ -7602,7 +7626,7 @@
       <c r="N252" s="19"/>
     </row>
     <row r="253">
-      <c r="A253" s="20"/>
+      <c r="A253" s="21"/>
       <c r="B253" s="16"/>
       <c r="C253" s="16"/>
       <c r="D253" s="16"/>
@@ -7624,7 +7648,7 @@
       <c r="N253" s="19"/>
     </row>
     <row r="254">
-      <c r="A254" s="20"/>
+      <c r="A254" s="21"/>
       <c r="B254" s="16"/>
       <c r="C254" s="16"/>
       <c r="D254" s="16"/>
@@ -7646,7 +7670,7 @@
       <c r="N254" s="19"/>
     </row>
     <row r="255">
-      <c r="A255" s="20"/>
+      <c r="A255" s="21"/>
       <c r="B255" s="16"/>
       <c r="C255" s="16"/>
       <c r="D255" s="16"/>
@@ -7668,7 +7692,7 @@
       <c r="N255" s="19"/>
     </row>
     <row r="256">
-      <c r="A256" s="20"/>
+      <c r="A256" s="21"/>
       <c r="B256" s="16"/>
       <c r="C256" s="16"/>
       <c r="D256" s="16"/>
@@ -7690,7 +7714,7 @@
       <c r="N256" s="19"/>
     </row>
     <row r="257">
-      <c r="A257" s="20"/>
+      <c r="A257" s="21"/>
       <c r="B257" s="16"/>
       <c r="C257" s="16"/>
       <c r="D257" s="16"/>
@@ -7712,7 +7736,7 @@
       <c r="N257" s="19"/>
     </row>
     <row r="258">
-      <c r="A258" s="20"/>
+      <c r="A258" s="21"/>
       <c r="B258" s="16"/>
       <c r="C258" s="16"/>
       <c r="D258" s="16"/>
@@ -7734,7 +7758,7 @@
       <c r="N258" s="19"/>
     </row>
     <row r="259">
-      <c r="A259" s="20"/>
+      <c r="A259" s="21"/>
       <c r="B259" s="16"/>
       <c r="C259" s="16"/>
       <c r="D259" s="16"/>
@@ -7756,7 +7780,7 @@
       <c r="N259" s="19"/>
     </row>
     <row r="260">
-      <c r="A260" s="20"/>
+      <c r="A260" s="21"/>
       <c r="B260" s="16"/>
       <c r="C260" s="16"/>
       <c r="D260" s="16"/>
@@ -7778,7 +7802,7 @@
       <c r="N260" s="19"/>
     </row>
     <row r="261">
-      <c r="A261" s="20"/>
+      <c r="A261" s="21"/>
       <c r="B261" s="16"/>
       <c r="C261" s="16"/>
       <c r="D261" s="16"/>
@@ -7800,7 +7824,7 @@
       <c r="N261" s="19"/>
     </row>
     <row r="262">
-      <c r="A262" s="20"/>
+      <c r="A262" s="21"/>
       <c r="B262" s="16"/>
       <c r="C262" s="16"/>
       <c r="D262" s="16"/>
@@ -7822,7 +7846,7 @@
       <c r="N262" s="19"/>
     </row>
     <row r="263">
-      <c r="A263" s="20"/>
+      <c r="A263" s="21"/>
       <c r="B263" s="16"/>
       <c r="C263" s="16"/>
       <c r="D263" s="16"/>
@@ -7844,7 +7868,7 @@
       <c r="N263" s="19"/>
     </row>
     <row r="264">
-      <c r="A264" s="20"/>
+      <c r="A264" s="21"/>
       <c r="B264" s="16"/>
       <c r="C264" s="16"/>
       <c r="D264" s="16"/>
@@ -7866,7 +7890,7 @@
       <c r="N264" s="19"/>
     </row>
     <row r="265">
-      <c r="A265" s="20"/>
+      <c r="A265" s="21"/>
       <c r="B265" s="16"/>
       <c r="C265" s="16"/>
       <c r="D265" s="16"/>
@@ -7888,7 +7912,7 @@
       <c r="N265" s="19"/>
     </row>
     <row r="266">
-      <c r="A266" s="20"/>
+      <c r="A266" s="21"/>
       <c r="B266" s="16"/>
       <c r="C266" s="16"/>
       <c r="D266" s="16"/>
@@ -7910,7 +7934,7 @@
       <c r="N266" s="19"/>
     </row>
     <row r="267">
-      <c r="A267" s="20"/>
+      <c r="A267" s="21"/>
       <c r="B267" s="16"/>
       <c r="C267" s="16"/>
       <c r="D267" s="16"/>
@@ -7932,7 +7956,7 @@
       <c r="N267" s="19"/>
     </row>
     <row r="268">
-      <c r="A268" s="20"/>
+      <c r="A268" s="21"/>
       <c r="B268" s="16"/>
       <c r="C268" s="16"/>
       <c r="D268" s="16"/>
@@ -7954,7 +7978,7 @@
       <c r="N268" s="19"/>
     </row>
     <row r="269">
-      <c r="A269" s="20"/>
+      <c r="A269" s="21"/>
       <c r="B269" s="16"/>
       <c r="C269" s="16"/>
       <c r="D269" s="16"/>
@@ -7976,7 +8000,7 @@
       <c r="N269" s="19"/>
     </row>
     <row r="270">
-      <c r="A270" s="20"/>
+      <c r="A270" s="21"/>
       <c r="B270" s="16"/>
       <c r="C270" s="16"/>
       <c r="D270" s="16"/>
@@ -7998,7 +8022,7 @@
       <c r="N270" s="19"/>
     </row>
     <row r="271">
-      <c r="A271" s="20"/>
+      <c r="A271" s="21"/>
       <c r="B271" s="16"/>
       <c r="C271" s="16"/>
       <c r="D271" s="16"/>
@@ -8020,7 +8044,7 @@
       <c r="N271" s="19"/>
     </row>
     <row r="272">
-      <c r="A272" s="20"/>
+      <c r="A272" s="21"/>
       <c r="B272" s="16"/>
       <c r="C272" s="16"/>
       <c r="D272" s="16"/>
@@ -8042,7 +8066,7 @@
       <c r="N272" s="19"/>
     </row>
     <row r="273">
-      <c r="A273" s="20"/>
+      <c r="A273" s="21"/>
       <c r="B273" s="16"/>
       <c r="C273" s="16"/>
       <c r="D273" s="16"/>
@@ -8064,7 +8088,7 @@
       <c r="N273" s="19"/>
     </row>
     <row r="274">
-      <c r="A274" s="20"/>
+      <c r="A274" s="21"/>
       <c r="B274" s="16"/>
       <c r="C274" s="16"/>
       <c r="D274" s="16"/>
@@ -8086,7 +8110,7 @@
       <c r="N274" s="19"/>
     </row>
     <row r="275">
-      <c r="A275" s="20"/>
+      <c r="A275" s="21"/>
       <c r="B275" s="16"/>
       <c r="C275" s="16"/>
       <c r="D275" s="16"/>
@@ -8108,7 +8132,7 @@
       <c r="N275" s="19"/>
     </row>
     <row r="276">
-      <c r="A276" s="20"/>
+      <c r="A276" s="21"/>
       <c r="B276" s="16"/>
       <c r="C276" s="16"/>
       <c r="D276" s="16"/>
@@ -8130,7 +8154,7 @@
       <c r="N276" s="19"/>
     </row>
     <row r="277">
-      <c r="A277" s="20"/>
+      <c r="A277" s="21"/>
       <c r="B277" s="16"/>
       <c r="C277" s="16"/>
       <c r="D277" s="16"/>
@@ -8152,7 +8176,7 @@
       <c r="N277" s="19"/>
     </row>
     <row r="278">
-      <c r="A278" s="20"/>
+      <c r="A278" s="21"/>
       <c r="B278" s="16"/>
       <c r="C278" s="16"/>
       <c r="D278" s="16"/>
@@ -8174,7 +8198,7 @@
       <c r="N278" s="19"/>
     </row>
     <row r="279">
-      <c r="A279" s="20"/>
+      <c r="A279" s="21"/>
       <c r="B279" s="16"/>
       <c r="C279" s="16"/>
       <c r="D279" s="16"/>
@@ -8196,7 +8220,7 @@
       <c r="N279" s="19"/>
     </row>
     <row r="280">
-      <c r="A280" s="20"/>
+      <c r="A280" s="21"/>
       <c r="B280" s="16"/>
       <c r="C280" s="16"/>
       <c r="D280" s="16"/>
@@ -8218,7 +8242,7 @@
       <c r="N280" s="19"/>
     </row>
     <row r="281">
-      <c r="A281" s="20"/>
+      <c r="A281" s="21"/>
       <c r="B281" s="16"/>
       <c r="C281" s="16"/>
       <c r="D281" s="16"/>
@@ -8240,7 +8264,7 @@
       <c r="N281" s="19"/>
     </row>
     <row r="282">
-      <c r="A282" s="20"/>
+      <c r="A282" s="21"/>
       <c r="B282" s="16"/>
       <c r="C282" s="16"/>
       <c r="D282" s="16"/>
@@ -8262,7 +8286,7 @@
       <c r="N282" s="19"/>
     </row>
     <row r="283">
-      <c r="A283" s="20"/>
+      <c r="A283" s="21"/>
       <c r="B283" s="16"/>
       <c r="C283" s="16"/>
       <c r="D283" s="16"/>
@@ -8284,7 +8308,7 @@
       <c r="N283" s="19"/>
     </row>
     <row r="284">
-      <c r="A284" s="20"/>
+      <c r="A284" s="21"/>
       <c r="B284" s="16"/>
       <c r="C284" s="16"/>
       <c r="D284" s="16"/>
@@ -8306,7 +8330,7 @@
       <c r="N284" s="19"/>
     </row>
     <row r="285">
-      <c r="A285" s="20"/>
+      <c r="A285" s="21"/>
       <c r="B285" s="16"/>
       <c r="C285" s="16"/>
       <c r="D285" s="16"/>
@@ -8328,7 +8352,7 @@
       <c r="N285" s="19"/>
     </row>
     <row r="286">
-      <c r="A286" s="20"/>
+      <c r="A286" s="21"/>
       <c r="B286" s="16"/>
       <c r="C286" s="16"/>
       <c r="D286" s="16"/>
@@ -8350,7 +8374,7 @@
       <c r="N286" s="19"/>
     </row>
     <row r="287">
-      <c r="A287" s="20"/>
+      <c r="A287" s="21"/>
       <c r="B287" s="16"/>
       <c r="C287" s="16"/>
       <c r="D287" s="16"/>
@@ -8372,7 +8396,7 @@
       <c r="N287" s="19"/>
     </row>
     <row r="288">
-      <c r="A288" s="20"/>
+      <c r="A288" s="21"/>
       <c r="B288" s="16"/>
       <c r="C288" s="16"/>
       <c r="D288" s="16"/>
@@ -8394,7 +8418,7 @@
       <c r="N288" s="19"/>
     </row>
     <row r="289">
-      <c r="A289" s="20"/>
+      <c r="A289" s="21"/>
       <c r="B289" s="16"/>
       <c r="C289" s="16"/>
       <c r="D289" s="16"/>
@@ -8416,7 +8440,7 @@
       <c r="N289" s="19"/>
     </row>
     <row r="290">
-      <c r="A290" s="20"/>
+      <c r="A290" s="21"/>
       <c r="B290" s="16"/>
       <c r="C290" s="16"/>
       <c r="D290" s="16"/>
@@ -8438,7 +8462,7 @@
       <c r="N290" s="19"/>
     </row>
     <row r="291">
-      <c r="A291" s="20"/>
+      <c r="A291" s="21"/>
       <c r="B291" s="16"/>
       <c r="C291" s="16"/>
       <c r="D291" s="16"/>
@@ -8460,7 +8484,7 @@
       <c r="N291" s="19"/>
     </row>
     <row r="292">
-      <c r="A292" s="20"/>
+      <c r="A292" s="21"/>
       <c r="B292" s="16"/>
       <c r="C292" s="16"/>
       <c r="D292" s="16"/>
@@ -8482,7 +8506,7 @@
       <c r="N292" s="19"/>
     </row>
     <row r="293">
-      <c r="A293" s="20"/>
+      <c r="A293" s="21"/>
       <c r="B293" s="16"/>
       <c r="C293" s="16"/>
       <c r="D293" s="16"/>
@@ -8504,7 +8528,7 @@
       <c r="N293" s="19"/>
     </row>
     <row r="294">
-      <c r="A294" s="20"/>
+      <c r="A294" s="21"/>
       <c r="B294" s="16"/>
       <c r="C294" s="16"/>
       <c r="D294" s="16"/>
@@ -8526,7 +8550,7 @@
       <c r="N294" s="19"/>
     </row>
     <row r="295">
-      <c r="A295" s="20"/>
+      <c r="A295" s="21"/>
       <c r="B295" s="16"/>
       <c r="C295" s="16"/>
       <c r="D295" s="16"/>
@@ -8548,7 +8572,7 @@
       <c r="N295" s="19"/>
     </row>
     <row r="296">
-      <c r="A296" s="20"/>
+      <c r="A296" s="21"/>
       <c r="B296" s="16"/>
       <c r="C296" s="16"/>
       <c r="D296" s="16"/>
@@ -8570,7 +8594,7 @@
       <c r="N296" s="19"/>
     </row>
     <row r="297">
-      <c r="A297" s="20"/>
+      <c r="A297" s="21"/>
       <c r="B297" s="16"/>
       <c r="C297" s="16"/>
       <c r="D297" s="16"/>
@@ -8592,7 +8616,7 @@
       <c r="N297" s="19"/>
     </row>
     <row r="298">
-      <c r="A298" s="20"/>
+      <c r="A298" s="21"/>
       <c r="B298" s="16"/>
       <c r="C298" s="16"/>
       <c r="D298" s="16"/>
@@ -8614,7 +8638,7 @@
       <c r="N298" s="19"/>
     </row>
     <row r="299">
-      <c r="A299" s="20"/>
+      <c r="A299" s="21"/>
       <c r="B299" s="16"/>
       <c r="C299" s="16"/>
       <c r="D299" s="16"/>
@@ -8636,7 +8660,7 @@
       <c r="N299" s="19"/>
     </row>
     <row r="300">
-      <c r="A300" s="20"/>
+      <c r="A300" s="21"/>
       <c r="B300" s="16"/>
       <c r="C300" s="16"/>
       <c r="D300" s="16"/>
@@ -8658,7 +8682,7 @@
       <c r="N300" s="19"/>
     </row>
     <row r="301">
-      <c r="A301" s="20"/>
+      <c r="A301" s="21"/>
       <c r="B301" s="16"/>
       <c r="C301" s="16"/>
       <c r="D301" s="16"/>
@@ -8680,7 +8704,7 @@
       <c r="N301" s="19"/>
     </row>
     <row r="302">
-      <c r="A302" s="20"/>
+      <c r="A302" s="21"/>
       <c r="B302" s="16"/>
       <c r="C302" s="16"/>
       <c r="D302" s="16"/>
@@ -8702,7 +8726,7 @@
       <c r="N302" s="19"/>
     </row>
     <row r="303">
-      <c r="A303" s="20"/>
+      <c r="A303" s="21"/>
       <c r="B303" s="16"/>
       <c r="C303" s="16"/>
       <c r="D303" s="16"/>
@@ -8724,7 +8748,7 @@
       <c r="N303" s="19"/>
     </row>
     <row r="304">
-      <c r="A304" s="20"/>
+      <c r="A304" s="21"/>
       <c r="B304" s="16"/>
       <c r="C304" s="16"/>
       <c r="D304" s="16"/>
@@ -8746,7 +8770,7 @@
       <c r="N304" s="19"/>
     </row>
     <row r="305">
-      <c r="A305" s="20"/>
+      <c r="A305" s="21"/>
       <c r="B305" s="16"/>
       <c r="C305" s="16"/>
       <c r="D305" s="16"/>
@@ -8768,7 +8792,7 @@
       <c r="N305" s="19"/>
     </row>
     <row r="306">
-      <c r="A306" s="20"/>
+      <c r="A306" s="21"/>
       <c r="B306" s="16"/>
       <c r="C306" s="16"/>
       <c r="D306" s="16"/>
@@ -8790,7 +8814,7 @@
       <c r="N306" s="19"/>
     </row>
     <row r="307">
-      <c r="A307" s="20"/>
+      <c r="A307" s="21"/>
       <c r="B307" s="16"/>
       <c r="C307" s="16"/>
       <c r="D307" s="16"/>
@@ -8812,7 +8836,7 @@
       <c r="N307" s="19"/>
     </row>
     <row r="308">
-      <c r="A308" s="20"/>
+      <c r="A308" s="21"/>
       <c r="B308" s="16"/>
       <c r="C308" s="16"/>
       <c r="D308" s="16"/>
@@ -8834,7 +8858,7 @@
       <c r="N308" s="19"/>
     </row>
     <row r="309">
-      <c r="A309" s="20"/>
+      <c r="A309" s="21"/>
       <c r="B309" s="16"/>
       <c r="C309" s="16"/>
       <c r="D309" s="16"/>
@@ -8856,7 +8880,7 @@
       <c r="N309" s="19"/>
     </row>
     <row r="310">
-      <c r="A310" s="20"/>
+      <c r="A310" s="21"/>
       <c r="B310" s="16"/>
       <c r="C310" s="16"/>
       <c r="D310" s="16"/>
@@ -8878,7 +8902,7 @@
       <c r="N310" s="19"/>
     </row>
     <row r="311">
-      <c r="A311" s="20"/>
+      <c r="A311" s="21"/>
       <c r="B311" s="16"/>
       <c r="C311" s="16"/>
       <c r="D311" s="16"/>
@@ -8900,7 +8924,7 @@
       <c r="N311" s="19"/>
     </row>
     <row r="312">
-      <c r="A312" s="20"/>
+      <c r="A312" s="21"/>
       <c r="B312" s="16"/>
       <c r="C312" s="16"/>
       <c r="D312" s="16"/>
@@ -8922,7 +8946,7 @@
       <c r="N312" s="19"/>
     </row>
     <row r="313">
-      <c r="A313" s="20"/>
+      <c r="A313" s="21"/>
       <c r="B313" s="16"/>
       <c r="C313" s="16"/>
       <c r="D313" s="16"/>
@@ -8944,7 +8968,7 @@
       <c r="N313" s="19"/>
     </row>
     <row r="314">
-      <c r="A314" s="20"/>
+      <c r="A314" s="21"/>
       <c r="B314" s="16"/>
       <c r="C314" s="16"/>
       <c r="D314" s="16"/>
@@ -8966,7 +8990,7 @@
       <c r="N314" s="19"/>
     </row>
     <row r="315">
-      <c r="A315" s="20"/>
+      <c r="A315" s="21"/>
       <c r="B315" s="16"/>
       <c r="C315" s="16"/>
       <c r="D315" s="16"/>
@@ -8988,7 +9012,7 @@
       <c r="N315" s="19"/>
     </row>
     <row r="316">
-      <c r="A316" s="20"/>
+      <c r="A316" s="21"/>
       <c r="B316" s="16"/>
       <c r="C316" s="16"/>
       <c r="D316" s="16"/>
@@ -9010,7 +9034,7 @@
       <c r="N316" s="19"/>
     </row>
     <row r="317">
-      <c r="A317" s="20"/>
+      <c r="A317" s="21"/>
       <c r="B317" s="16"/>
       <c r="C317" s="16"/>
       <c r="D317" s="16"/>
@@ -9032,7 +9056,7 @@
       <c r="N317" s="19"/>
     </row>
     <row r="318">
-      <c r="A318" s="20"/>
+      <c r="A318" s="21"/>
       <c r="B318" s="16"/>
       <c r="C318" s="16"/>
       <c r="D318" s="16"/>
@@ -9054,7 +9078,7 @@
       <c r="N318" s="19"/>
     </row>
     <row r="319">
-      <c r="A319" s="20"/>
+      <c r="A319" s="21"/>
       <c r="B319" s="16"/>
       <c r="C319" s="16"/>
       <c r="D319" s="16"/>
@@ -9076,7 +9100,7 @@
       <c r="N319" s="19"/>
     </row>
     <row r="320">
-      <c r="A320" s="20"/>
+      <c r="A320" s="21"/>
       <c r="B320" s="16"/>
       <c r="C320" s="16"/>
       <c r="D320" s="16"/>
@@ -9098,7 +9122,7 @@
       <c r="N320" s="19"/>
     </row>
     <row r="321">
-      <c r="A321" s="20"/>
+      <c r="A321" s="21"/>
       <c r="B321" s="16"/>
       <c r="C321" s="16"/>
       <c r="D321" s="16"/>
@@ -9120,7 +9144,7 @@
       <c r="N321" s="19"/>
     </row>
     <row r="322">
-      <c r="A322" s="20"/>
+      <c r="A322" s="21"/>
       <c r="B322" s="16"/>
       <c r="C322" s="16"/>
       <c r="D322" s="16"/>
@@ -9142,7 +9166,7 @@
       <c r="N322" s="19"/>
     </row>
     <row r="323">
-      <c r="A323" s="20"/>
+      <c r="A323" s="21"/>
       <c r="B323" s="16"/>
       <c r="C323" s="16"/>
       <c r="D323" s="16"/>
@@ -9164,7 +9188,7 @@
       <c r="N323" s="19"/>
     </row>
     <row r="324">
-      <c r="A324" s="20"/>
+      <c r="A324" s="21"/>
       <c r="B324" s="16"/>
       <c r="C324" s="16"/>
       <c r="D324" s="16"/>
@@ -9186,7 +9210,7 @@
       <c r="N324" s="19"/>
     </row>
     <row r="325">
-      <c r="A325" s="20"/>
+      <c r="A325" s="21"/>
       <c r="B325" s="16"/>
       <c r="C325" s="16"/>
       <c r="D325" s="16"/>
@@ -9208,7 +9232,7 @@
       <c r="N325" s="19"/>
     </row>
     <row r="326">
-      <c r="A326" s="20"/>
+      <c r="A326" s="21"/>
       <c r="B326" s="16"/>
       <c r="C326" s="16"/>
       <c r="D326" s="16"/>
@@ -9230,7 +9254,7 @@
       <c r="N326" s="19"/>
     </row>
     <row r="327">
-      <c r="A327" s="20"/>
+      <c r="A327" s="21"/>
       <c r="B327" s="16"/>
       <c r="C327" s="16"/>
       <c r="D327" s="16"/>
@@ -9252,7 +9276,7 @@
       <c r="N327" s="19"/>
     </row>
     <row r="328">
-      <c r="A328" s="20"/>
+      <c r="A328" s="21"/>
       <c r="B328" s="16"/>
       <c r="C328" s="16"/>
       <c r="D328" s="16"/>
@@ -9274,7 +9298,7 @@
       <c r="N328" s="19"/>
     </row>
     <row r="329">
-      <c r="A329" s="20"/>
+      <c r="A329" s="21"/>
       <c r="B329" s="16"/>
       <c r="C329" s="16"/>
       <c r="D329" s="16"/>
@@ -9296,7 +9320,7 @@
       <c r="N329" s="19"/>
     </row>
     <row r="330">
-      <c r="A330" s="20"/>
+      <c r="A330" s="21"/>
       <c r="B330" s="16"/>
       <c r="C330" s="16"/>
       <c r="D330" s="16"/>
@@ -9318,7 +9342,7 @@
       <c r="N330" s="19"/>
     </row>
     <row r="331">
-      <c r="A331" s="20"/>
+      <c r="A331" s="21"/>
       <c r="B331" s="16"/>
       <c r="C331" s="16"/>
       <c r="D331" s="16"/>
@@ -9340,7 +9364,7 @@
       <c r="N331" s="19"/>
     </row>
     <row r="332">
-      <c r="A332" s="20"/>
+      <c r="A332" s="21"/>
       <c r="B332" s="16"/>
       <c r="C332" s="16"/>
       <c r="D332" s="16"/>
@@ -9362,7 +9386,7 @@
       <c r="N332" s="19"/>
     </row>
     <row r="333">
-      <c r="A333" s="20"/>
+      <c r="A333" s="21"/>
       <c r="B333" s="16"/>
       <c r="C333" s="16"/>
       <c r="D333" s="16"/>
@@ -9384,7 +9408,7 @@
       <c r="N333" s="19"/>
     </row>
     <row r="334">
-      <c r="A334" s="20"/>
+      <c r="A334" s="21"/>
       <c r="B334" s="16"/>
       <c r="C334" s="16"/>
       <c r="D334" s="16"/>
@@ -9406,7 +9430,7 @@
       <c r="N334" s="19"/>
     </row>
     <row r="335">
-      <c r="A335" s="20"/>
+      <c r="A335" s="21"/>
       <c r="B335" s="16"/>
       <c r="C335" s="16"/>
       <c r="D335" s="16"/>
@@ -9428,7 +9452,7 @@
       <c r="N335" s="19"/>
     </row>
     <row r="336">
-      <c r="A336" s="20"/>
+      <c r="A336" s="21"/>
       <c r="B336" s="16"/>
       <c r="C336" s="16"/>
       <c r="D336" s="16"/>
@@ -9450,7 +9474,7 @@
       <c r="N336" s="19"/>
     </row>
     <row r="337">
-      <c r="A337" s="20"/>
+      <c r="A337" s="21"/>
       <c r="B337" s="16"/>
       <c r="C337" s="16"/>
       <c r="D337" s="16"/>
@@ -9472,7 +9496,7 @@
       <c r="N337" s="19"/>
     </row>
     <row r="338">
-      <c r="A338" s="20"/>
+      <c r="A338" s="21"/>
       <c r="B338" s="16"/>
       <c r="C338" s="16"/>
       <c r="D338" s="16"/>
@@ -9494,7 +9518,7 @@
       <c r="N338" s="19"/>
     </row>
     <row r="339">
-      <c r="A339" s="20"/>
+      <c r="A339" s="21"/>
       <c r="B339" s="16"/>
       <c r="C339" s="16"/>
       <c r="D339" s="16"/>
@@ -9516,7 +9540,7 @@
       <c r="N339" s="19"/>
     </row>
     <row r="340">
-      <c r="A340" s="20"/>
+      <c r="A340" s="21"/>
       <c r="B340" s="16"/>
       <c r="C340" s="16"/>
       <c r="D340" s="16"/>
@@ -9538,7 +9562,7 @@
       <c r="N340" s="19"/>
     </row>
     <row r="341">
-      <c r="A341" s="20"/>
+      <c r="A341" s="21"/>
       <c r="B341" s="16"/>
       <c r="C341" s="16"/>
       <c r="D341" s="16"/>
@@ -9560,7 +9584,7 @@
       <c r="N341" s="19"/>
     </row>
     <row r="342">
-      <c r="A342" s="20"/>
+      <c r="A342" s="21"/>
       <c r="B342" s="16"/>
       <c r="C342" s="16"/>
       <c r="D342" s="16"/>
@@ -9582,7 +9606,7 @@
       <c r="N342" s="19"/>
     </row>
     <row r="343">
-      <c r="A343" s="20"/>
+      <c r="A343" s="21"/>
       <c r="B343" s="16"/>
       <c r="C343" s="16"/>
       <c r="D343" s="16"/>
@@ -9604,7 +9628,7 @@
       <c r="N343" s="19"/>
     </row>
     <row r="344">
-      <c r="A344" s="20"/>
+      <c r="A344" s="21"/>
       <c r="B344" s="16"/>
       <c r="C344" s="16"/>
       <c r="D344" s="16"/>
@@ -9626,7 +9650,7 @@
       <c r="N344" s="19"/>
     </row>
     <row r="345">
-      <c r="A345" s="20"/>
+      <c r="A345" s="21"/>
       <c r="B345" s="16"/>
       <c r="C345" s="16"/>
       <c r="D345" s="16"/>
@@ -9648,7 +9672,7 @@
       <c r="N345" s="19"/>
     </row>
     <row r="346">
-      <c r="A346" s="20"/>
+      <c r="A346" s="21"/>
       <c r="B346" s="16"/>
       <c r="C346" s="16"/>
       <c r="D346" s="16"/>
@@ -9670,7 +9694,7 @@
       <c r="N346" s="19"/>
     </row>
     <row r="347">
-      <c r="A347" s="20"/>
+      <c r="A347" s="21"/>
       <c r="B347" s="16"/>
       <c r="C347" s="16"/>
       <c r="D347" s="16"/>
@@ -9692,7 +9716,7 @@
       <c r="N347" s="19"/>
     </row>
     <row r="348">
-      <c r="A348" s="20"/>
+      <c r="A348" s="21"/>
       <c r="B348" s="16"/>
       <c r="C348" s="16"/>
       <c r="D348" s="16"/>
@@ -9714,7 +9738,7 @@
       <c r="N348" s="19"/>
     </row>
     <row r="349">
-      <c r="A349" s="20"/>
+      <c r="A349" s="21"/>
       <c r="B349" s="16"/>
       <c r="C349" s="16"/>
       <c r="D349" s="16"/>
@@ -9736,7 +9760,7 @@
       <c r="N349" s="19"/>
     </row>
     <row r="350">
-      <c r="A350" s="20"/>
+      <c r="A350" s="21"/>
       <c r="B350" s="16"/>
       <c r="C350" s="16"/>
       <c r="D350" s="16"/>
@@ -9758,7 +9782,7 @@
       <c r="N350" s="19"/>
     </row>
     <row r="351">
-      <c r="A351" s="20"/>
+      <c r="A351" s="21"/>
       <c r="B351" s="16"/>
       <c r="C351" s="16"/>
       <c r="D351" s="16"/>
@@ -9780,7 +9804,7 @@
       <c r="N351" s="19"/>
     </row>
     <row r="352">
-      <c r="A352" s="20"/>
+      <c r="A352" s="21"/>
       <c r="B352" s="16"/>
       <c r="C352" s="16"/>
       <c r="D352" s="16"/>
@@ -9802,7 +9826,7 @@
       <c r="N352" s="19"/>
     </row>
     <row r="353">
-      <c r="A353" s="20"/>
+      <c r="A353" s="21"/>
       <c r="B353" s="16"/>
       <c r="C353" s="16"/>
       <c r="D353" s="16"/>
@@ -9824,7 +9848,7 @@
       <c r="N353" s="19"/>
     </row>
     <row r="354">
-      <c r="A354" s="20"/>
+      <c r="A354" s="21"/>
       <c r="B354" s="16"/>
       <c r="C354" s="16"/>
       <c r="D354" s="16"/>
@@ -9846,7 +9870,7 @@
       <c r="N354" s="19"/>
     </row>
     <row r="355">
-      <c r="A355" s="20"/>
+      <c r="A355" s="21"/>
       <c r="B355" s="16"/>
       <c r="C355" s="16"/>
       <c r="D355" s="16"/>
@@ -9868,7 +9892,7 @@
       <c r="N355" s="19"/>
     </row>
     <row r="356">
-      <c r="A356" s="20"/>
+      <c r="A356" s="21"/>
       <c r="B356" s="16"/>
       <c r="C356" s="16"/>
       <c r="D356" s="16"/>
@@ -9890,7 +9914,7 @@
       <c r="N356" s="19"/>
     </row>
     <row r="357">
-      <c r="A357" s="20"/>
+      <c r="A357" s="21"/>
       <c r="B357" s="16"/>
       <c r="C357" s="16"/>
       <c r="D357" s="16"/>
@@ -9912,7 +9936,7 @@
       <c r="N357" s="19"/>
     </row>
     <row r="358">
-      <c r="A358" s="20"/>
+      <c r="A358" s="21"/>
       <c r="B358" s="16"/>
       <c r="C358" s="16"/>
       <c r="D358" s="16"/>
@@ -9934,7 +9958,7 @@
       <c r="N358" s="19"/>
     </row>
     <row r="359">
-      <c r="A359" s="20"/>
+      <c r="A359" s="21"/>
       <c r="B359" s="16"/>
       <c r="C359" s="16"/>
       <c r="D359" s="16"/>
@@ -9956,7 +9980,7 @@
       <c r="N359" s="19"/>
     </row>
     <row r="360">
-      <c r="A360" s="20"/>
+      <c r="A360" s="21"/>
       <c r="B360" s="16"/>
       <c r="C360" s="16"/>
       <c r="D360" s="16"/>
@@ -9978,7 +10002,7 @@
       <c r="N360" s="19"/>
     </row>
     <row r="361">
-      <c r="A361" s="20"/>
+      <c r="A361" s="21"/>
       <c r="B361" s="16"/>
       <c r="C361" s="16"/>
       <c r="D361" s="16"/>
@@ -10000,7 +10024,7 @@
       <c r="N361" s="19"/>
     </row>
     <row r="362">
-      <c r="A362" s="20"/>
+      <c r="A362" s="21"/>
       <c r="B362" s="16"/>
       <c r="C362" s="16"/>
       <c r="D362" s="16"/>
@@ -10022,7 +10046,7 @@
       <c r="N362" s="19"/>
     </row>
     <row r="363">
-      <c r="A363" s="20"/>
+      <c r="A363" s="21"/>
       <c r="B363" s="16"/>
       <c r="C363" s="16"/>
       <c r="D363" s="16"/>
@@ -10044,7 +10068,7 @@
       <c r="N363" s="19"/>
     </row>
     <row r="364">
-      <c r="A364" s="20"/>
+      <c r="A364" s="21"/>
       <c r="B364" s="16"/>
       <c r="C364" s="16"/>
       <c r="D364" s="16"/>
@@ -10066,7 +10090,7 @@
       <c r="N364" s="19"/>
     </row>
     <row r="365">
-      <c r="A365" s="20"/>
+      <c r="A365" s="21"/>
       <c r="B365" s="16"/>
       <c r="C365" s="16"/>
       <c r="D365" s="16"/>
@@ -10088,7 +10112,7 @@
       <c r="N365" s="19"/>
     </row>
     <row r="366">
-      <c r="A366" s="20"/>
+      <c r="A366" s="21"/>
       <c r="B366" s="16"/>
       <c r="C366" s="16"/>
       <c r="D366" s="16"/>
@@ -10110,7 +10134,7 @@
       <c r="N366" s="19"/>
     </row>
     <row r="367">
-      <c r="A367" s="20"/>
+      <c r="A367" s="21"/>
       <c r="B367" s="16"/>
       <c r="C367" s="16"/>
       <c r="D367" s="16"/>
@@ -10132,7 +10156,7 @@
       <c r="N367" s="19"/>
     </row>
     <row r="368">
-      <c r="A368" s="20"/>
+      <c r="A368" s="21"/>
       <c r="B368" s="16"/>
       <c r="C368" s="16"/>
       <c r="D368" s="16"/>
@@ -10154,7 +10178,7 @@
       <c r="N368" s="19"/>
     </row>
     <row r="369">
-      <c r="A369" s="20"/>
+      <c r="A369" s="21"/>
       <c r="B369" s="16"/>
       <c r="C369" s="16"/>
       <c r="D369" s="16"/>
@@ -10176,7 +10200,7 @@
       <c r="N369" s="19"/>
     </row>
     <row r="370">
-      <c r="A370" s="20"/>
+      <c r="A370" s="21"/>
       <c r="B370" s="16"/>
       <c r="C370" s="16"/>
       <c r="D370" s="16"/>
@@ -10198,7 +10222,7 @@
       <c r="N370" s="19"/>
     </row>
     <row r="371">
-      <c r="A371" s="20"/>
+      <c r="A371" s="21"/>
       <c r="B371" s="16"/>
       <c r="C371" s="16"/>
       <c r="D371" s="16"/>
@@ -10220,7 +10244,7 @@
       <c r="N371" s="19"/>
     </row>
     <row r="372">
-      <c r="A372" s="20"/>
+      <c r="A372" s="21"/>
       <c r="B372" s="16"/>
       <c r="C372" s="16"/>
       <c r="D372" s="16"/>
@@ -10242,7 +10266,7 @@
       <c r="N372" s="19"/>
     </row>
     <row r="373">
-      <c r="A373" s="20"/>
+      <c r="A373" s="21"/>
       <c r="B373" s="16"/>
       <c r="C373" s="16"/>
       <c r="D373" s="16"/>
@@ -10264,7 +10288,7 @@
       <c r="N373" s="19"/>
     </row>
     <row r="374">
-      <c r="A374" s="20"/>
+      <c r="A374" s="21"/>
       <c r="B374" s="16"/>
       <c r="C374" s="16"/>
       <c r="D374" s="16"/>
@@ -10286,7 +10310,7 @@
       <c r="N374" s="19"/>
     </row>
     <row r="375">
-      <c r="A375" s="20"/>
+      <c r="A375" s="21"/>
       <c r="B375" s="16"/>
       <c r="C375" s="16"/>
       <c r="D375" s="16"/>
@@ -10308,7 +10332,7 @@
       <c r="N375" s="19"/>
     </row>
     <row r="376">
-      <c r="A376" s="20"/>
+      <c r="A376" s="21"/>
       <c r="B376" s="16"/>
       <c r="C376" s="16"/>
       <c r="D376" s="16"/>
@@ -10330,7 +10354,7 @@
       <c r="N376" s="19"/>
     </row>
     <row r="377">
-      <c r="A377" s="20"/>
+      <c r="A377" s="21"/>
       <c r="B377" s="16"/>
       <c r="C377" s="16"/>
       <c r="D377" s="16"/>
@@ -10352,7 +10376,7 @@
       <c r="N377" s="19"/>
     </row>
     <row r="378">
-      <c r="A378" s="20"/>
+      <c r="A378" s="21"/>
       <c r="B378" s="16"/>
       <c r="C378" s="16"/>
       <c r="D378" s="16"/>
@@ -10374,7 +10398,7 @@
       <c r="N378" s="19"/>
     </row>
     <row r="379">
-      <c r="A379" s="20"/>
+      <c r="A379" s="21"/>
       <c r="B379" s="16"/>
       <c r="C379" s="16"/>
       <c r="D379" s="16"/>
@@ -10396,7 +10420,7 @@
       <c r="N379" s="19"/>
     </row>
     <row r="380">
-      <c r="A380" s="20"/>
+      <c r="A380" s="21"/>
       <c r="B380" s="16"/>
       <c r="C380" s="16"/>
       <c r="D380" s="16"/>
@@ -10418,7 +10442,7 @@
       <c r="N380" s="19"/>
     </row>
     <row r="381">
-      <c r="A381" s="20"/>
+      <c r="A381" s="21"/>
       <c r="B381" s="16"/>
       <c r="C381" s="16"/>
       <c r="D381" s="16"/>
@@ -10440,7 +10464,7 @@
       <c r="N381" s="19"/>
     </row>
     <row r="382">
-      <c r="A382" s="20"/>
+      <c r="A382" s="21"/>
       <c r="B382" s="16"/>
       <c r="C382" s="16"/>
       <c r="D382" s="16"/>
@@ -10462,7 +10486,7 @@
       <c r="N382" s="19"/>
     </row>
     <row r="383">
-      <c r="A383" s="20"/>
+      <c r="A383" s="21"/>
       <c r="B383" s="16"/>
       <c r="C383" s="16"/>
       <c r="D383" s="16"/>
@@ -10484,7 +10508,7 @@
       <c r="N383" s="19"/>
     </row>
     <row r="384">
-      <c r="A384" s="20"/>
+      <c r="A384" s="21"/>
       <c r="B384" s="16"/>
       <c r="C384" s="16"/>
       <c r="D384" s="16"/>
@@ -10506,7 +10530,7 @@
       <c r="N384" s="19"/>
     </row>
     <row r="385">
-      <c r="A385" s="20"/>
+      <c r="A385" s="21"/>
       <c r="B385" s="16"/>
       <c r="C385" s="16"/>
       <c r="D385" s="16"/>
@@ -10528,7 +10552,7 @@
       <c r="N385" s="19"/>
     </row>
     <row r="386">
-      <c r="A386" s="20"/>
+      <c r="A386" s="21"/>
       <c r="B386" s="16"/>
       <c r="C386" s="16"/>
       <c r="D386" s="16"/>
@@ -10550,7 +10574,7 @@
       <c r="N386" s="19"/>
     </row>
     <row r="387">
-      <c r="A387" s="20"/>
+      <c r="A387" s="21"/>
       <c r="B387" s="16"/>
       <c r="C387" s="16"/>
       <c r="D387" s="16"/>
@@ -10572,7 +10596,7 @@
       <c r="N387" s="19"/>
     </row>
     <row r="388">
-      <c r="A388" s="20"/>
+      <c r="A388" s="21"/>
       <c r="B388" s="16"/>
       <c r="C388" s="16"/>
       <c r="D388" s="16"/>
@@ -10594,7 +10618,7 @@
       <c r="N388" s="19"/>
     </row>
     <row r="389">
-      <c r="A389" s="20"/>
+      <c r="A389" s="21"/>
       <c r="B389" s="16"/>
       <c r="C389" s="16"/>
       <c r="D389" s="16"/>
@@ -10616,7 +10640,7 @@
       <c r="N389" s="19"/>
     </row>
     <row r="390">
-      <c r="A390" s="20"/>
+      <c r="A390" s="21"/>
       <c r="B390" s="16"/>
       <c r="C390" s="16"/>
       <c r="D390" s="16"/>
@@ -10638,7 +10662,7 @@
       <c r="N390" s="19"/>
     </row>
     <row r="391">
-      <c r="A391" s="20"/>
+      <c r="A391" s="21"/>
       <c r="B391" s="16"/>
       <c r="C391" s="16"/>
       <c r="D391" s="16"/>
@@ -10660,7 +10684,7 @@
       <c r="N391" s="19"/>
     </row>
     <row r="392">
-      <c r="A392" s="20"/>
+      <c r="A392" s="21"/>
       <c r="B392" s="16"/>
       <c r="C392" s="16"/>
       <c r="D392" s="16"/>
@@ -10682,7 +10706,7 @@
       <c r="N392" s="19"/>
     </row>
     <row r="393">
-      <c r="A393" s="20"/>
+      <c r="A393" s="21"/>
       <c r="B393" s="16"/>
       <c r="C393" s="16"/>
       <c r="D393" s="16"/>
@@ -10704,7 +10728,7 @@
       <c r="N393" s="19"/>
     </row>
     <row r="394">
-      <c r="A394" s="20"/>
+      <c r="A394" s="21"/>
       <c r="B394" s="16"/>
       <c r="C394" s="16"/>
       <c r="D394" s="16"/>
@@ -10726,7 +10750,7 @@
       <c r="N394" s="19"/>
     </row>
     <row r="395">
-      <c r="A395" s="20"/>
+      <c r="A395" s="21"/>
       <c r="B395" s="16"/>
       <c r="C395" s="16"/>
       <c r="D395" s="16"/>
@@ -10748,7 +10772,7 @@
       <c r="N395" s="19"/>
     </row>
     <row r="396">
-      <c r="A396" s="20"/>
+      <c r="A396" s="21"/>
       <c r="B396" s="16"/>
       <c r="C396" s="16"/>
       <c r="D396" s="16"/>
@@ -10770,7 +10794,7 @@
       <c r="N396" s="19"/>
     </row>
     <row r="397">
-      <c r="A397" s="20"/>
+      <c r="A397" s="21"/>
       <c r="B397" s="16"/>
       <c r="C397" s="16"/>
       <c r="D397" s="16"/>
@@ -10792,7 +10816,7 @@
       <c r="N397" s="19"/>
     </row>
     <row r="398">
-      <c r="A398" s="20"/>
+      <c r="A398" s="21"/>
       <c r="B398" s="16"/>
       <c r="C398" s="16"/>
       <c r="D398" s="16"/>
@@ -10814,7 +10838,7 @@
       <c r="N398" s="19"/>
     </row>
     <row r="399">
-      <c r="A399" s="20"/>
+      <c r="A399" s="21"/>
       <c r="B399" s="16"/>
       <c r="C399" s="16"/>
       <c r="D399" s="16"/>
@@ -10836,7 +10860,7 @@
       <c r="N399" s="19"/>
     </row>
     <row r="400">
-      <c r="A400" s="20"/>
+      <c r="A400" s="21"/>
       <c r="B400" s="16"/>
       <c r="C400" s="16"/>
       <c r="D400" s="16"/>
@@ -10858,7 +10882,7 @@
       <c r="N400" s="19"/>
     </row>
     <row r="401">
-      <c r="A401" s="20"/>
+      <c r="A401" s="21"/>
       <c r="B401" s="16"/>
       <c r="C401" s="16"/>
       <c r="D401" s="16"/>
@@ -10896,7 +10920,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="lessThan" id="{0A2C7CCA-C66E-4608-BFE4-CA77F28D0127}">
+          <x14:cfRule type="cellIs" priority="2" operator="lessThan" id="{A200C9DA-AB33-4994-8FA4-F7E5FD39AA8D}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -10917,7 +10941,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3" disablePrompts="0">
-        <x14:dataValidation xr:uid="{5104895D-034F-4B7E-9562-CC528460866C}" type="list" allowBlank="1" error="Please choose a value from the dropdown list." errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's overall feeling" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{F702A3BB-8EBB-4F8C-847F-372FE0C054E2}" type="list" allowBlank="1" error="Please choose a value from the dropdown list." errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's overall feeling" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Excellent,Good,Neutral,Low,Stressed"</xm:f>
           </x14:formula1>
@@ -10926,16 +10950,16 @@
           </x14:formula2>
           <xm:sqref>K6:K401</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{16B90CE1-E07F-4A40-B96B-85397697717F}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's satisfaction level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{494EEC5D-975A-4FB4-8C19-ACF6A6076EFB}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's satisfaction level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>L6:L401</xm:sqref>
+          <xm:sqref>L6:L51 L54:L401 L52</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{602249B5-4D63-4F3A-8E9A-C800E794B315}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's energy level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{9A84F9B7-0B98-4554-9FF3-39EA83827984}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's energy level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"High,Medium,Low"</xm:f>
           </x14:formula1>

--- a/12620994.xlsx
+++ b/12620994.xlsx
@@ -3218,77 +3218,144 @@
       <c r="K52" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="L52" s="18" t="s">
+      <c r="L52" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="M52" s="20" t="s">
+      <c r="M52" s="18" t="s">
         <v>53</v>
       </c>
       <c r="N52" s="19"/>
     </row>
     <row r="53">
-      <c r="A53" s="21"/>
-      <c r="B53" s="16"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
-      <c r="H53" s="16"/>
-      <c r="I53" s="17" t="str">
+      <c r="A53" s="11">
+        <v>46292</v>
+      </c>
+      <c r="B53" s="16">
+        <v>480</v>
+      </c>
+      <c r="C53" s="16">
+        <v>0</v>
+      </c>
+      <c r="D53" s="16">
+        <v>60</v>
+      </c>
+      <c r="E53" s="16">
+        <v>35</v>
+      </c>
+      <c r="F53" s="16">
+        <v>0</v>
+      </c>
+      <c r="G53" s="16">
+        <v>0</v>
+      </c>
+      <c r="H53" s="16">
+        <v>120</v>
+      </c>
+      <c r="I53" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="17" t="str">
+        <v>695</v>
+      </c>
+      <c r="J53" s="17">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="18"/>
-      <c r="M53" s="18"/>
+        <v>745</v>
+      </c>
+      <c r="K53" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="L53" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M53" s="18" t="s">
+        <v>53</v>
+      </c>
       <c r="N53" s="19"/>
     </row>
     <row r="54">
-      <c r="A54" s="21"/>
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
-      <c r="H54" s="16"/>
-      <c r="I54" s="17" t="str">
+      <c r="A54" s="11">
+        <v>46293</v>
+      </c>
+      <c r="B54" s="16">
+        <v>400</v>
+      </c>
+      <c r="C54" s="16">
+        <v>0</v>
+      </c>
+      <c r="D54" s="16">
+        <v>50</v>
+      </c>
+      <c r="E54" s="16">
+        <v>40</v>
+      </c>
+      <c r="F54" s="16">
+        <v>0</v>
+      </c>
+      <c r="G54" s="16">
+        <v>0</v>
+      </c>
+      <c r="H54" s="16">
+        <v>200</v>
+      </c>
+      <c r="I54" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="17" t="str">
+        <v>690</v>
+      </c>
+      <c r="J54" s="17">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="18"/>
-      <c r="L54" s="18"/>
-      <c r="M54" s="18"/>
+        <v>750</v>
+      </c>
+      <c r="K54" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="L54" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="M54" s="18" t="s">
+        <v>57</v>
+      </c>
       <c r="N54" s="19"/>
     </row>
     <row r="55">
-      <c r="A55" s="21"/>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="17" t="str">
+      <c r="A55" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B55" s="16">
+        <v>500</v>
+      </c>
+      <c r="C55" s="16">
+        <v>50</v>
+      </c>
+      <c r="D55" s="16">
+        <v>70</v>
+      </c>
+      <c r="E55" s="16">
+        <v>58</v>
+      </c>
+      <c r="F55" s="16">
+        <v>0</v>
+      </c>
+      <c r="G55" s="16">
+        <v>0</v>
+      </c>
+      <c r="H55" s="16">
+        <v>150</v>
+      </c>
+      <c r="I55" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="17" t="str">
+        <v>828</v>
+      </c>
+      <c r="J55" s="17">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="18"/>
-      <c r="L55" s="18"/>
-      <c r="M55" s="18"/>
+        <v>612</v>
+      </c>
+      <c r="K55" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="L55" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="M55" s="18" t="s">
+        <v>53</v>
+      </c>
       <c r="N55" s="19"/>
     </row>
     <row r="56">
@@ -10920,7 +10987,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="lessThan" id="{A200C9DA-AB33-4994-8FA4-F7E5FD39AA8D}">
+          <x14:cfRule type="cellIs" priority="2" operator="lessThan" id="{3CFDA9BF-1AE6-4106-806C-8135A2570AA1}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -10941,7 +11008,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3" disablePrompts="0">
-        <x14:dataValidation xr:uid="{F702A3BB-8EBB-4F8C-847F-372FE0C054E2}" type="list" allowBlank="1" error="Please choose a value from the dropdown list." errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's overall feeling" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{91F4F13C-ECBA-4170-BBDF-A502D754F8D9}" type="list" allowBlank="1" error="Please choose a value from the dropdown list." errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's overall feeling" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Excellent,Good,Neutral,Low,Stressed"</xm:f>
           </x14:formula1>
@@ -10950,16 +11017,16 @@
           </x14:formula2>
           <xm:sqref>K6:K401</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{494EEC5D-975A-4FB4-8C19-ACF6A6076EFB}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's satisfaction level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{EBC7801D-984A-4C9A-A170-5281A59ECDC2}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's satisfaction level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>L6:L51 L54:L401 L52</xm:sqref>
+          <xm:sqref>L6:L51 L56:L401 L52 L53 L54 L55</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{9A84F9B7-0B98-4554-9FF3-39EA83827984}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's energy level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{22C882DC-E02F-49FE-984C-39D607219A87}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's energy level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"High,Medium,Low"</xm:f>
           </x14:formula1>

--- a/12620994.xlsx
+++ b/12620994.xlsx
@@ -324,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
@@ -364,9 +364,6 @@
     </xf>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3218,7 +3215,7 @@
       <c r="K52" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="L52" s="20" t="s">
+      <c r="L52" s="18" t="s">
         <v>52</v>
       </c>
       <c r="M52" s="18" t="s">
@@ -3262,7 +3259,7 @@
       <c r="K53" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="20" t="s">
+      <c r="L53" s="18" t="s">
         <v>58</v>
       </c>
       <c r="M53" s="18" t="s">
@@ -3306,7 +3303,7 @@
       <c r="K54" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="L54" s="20" t="s">
+      <c r="L54" s="18" t="s">
         <v>52</v>
       </c>
       <c r="M54" s="18" t="s">
@@ -3350,7 +3347,7 @@
       <c r="K55" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="L55" s="20" t="s">
+      <c r="L55" s="18" t="s">
         <v>52</v>
       </c>
       <c r="M55" s="18" t="s">
@@ -3359,29 +3356,51 @@
       <c r="N55" s="19"/>
     </row>
     <row r="56">
-      <c r="A56" s="21"/>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-      <c r="H56" s="16"/>
-      <c r="I56" s="17" t="str">
+      <c r="A56" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B56" s="16">
+        <v>500</v>
+      </c>
+      <c r="C56" s="16">
+        <v>30</v>
+      </c>
+      <c r="D56" s="16">
+        <v>60</v>
+      </c>
+      <c r="E56" s="16">
+        <v>60</v>
+      </c>
+      <c r="F56" s="16">
+        <v>0</v>
+      </c>
+      <c r="G56" s="16">
+        <v>0</v>
+      </c>
+      <c r="H56" s="16">
+        <v>200</v>
+      </c>
+      <c r="I56" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="17" t="str">
+        <v>850</v>
+      </c>
+      <c r="J56" s="17">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="18"/>
-      <c r="L56" s="18"/>
-      <c r="M56" s="18"/>
+        <v>590</v>
+      </c>
+      <c r="K56" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="L56" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="M56" s="18" t="s">
+        <v>53</v>
+      </c>
       <c r="N56" s="19"/>
     </row>
     <row r="57">
-      <c r="A57" s="21"/>
+      <c r="A57" s="20"/>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
       <c r="D57" s="16"/>
@@ -3403,7 +3422,7 @@
       <c r="N57" s="19"/>
     </row>
     <row r="58">
-      <c r="A58" s="21"/>
+      <c r="A58" s="20"/>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
       <c r="D58" s="16"/>
@@ -3425,7 +3444,7 @@
       <c r="N58" s="19"/>
     </row>
     <row r="59">
-      <c r="A59" s="21"/>
+      <c r="A59" s="20"/>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
       <c r="D59" s="16"/>
@@ -3447,7 +3466,7 @@
       <c r="N59" s="19"/>
     </row>
     <row r="60">
-      <c r="A60" s="21"/>
+      <c r="A60" s="20"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
       <c r="D60" s="16"/>
@@ -3469,7 +3488,7 @@
       <c r="N60" s="19"/>
     </row>
     <row r="61">
-      <c r="A61" s="21"/>
+      <c r="A61" s="20"/>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
       <c r="D61" s="16"/>
@@ -3491,7 +3510,7 @@
       <c r="N61" s="19"/>
     </row>
     <row r="62">
-      <c r="A62" s="21"/>
+      <c r="A62" s="20"/>
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
       <c r="D62" s="16"/>
@@ -3513,7 +3532,7 @@
       <c r="N62" s="19"/>
     </row>
     <row r="63">
-      <c r="A63" s="21"/>
+      <c r="A63" s="20"/>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
       <c r="D63" s="16"/>
@@ -3535,7 +3554,7 @@
       <c r="N63" s="19"/>
     </row>
     <row r="64">
-      <c r="A64" s="21"/>
+      <c r="A64" s="20"/>
       <c r="B64" s="16"/>
       <c r="C64" s="16"/>
       <c r="D64" s="16"/>
@@ -3557,7 +3576,7 @@
       <c r="N64" s="19"/>
     </row>
     <row r="65">
-      <c r="A65" s="21"/>
+      <c r="A65" s="20"/>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
       <c r="D65" s="16"/>
@@ -3579,7 +3598,7 @@
       <c r="N65" s="19"/>
     </row>
     <row r="66">
-      <c r="A66" s="21"/>
+      <c r="A66" s="20"/>
       <c r="B66" s="16"/>
       <c r="C66" s="16"/>
       <c r="D66" s="16"/>
@@ -3601,7 +3620,7 @@
       <c r="N66" s="19"/>
     </row>
     <row r="67">
-      <c r="A67" s="21"/>
+      <c r="A67" s="20"/>
       <c r="B67" s="16"/>
       <c r="C67" s="16"/>
       <c r="D67" s="16"/>
@@ -3623,7 +3642,7 @@
       <c r="N67" s="19"/>
     </row>
     <row r="68">
-      <c r="A68" s="21"/>
+      <c r="A68" s="20"/>
       <c r="B68" s="16"/>
       <c r="C68" s="16"/>
       <c r="D68" s="16"/>
@@ -3645,7 +3664,7 @@
       <c r="N68" s="19"/>
     </row>
     <row r="69">
-      <c r="A69" s="21"/>
+      <c r="A69" s="20"/>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
       <c r="D69" s="16"/>
@@ -3667,7 +3686,7 @@
       <c r="N69" s="19"/>
     </row>
     <row r="70">
-      <c r="A70" s="21"/>
+      <c r="A70" s="20"/>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
       <c r="D70" s="16"/>
@@ -3689,7 +3708,7 @@
       <c r="N70" s="19"/>
     </row>
     <row r="71">
-      <c r="A71" s="21"/>
+      <c r="A71" s="20"/>
       <c r="B71" s="16"/>
       <c r="C71" s="16"/>
       <c r="D71" s="16"/>
@@ -3711,7 +3730,7 @@
       <c r="N71" s="19"/>
     </row>
     <row r="72">
-      <c r="A72" s="21"/>
+      <c r="A72" s="20"/>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
       <c r="D72" s="16"/>
@@ -3733,7 +3752,7 @@
       <c r="N72" s="19"/>
     </row>
     <row r="73">
-      <c r="A73" s="21"/>
+      <c r="A73" s="20"/>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
       <c r="D73" s="16"/>
@@ -3755,7 +3774,7 @@
       <c r="N73" s="19"/>
     </row>
     <row r="74">
-      <c r="A74" s="21"/>
+      <c r="A74" s="20"/>
       <c r="B74" s="16"/>
       <c r="C74" s="16"/>
       <c r="D74" s="16"/>
@@ -3777,7 +3796,7 @@
       <c r="N74" s="19"/>
     </row>
     <row r="75">
-      <c r="A75" s="21"/>
+      <c r="A75" s="20"/>
       <c r="B75" s="16"/>
       <c r="C75" s="16"/>
       <c r="D75" s="16"/>
@@ -3799,7 +3818,7 @@
       <c r="N75" s="19"/>
     </row>
     <row r="76">
-      <c r="A76" s="21"/>
+      <c r="A76" s="20"/>
       <c r="B76" s="16"/>
       <c r="C76" s="16"/>
       <c r="D76" s="16"/>
@@ -3821,7 +3840,7 @@
       <c r="N76" s="19"/>
     </row>
     <row r="77">
-      <c r="A77" s="21"/>
+      <c r="A77" s="20"/>
       <c r="B77" s="16"/>
       <c r="C77" s="16"/>
       <c r="D77" s="16"/>
@@ -3843,7 +3862,7 @@
       <c r="N77" s="19"/>
     </row>
     <row r="78">
-      <c r="A78" s="21"/>
+      <c r="A78" s="20"/>
       <c r="B78" s="16"/>
       <c r="C78" s="16"/>
       <c r="D78" s="16"/>
@@ -3865,7 +3884,7 @@
       <c r="N78" s="19"/>
     </row>
     <row r="79">
-      <c r="A79" s="21"/>
+      <c r="A79" s="20"/>
       <c r="B79" s="16"/>
       <c r="C79" s="16"/>
       <c r="D79" s="16"/>
@@ -3887,7 +3906,7 @@
       <c r="N79" s="19"/>
     </row>
     <row r="80">
-      <c r="A80" s="21"/>
+      <c r="A80" s="20"/>
       <c r="B80" s="16"/>
       <c r="C80" s="16"/>
       <c r="D80" s="16"/>
@@ -3909,7 +3928,7 @@
       <c r="N80" s="19"/>
     </row>
     <row r="81">
-      <c r="A81" s="21"/>
+      <c r="A81" s="20"/>
       <c r="B81" s="16"/>
       <c r="C81" s="16"/>
       <c r="D81" s="16"/>
@@ -3931,7 +3950,7 @@
       <c r="N81" s="19"/>
     </row>
     <row r="82">
-      <c r="A82" s="21"/>
+      <c r="A82" s="20"/>
       <c r="B82" s="16"/>
       <c r="C82" s="16"/>
       <c r="D82" s="16"/>
@@ -3953,7 +3972,7 @@
       <c r="N82" s="19"/>
     </row>
     <row r="83">
-      <c r="A83" s="21"/>
+      <c r="A83" s="20"/>
       <c r="B83" s="16"/>
       <c r="C83" s="16"/>
       <c r="D83" s="16"/>
@@ -3975,7 +3994,7 @@
       <c r="N83" s="19"/>
     </row>
     <row r="84">
-      <c r="A84" s="21"/>
+      <c r="A84" s="20"/>
       <c r="B84" s="16"/>
       <c r="C84" s="16"/>
       <c r="D84" s="16"/>
@@ -3997,7 +4016,7 @@
       <c r="N84" s="19"/>
     </row>
     <row r="85">
-      <c r="A85" s="21"/>
+      <c r="A85" s="20"/>
       <c r="B85" s="16"/>
       <c r="C85" s="16"/>
       <c r="D85" s="16"/>
@@ -4019,7 +4038,7 @@
       <c r="N85" s="19"/>
     </row>
     <row r="86">
-      <c r="A86" s="21"/>
+      <c r="A86" s="20"/>
       <c r="B86" s="16"/>
       <c r="C86" s="16"/>
       <c r="D86" s="16"/>
@@ -4041,7 +4060,7 @@
       <c r="N86" s="19"/>
     </row>
     <row r="87">
-      <c r="A87" s="21"/>
+      <c r="A87" s="20"/>
       <c r="B87" s="16"/>
       <c r="C87" s="16"/>
       <c r="D87" s="16"/>
@@ -4063,7 +4082,7 @@
       <c r="N87" s="19"/>
     </row>
     <row r="88">
-      <c r="A88" s="21"/>
+      <c r="A88" s="20"/>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
       <c r="D88" s="16"/>
@@ -4085,7 +4104,7 @@
       <c r="N88" s="19"/>
     </row>
     <row r="89">
-      <c r="A89" s="21"/>
+      <c r="A89" s="20"/>
       <c r="B89" s="16"/>
       <c r="C89" s="16"/>
       <c r="D89" s="16"/>
@@ -4107,7 +4126,7 @@
       <c r="N89" s="19"/>
     </row>
     <row r="90">
-      <c r="A90" s="21"/>
+      <c r="A90" s="20"/>
       <c r="B90" s="16"/>
       <c r="C90" s="16"/>
       <c r="D90" s="16"/>
@@ -4129,7 +4148,7 @@
       <c r="N90" s="19"/>
     </row>
     <row r="91">
-      <c r="A91" s="21"/>
+      <c r="A91" s="20"/>
       <c r="B91" s="16"/>
       <c r="C91" s="16"/>
       <c r="D91" s="16"/>
@@ -4151,7 +4170,7 @@
       <c r="N91" s="19"/>
     </row>
     <row r="92">
-      <c r="A92" s="21"/>
+      <c r="A92" s="20"/>
       <c r="B92" s="16"/>
       <c r="C92" s="16"/>
       <c r="D92" s="16"/>
@@ -4173,7 +4192,7 @@
       <c r="N92" s="19"/>
     </row>
     <row r="93">
-      <c r="A93" s="21"/>
+      <c r="A93" s="20"/>
       <c r="B93" s="16"/>
       <c r="C93" s="16"/>
       <c r="D93" s="16"/>
@@ -4195,7 +4214,7 @@
       <c r="N93" s="19"/>
     </row>
     <row r="94">
-      <c r="A94" s="21"/>
+      <c r="A94" s="20"/>
       <c r="B94" s="16"/>
       <c r="C94" s="16"/>
       <c r="D94" s="16"/>
@@ -4217,7 +4236,7 @@
       <c r="N94" s="19"/>
     </row>
     <row r="95">
-      <c r="A95" s="21"/>
+      <c r="A95" s="20"/>
       <c r="B95" s="16"/>
       <c r="C95" s="16"/>
       <c r="D95" s="16"/>
@@ -4239,7 +4258,7 @@
       <c r="N95" s="19"/>
     </row>
     <row r="96">
-      <c r="A96" s="21"/>
+      <c r="A96" s="20"/>
       <c r="B96" s="16"/>
       <c r="C96" s="16"/>
       <c r="D96" s="16"/>
@@ -4261,7 +4280,7 @@
       <c r="N96" s="19"/>
     </row>
     <row r="97">
-      <c r="A97" s="21"/>
+      <c r="A97" s="20"/>
       <c r="B97" s="16"/>
       <c r="C97" s="16"/>
       <c r="D97" s="16"/>
@@ -4283,7 +4302,7 @@
       <c r="N97" s="19"/>
     </row>
     <row r="98">
-      <c r="A98" s="21"/>
+      <c r="A98" s="20"/>
       <c r="B98" s="16"/>
       <c r="C98" s="16"/>
       <c r="D98" s="16"/>
@@ -4305,7 +4324,7 @@
       <c r="N98" s="19"/>
     </row>
     <row r="99">
-      <c r="A99" s="21"/>
+      <c r="A99" s="20"/>
       <c r="B99" s="16"/>
       <c r="C99" s="16"/>
       <c r="D99" s="16"/>
@@ -4327,7 +4346,7 @@
       <c r="N99" s="19"/>
     </row>
     <row r="100">
-      <c r="A100" s="21"/>
+      <c r="A100" s="20"/>
       <c r="B100" s="16"/>
       <c r="C100" s="16"/>
       <c r="D100" s="16"/>
@@ -4349,7 +4368,7 @@
       <c r="N100" s="19"/>
     </row>
     <row r="101">
-      <c r="A101" s="21"/>
+      <c r="A101" s="20"/>
       <c r="B101" s="16"/>
       <c r="C101" s="16"/>
       <c r="D101" s="16"/>
@@ -4371,7 +4390,7 @@
       <c r="N101" s="19"/>
     </row>
     <row r="102">
-      <c r="A102" s="21"/>
+      <c r="A102" s="20"/>
       <c r="B102" s="16"/>
       <c r="C102" s="16"/>
       <c r="D102" s="16"/>
@@ -4393,7 +4412,7 @@
       <c r="N102" s="19"/>
     </row>
     <row r="103">
-      <c r="A103" s="21"/>
+      <c r="A103" s="20"/>
       <c r="B103" s="16"/>
       <c r="C103" s="16"/>
       <c r="D103" s="16"/>
@@ -4415,7 +4434,7 @@
       <c r="N103" s="19"/>
     </row>
     <row r="104">
-      <c r="A104" s="21"/>
+      <c r="A104" s="20"/>
       <c r="B104" s="16"/>
       <c r="C104" s="16"/>
       <c r="D104" s="16"/>
@@ -4437,7 +4456,7 @@
       <c r="N104" s="19"/>
     </row>
     <row r="105">
-      <c r="A105" s="21"/>
+      <c r="A105" s="20"/>
       <c r="B105" s="16"/>
       <c r="C105" s="16"/>
       <c r="D105" s="16"/>
@@ -4459,7 +4478,7 @@
       <c r="N105" s="19"/>
     </row>
     <row r="106">
-      <c r="A106" s="21"/>
+      <c r="A106" s="20"/>
       <c r="B106" s="16"/>
       <c r="C106" s="16"/>
       <c r="D106" s="16"/>
@@ -4481,7 +4500,7 @@
       <c r="N106" s="19"/>
     </row>
     <row r="107">
-      <c r="A107" s="21"/>
+      <c r="A107" s="20"/>
       <c r="B107" s="16"/>
       <c r="C107" s="16"/>
       <c r="D107" s="16"/>
@@ -4503,7 +4522,7 @@
       <c r="N107" s="19"/>
     </row>
     <row r="108">
-      <c r="A108" s="21"/>
+      <c r="A108" s="20"/>
       <c r="B108" s="16"/>
       <c r="C108" s="16"/>
       <c r="D108" s="16"/>
@@ -4525,7 +4544,7 @@
       <c r="N108" s="19"/>
     </row>
     <row r="109">
-      <c r="A109" s="21"/>
+      <c r="A109" s="20"/>
       <c r="B109" s="16"/>
       <c r="C109" s="16"/>
       <c r="D109" s="16"/>
@@ -4547,7 +4566,7 @@
       <c r="N109" s="19"/>
     </row>
     <row r="110">
-      <c r="A110" s="21"/>
+      <c r="A110" s="20"/>
       <c r="B110" s="16"/>
       <c r="C110" s="16"/>
       <c r="D110" s="16"/>
@@ -4569,7 +4588,7 @@
       <c r="N110" s="19"/>
     </row>
     <row r="111">
-      <c r="A111" s="21"/>
+      <c r="A111" s="20"/>
       <c r="B111" s="16"/>
       <c r="C111" s="16"/>
       <c r="D111" s="16"/>
@@ -4591,7 +4610,7 @@
       <c r="N111" s="19"/>
     </row>
     <row r="112">
-      <c r="A112" s="21"/>
+      <c r="A112" s="20"/>
       <c r="B112" s="16"/>
       <c r="C112" s="16"/>
       <c r="D112" s="16"/>
@@ -4613,7 +4632,7 @@
       <c r="N112" s="19"/>
     </row>
     <row r="113">
-      <c r="A113" s="21"/>
+      <c r="A113" s="20"/>
       <c r="B113" s="16"/>
       <c r="C113" s="16"/>
       <c r="D113" s="16"/>
@@ -4635,7 +4654,7 @@
       <c r="N113" s="19"/>
     </row>
     <row r="114">
-      <c r="A114" s="21"/>
+      <c r="A114" s="20"/>
       <c r="B114" s="16"/>
       <c r="C114" s="16"/>
       <c r="D114" s="16"/>
@@ -4657,7 +4676,7 @@
       <c r="N114" s="19"/>
     </row>
     <row r="115">
-      <c r="A115" s="21"/>
+      <c r="A115" s="20"/>
       <c r="B115" s="16"/>
       <c r="C115" s="16"/>
       <c r="D115" s="16"/>
@@ -4679,7 +4698,7 @@
       <c r="N115" s="19"/>
     </row>
     <row r="116">
-      <c r="A116" s="21"/>
+      <c r="A116" s="20"/>
       <c r="B116" s="16"/>
       <c r="C116" s="16"/>
       <c r="D116" s="16"/>
@@ -4701,7 +4720,7 @@
       <c r="N116" s="19"/>
     </row>
     <row r="117">
-      <c r="A117" s="21"/>
+      <c r="A117" s="20"/>
       <c r="B117" s="16"/>
       <c r="C117" s="16"/>
       <c r="D117" s="16"/>
@@ -4723,7 +4742,7 @@
       <c r="N117" s="19"/>
     </row>
     <row r="118">
-      <c r="A118" s="21"/>
+      <c r="A118" s="20"/>
       <c r="B118" s="16"/>
       <c r="C118" s="16"/>
       <c r="D118" s="16"/>
@@ -4745,7 +4764,7 @@
       <c r="N118" s="19"/>
     </row>
     <row r="119">
-      <c r="A119" s="21"/>
+      <c r="A119" s="20"/>
       <c r="B119" s="16"/>
       <c r="C119" s="16"/>
       <c r="D119" s="16"/>
@@ -4767,7 +4786,7 @@
       <c r="N119" s="19"/>
     </row>
     <row r="120">
-      <c r="A120" s="21"/>
+      <c r="A120" s="20"/>
       <c r="B120" s="16"/>
       <c r="C120" s="16"/>
       <c r="D120" s="16"/>
@@ -4789,7 +4808,7 @@
       <c r="N120" s="19"/>
     </row>
     <row r="121">
-      <c r="A121" s="21"/>
+      <c r="A121" s="20"/>
       <c r="B121" s="16"/>
       <c r="C121" s="16"/>
       <c r="D121" s="16"/>
@@ -4811,7 +4830,7 @@
       <c r="N121" s="19"/>
     </row>
     <row r="122">
-      <c r="A122" s="21"/>
+      <c r="A122" s="20"/>
       <c r="B122" s="16"/>
       <c r="C122" s="16"/>
       <c r="D122" s="16"/>
@@ -4833,7 +4852,7 @@
       <c r="N122" s="19"/>
     </row>
     <row r="123">
-      <c r="A123" s="21"/>
+      <c r="A123" s="20"/>
       <c r="B123" s="16"/>
       <c r="C123" s="16"/>
       <c r="D123" s="16"/>
@@ -4855,7 +4874,7 @@
       <c r="N123" s="19"/>
     </row>
     <row r="124">
-      <c r="A124" s="21"/>
+      <c r="A124" s="20"/>
       <c r="B124" s="16"/>
       <c r="C124" s="16"/>
       <c r="D124" s="16"/>
@@ -4877,7 +4896,7 @@
       <c r="N124" s="19"/>
     </row>
     <row r="125">
-      <c r="A125" s="21"/>
+      <c r="A125" s="20"/>
       <c r="B125" s="16"/>
       <c r="C125" s="16"/>
       <c r="D125" s="16"/>
@@ -4899,7 +4918,7 @@
       <c r="N125" s="19"/>
     </row>
     <row r="126">
-      <c r="A126" s="21"/>
+      <c r="A126" s="20"/>
       <c r="B126" s="16"/>
       <c r="C126" s="16"/>
       <c r="D126" s="16"/>
@@ -4921,7 +4940,7 @@
       <c r="N126" s="19"/>
     </row>
     <row r="127">
-      <c r="A127" s="21"/>
+      <c r="A127" s="20"/>
       <c r="B127" s="16"/>
       <c r="C127" s="16"/>
       <c r="D127" s="16"/>
@@ -4943,7 +4962,7 @@
       <c r="N127" s="19"/>
     </row>
     <row r="128">
-      <c r="A128" s="21"/>
+      <c r="A128" s="20"/>
       <c r="B128" s="16"/>
       <c r="C128" s="16"/>
       <c r="D128" s="16"/>
@@ -4965,7 +4984,7 @@
       <c r="N128" s="19"/>
     </row>
     <row r="129">
-      <c r="A129" s="21"/>
+      <c r="A129" s="20"/>
       <c r="B129" s="16"/>
       <c r="C129" s="16"/>
       <c r="D129" s="16"/>
@@ -4987,7 +5006,7 @@
       <c r="N129" s="19"/>
     </row>
     <row r="130">
-      <c r="A130" s="21"/>
+      <c r="A130" s="20"/>
       <c r="B130" s="16"/>
       <c r="C130" s="16"/>
       <c r="D130" s="16"/>
@@ -5009,7 +5028,7 @@
       <c r="N130" s="19"/>
     </row>
     <row r="131">
-      <c r="A131" s="21"/>
+      <c r="A131" s="20"/>
       <c r="B131" s="16"/>
       <c r="C131" s="16"/>
       <c r="D131" s="16"/>
@@ -5031,7 +5050,7 @@
       <c r="N131" s="19"/>
     </row>
     <row r="132">
-      <c r="A132" s="21"/>
+      <c r="A132" s="20"/>
       <c r="B132" s="16"/>
       <c r="C132" s="16"/>
       <c r="D132" s="16"/>
@@ -5053,7 +5072,7 @@
       <c r="N132" s="19"/>
     </row>
     <row r="133">
-      <c r="A133" s="21"/>
+      <c r="A133" s="20"/>
       <c r="B133" s="16"/>
       <c r="C133" s="16"/>
       <c r="D133" s="16"/>
@@ -5075,7 +5094,7 @@
       <c r="N133" s="19"/>
     </row>
     <row r="134">
-      <c r="A134" s="21"/>
+      <c r="A134" s="20"/>
       <c r="B134" s="16"/>
       <c r="C134" s="16"/>
       <c r="D134" s="16"/>
@@ -5097,7 +5116,7 @@
       <c r="N134" s="19"/>
     </row>
     <row r="135">
-      <c r="A135" s="21"/>
+      <c r="A135" s="20"/>
       <c r="B135" s="16"/>
       <c r="C135" s="16"/>
       <c r="D135" s="16"/>
@@ -5119,7 +5138,7 @@
       <c r="N135" s="19"/>
     </row>
     <row r="136">
-      <c r="A136" s="21"/>
+      <c r="A136" s="20"/>
       <c r="B136" s="16"/>
       <c r="C136" s="16"/>
       <c r="D136" s="16"/>
@@ -5141,7 +5160,7 @@
       <c r="N136" s="19"/>
     </row>
     <row r="137">
-      <c r="A137" s="21"/>
+      <c r="A137" s="20"/>
       <c r="B137" s="16"/>
       <c r="C137" s="16"/>
       <c r="D137" s="16"/>
@@ -5163,7 +5182,7 @@
       <c r="N137" s="19"/>
     </row>
     <row r="138">
-      <c r="A138" s="21"/>
+      <c r="A138" s="20"/>
       <c r="B138" s="16"/>
       <c r="C138" s="16"/>
       <c r="D138" s="16"/>
@@ -5185,7 +5204,7 @@
       <c r="N138" s="19"/>
     </row>
     <row r="139">
-      <c r="A139" s="21"/>
+      <c r="A139" s="20"/>
       <c r="B139" s="16"/>
       <c r="C139" s="16"/>
       <c r="D139" s="16"/>
@@ -5207,7 +5226,7 @@
       <c r="N139" s="19"/>
     </row>
     <row r="140">
-      <c r="A140" s="21"/>
+      <c r="A140" s="20"/>
       <c r="B140" s="16"/>
       <c r="C140" s="16"/>
       <c r="D140" s="16"/>
@@ -5229,7 +5248,7 @@
       <c r="N140" s="19"/>
     </row>
     <row r="141">
-      <c r="A141" s="21"/>
+      <c r="A141" s="20"/>
       <c r="B141" s="16"/>
       <c r="C141" s="16"/>
       <c r="D141" s="16"/>
@@ -5251,7 +5270,7 @@
       <c r="N141" s="19"/>
     </row>
     <row r="142">
-      <c r="A142" s="21"/>
+      <c r="A142" s="20"/>
       <c r="B142" s="16"/>
       <c r="C142" s="16"/>
       <c r="D142" s="16"/>
@@ -5273,7 +5292,7 @@
       <c r="N142" s="19"/>
     </row>
     <row r="143">
-      <c r="A143" s="21"/>
+      <c r="A143" s="20"/>
       <c r="B143" s="16"/>
       <c r="C143" s="16"/>
       <c r="D143" s="16"/>
@@ -5295,7 +5314,7 @@
       <c r="N143" s="19"/>
     </row>
     <row r="144">
-      <c r="A144" s="21"/>
+      <c r="A144" s="20"/>
       <c r="B144" s="16"/>
       <c r="C144" s="16"/>
       <c r="D144" s="16"/>
@@ -5317,7 +5336,7 @@
       <c r="N144" s="19"/>
     </row>
     <row r="145">
-      <c r="A145" s="21"/>
+      <c r="A145" s="20"/>
       <c r="B145" s="16"/>
       <c r="C145" s="16"/>
       <c r="D145" s="16"/>
@@ -5339,7 +5358,7 @@
       <c r="N145" s="19"/>
     </row>
     <row r="146">
-      <c r="A146" s="21"/>
+      <c r="A146" s="20"/>
       <c r="B146" s="16"/>
       <c r="C146" s="16"/>
       <c r="D146" s="16"/>
@@ -5361,7 +5380,7 @@
       <c r="N146" s="19"/>
     </row>
     <row r="147">
-      <c r="A147" s="21"/>
+      <c r="A147" s="20"/>
       <c r="B147" s="16"/>
       <c r="C147" s="16"/>
       <c r="D147" s="16"/>
@@ -5383,7 +5402,7 @@
       <c r="N147" s="19"/>
     </row>
     <row r="148">
-      <c r="A148" s="21"/>
+      <c r="A148" s="20"/>
       <c r="B148" s="16"/>
       <c r="C148" s="16"/>
       <c r="D148" s="16"/>
@@ -5405,7 +5424,7 @@
       <c r="N148" s="19"/>
     </row>
     <row r="149">
-      <c r="A149" s="21"/>
+      <c r="A149" s="20"/>
       <c r="B149" s="16"/>
       <c r="C149" s="16"/>
       <c r="D149" s="16"/>
@@ -5427,7 +5446,7 @@
       <c r="N149" s="19"/>
     </row>
     <row r="150">
-      <c r="A150" s="21"/>
+      <c r="A150" s="20"/>
       <c r="B150" s="16"/>
       <c r="C150" s="16"/>
       <c r="D150" s="16"/>
@@ -5449,7 +5468,7 @@
       <c r="N150" s="19"/>
     </row>
     <row r="151">
-      <c r="A151" s="21"/>
+      <c r="A151" s="20"/>
       <c r="B151" s="16"/>
       <c r="C151" s="16"/>
       <c r="D151" s="16"/>
@@ -5471,7 +5490,7 @@
       <c r="N151" s="19"/>
     </row>
     <row r="152">
-      <c r="A152" s="21"/>
+      <c r="A152" s="20"/>
       <c r="B152" s="16"/>
       <c r="C152" s="16"/>
       <c r="D152" s="16"/>
@@ -5493,7 +5512,7 @@
       <c r="N152" s="19"/>
     </row>
     <row r="153">
-      <c r="A153" s="21"/>
+      <c r="A153" s="20"/>
       <c r="B153" s="16"/>
       <c r="C153" s="16"/>
       <c r="D153" s="16"/>
@@ -5515,7 +5534,7 @@
       <c r="N153" s="19"/>
     </row>
     <row r="154">
-      <c r="A154" s="21"/>
+      <c r="A154" s="20"/>
       <c r="B154" s="16"/>
       <c r="C154" s="16"/>
       <c r="D154" s="16"/>
@@ -5537,7 +5556,7 @@
       <c r="N154" s="19"/>
     </row>
     <row r="155">
-      <c r="A155" s="21"/>
+      <c r="A155" s="20"/>
       <c r="B155" s="16"/>
       <c r="C155" s="16"/>
       <c r="D155" s="16"/>
@@ -5559,7 +5578,7 @@
       <c r="N155" s="19"/>
     </row>
     <row r="156">
-      <c r="A156" s="21"/>
+      <c r="A156" s="20"/>
       <c r="B156" s="16"/>
       <c r="C156" s="16"/>
       <c r="D156" s="16"/>
@@ -5581,7 +5600,7 @@
       <c r="N156" s="19"/>
     </row>
     <row r="157">
-      <c r="A157" s="21"/>
+      <c r="A157" s="20"/>
       <c r="B157" s="16"/>
       <c r="C157" s="16"/>
       <c r="D157" s="16"/>
@@ -5603,7 +5622,7 @@
       <c r="N157" s="19"/>
     </row>
     <row r="158">
-      <c r="A158" s="21"/>
+      <c r="A158" s="20"/>
       <c r="B158" s="16"/>
       <c r="C158" s="16"/>
       <c r="D158" s="16"/>
@@ -5625,7 +5644,7 @@
       <c r="N158" s="19"/>
     </row>
     <row r="159">
-      <c r="A159" s="21"/>
+      <c r="A159" s="20"/>
       <c r="B159" s="16"/>
       <c r="C159" s="16"/>
       <c r="D159" s="16"/>
@@ -5647,7 +5666,7 @@
       <c r="N159" s="19"/>
     </row>
     <row r="160">
-      <c r="A160" s="21"/>
+      <c r="A160" s="20"/>
       <c r="B160" s="16"/>
       <c r="C160" s="16"/>
       <c r="D160" s="16"/>
@@ -5669,7 +5688,7 @@
       <c r="N160" s="19"/>
     </row>
     <row r="161">
-      <c r="A161" s="21"/>
+      <c r="A161" s="20"/>
       <c r="B161" s="16"/>
       <c r="C161" s="16"/>
       <c r="D161" s="16"/>
@@ -5691,7 +5710,7 @@
       <c r="N161" s="19"/>
     </row>
     <row r="162">
-      <c r="A162" s="21"/>
+      <c r="A162" s="20"/>
       <c r="B162" s="16"/>
       <c r="C162" s="16"/>
       <c r="D162" s="16"/>
@@ -5713,7 +5732,7 @@
       <c r="N162" s="19"/>
     </row>
     <row r="163">
-      <c r="A163" s="21"/>
+      <c r="A163" s="20"/>
       <c r="B163" s="16"/>
       <c r="C163" s="16"/>
       <c r="D163" s="16"/>
@@ -5735,7 +5754,7 @@
       <c r="N163" s="19"/>
     </row>
     <row r="164">
-      <c r="A164" s="21"/>
+      <c r="A164" s="20"/>
       <c r="B164" s="16"/>
       <c r="C164" s="16"/>
       <c r="D164" s="16"/>
@@ -5757,7 +5776,7 @@
       <c r="N164" s="19"/>
     </row>
     <row r="165">
-      <c r="A165" s="21"/>
+      <c r="A165" s="20"/>
       <c r="B165" s="16"/>
       <c r="C165" s="16"/>
       <c r="D165" s="16"/>
@@ -5779,7 +5798,7 @@
       <c r="N165" s="19"/>
     </row>
     <row r="166">
-      <c r="A166" s="21"/>
+      <c r="A166" s="20"/>
       <c r="B166" s="16"/>
       <c r="C166" s="16"/>
       <c r="D166" s="16"/>
@@ -5801,7 +5820,7 @@
       <c r="N166" s="19"/>
     </row>
     <row r="167">
-      <c r="A167" s="21"/>
+      <c r="A167" s="20"/>
       <c r="B167" s="16"/>
       <c r="C167" s="16"/>
       <c r="D167" s="16"/>
@@ -5823,7 +5842,7 @@
       <c r="N167" s="19"/>
     </row>
     <row r="168">
-      <c r="A168" s="21"/>
+      <c r="A168" s="20"/>
       <c r="B168" s="16"/>
       <c r="C168" s="16"/>
       <c r="D168" s="16"/>
@@ -5845,7 +5864,7 @@
       <c r="N168" s="19"/>
     </row>
     <row r="169">
-      <c r="A169" s="21"/>
+      <c r="A169" s="20"/>
       <c r="B169" s="16"/>
       <c r="C169" s="16"/>
       <c r="D169" s="16"/>
@@ -5867,7 +5886,7 @@
       <c r="N169" s="19"/>
     </row>
     <row r="170">
-      <c r="A170" s="21"/>
+      <c r="A170" s="20"/>
       <c r="B170" s="16"/>
       <c r="C170" s="16"/>
       <c r="D170" s="16"/>
@@ -5889,7 +5908,7 @@
       <c r="N170" s="19"/>
     </row>
     <row r="171">
-      <c r="A171" s="21"/>
+      <c r="A171" s="20"/>
       <c r="B171" s="16"/>
       <c r="C171" s="16"/>
       <c r="D171" s="16"/>
@@ -5911,7 +5930,7 @@
       <c r="N171" s="19"/>
     </row>
     <row r="172">
-      <c r="A172" s="21"/>
+      <c r="A172" s="20"/>
       <c r="B172" s="16"/>
       <c r="C172" s="16"/>
       <c r="D172" s="16"/>
@@ -5933,7 +5952,7 @@
       <c r="N172" s="19"/>
     </row>
     <row r="173">
-      <c r="A173" s="21"/>
+      <c r="A173" s="20"/>
       <c r="B173" s="16"/>
       <c r="C173" s="16"/>
       <c r="D173" s="16"/>
@@ -5955,7 +5974,7 @@
       <c r="N173" s="19"/>
     </row>
     <row r="174">
-      <c r="A174" s="21"/>
+      <c r="A174" s="20"/>
       <c r="B174" s="16"/>
       <c r="C174" s="16"/>
       <c r="D174" s="16"/>
@@ -5977,7 +5996,7 @@
       <c r="N174" s="19"/>
     </row>
     <row r="175">
-      <c r="A175" s="21"/>
+      <c r="A175" s="20"/>
       <c r="B175" s="16"/>
       <c r="C175" s="16"/>
       <c r="D175" s="16"/>
@@ -5999,7 +6018,7 @@
       <c r="N175" s="19"/>
     </row>
     <row r="176">
-      <c r="A176" s="21"/>
+      <c r="A176" s="20"/>
       <c r="B176" s="16"/>
       <c r="C176" s="16"/>
       <c r="D176" s="16"/>
@@ -6021,7 +6040,7 @@
       <c r="N176" s="19"/>
     </row>
     <row r="177">
-      <c r="A177" s="21"/>
+      <c r="A177" s="20"/>
       <c r="B177" s="16"/>
       <c r="C177" s="16"/>
       <c r="D177" s="16"/>
@@ -6043,7 +6062,7 @@
       <c r="N177" s="19"/>
     </row>
     <row r="178">
-      <c r="A178" s="21"/>
+      <c r="A178" s="20"/>
       <c r="B178" s="16"/>
       <c r="C178" s="16"/>
       <c r="D178" s="16"/>
@@ -6065,7 +6084,7 @@
       <c r="N178" s="19"/>
     </row>
     <row r="179">
-      <c r="A179" s="21"/>
+      <c r="A179" s="20"/>
       <c r="B179" s="16"/>
       <c r="C179" s="16"/>
       <c r="D179" s="16"/>
@@ -6087,7 +6106,7 @@
       <c r="N179" s="19"/>
     </row>
     <row r="180">
-      <c r="A180" s="21"/>
+      <c r="A180" s="20"/>
       <c r="B180" s="16"/>
       <c r="C180" s="16"/>
       <c r="D180" s="16"/>
@@ -6109,7 +6128,7 @@
       <c r="N180" s="19"/>
     </row>
     <row r="181">
-      <c r="A181" s="21"/>
+      <c r="A181" s="20"/>
       <c r="B181" s="16"/>
       <c r="C181" s="16"/>
       <c r="D181" s="16"/>
@@ -6131,7 +6150,7 @@
       <c r="N181" s="19"/>
     </row>
     <row r="182">
-      <c r="A182" s="21"/>
+      <c r="A182" s="20"/>
       <c r="B182" s="16"/>
       <c r="C182" s="16"/>
       <c r="D182" s="16"/>
@@ -6153,7 +6172,7 @@
       <c r="N182" s="19"/>
     </row>
     <row r="183">
-      <c r="A183" s="21"/>
+      <c r="A183" s="20"/>
       <c r="B183" s="16"/>
       <c r="C183" s="16"/>
       <c r="D183" s="16"/>
@@ -6175,7 +6194,7 @@
       <c r="N183" s="19"/>
     </row>
     <row r="184">
-      <c r="A184" s="21"/>
+      <c r="A184" s="20"/>
       <c r="B184" s="16"/>
       <c r="C184" s="16"/>
       <c r="D184" s="16"/>
@@ -6197,7 +6216,7 @@
       <c r="N184" s="19"/>
     </row>
     <row r="185">
-      <c r="A185" s="21"/>
+      <c r="A185" s="20"/>
       <c r="B185" s="16"/>
       <c r="C185" s="16"/>
       <c r="D185" s="16"/>
@@ -6219,7 +6238,7 @@
       <c r="N185" s="19"/>
     </row>
     <row r="186">
-      <c r="A186" s="21"/>
+      <c r="A186" s="20"/>
       <c r="B186" s="16"/>
       <c r="C186" s="16"/>
       <c r="D186" s="16"/>
@@ -6241,7 +6260,7 @@
       <c r="N186" s="19"/>
     </row>
     <row r="187">
-      <c r="A187" s="21"/>
+      <c r="A187" s="20"/>
       <c r="B187" s="16"/>
       <c r="C187" s="16"/>
       <c r="D187" s="16"/>
@@ -6263,7 +6282,7 @@
       <c r="N187" s="19"/>
     </row>
     <row r="188">
-      <c r="A188" s="21"/>
+      <c r="A188" s="20"/>
       <c r="B188" s="16"/>
       <c r="C188" s="16"/>
       <c r="D188" s="16"/>
@@ -6285,7 +6304,7 @@
       <c r="N188" s="19"/>
     </row>
     <row r="189">
-      <c r="A189" s="21"/>
+      <c r="A189" s="20"/>
       <c r="B189" s="16"/>
       <c r="C189" s="16"/>
       <c r="D189" s="16"/>
@@ -6307,7 +6326,7 @@
       <c r="N189" s="19"/>
     </row>
     <row r="190">
-      <c r="A190" s="21"/>
+      <c r="A190" s="20"/>
       <c r="B190" s="16"/>
       <c r="C190" s="16"/>
       <c r="D190" s="16"/>
@@ -6329,7 +6348,7 @@
       <c r="N190" s="19"/>
     </row>
     <row r="191">
-      <c r="A191" s="21"/>
+      <c r="A191" s="20"/>
       <c r="B191" s="16"/>
       <c r="C191" s="16"/>
       <c r="D191" s="16"/>
@@ -6351,7 +6370,7 @@
       <c r="N191" s="19"/>
     </row>
     <row r="192">
-      <c r="A192" s="21"/>
+      <c r="A192" s="20"/>
       <c r="B192" s="16"/>
       <c r="C192" s="16"/>
       <c r="D192" s="16"/>
@@ -6373,7 +6392,7 @@
       <c r="N192" s="19"/>
     </row>
     <row r="193">
-      <c r="A193" s="21"/>
+      <c r="A193" s="20"/>
       <c r="B193" s="16"/>
       <c r="C193" s="16"/>
       <c r="D193" s="16"/>
@@ -6395,7 +6414,7 @@
       <c r="N193" s="19"/>
     </row>
     <row r="194">
-      <c r="A194" s="21"/>
+      <c r="A194" s="20"/>
       <c r="B194" s="16"/>
       <c r="C194" s="16"/>
       <c r="D194" s="16"/>
@@ -6417,7 +6436,7 @@
       <c r="N194" s="19"/>
     </row>
     <row r="195">
-      <c r="A195" s="21"/>
+      <c r="A195" s="20"/>
       <c r="B195" s="16"/>
       <c r="C195" s="16"/>
       <c r="D195" s="16"/>
@@ -6439,7 +6458,7 @@
       <c r="N195" s="19"/>
     </row>
     <row r="196">
-      <c r="A196" s="21"/>
+      <c r="A196" s="20"/>
       <c r="B196" s="16"/>
       <c r="C196" s="16"/>
       <c r="D196" s="16"/>
@@ -6461,7 +6480,7 @@
       <c r="N196" s="19"/>
     </row>
     <row r="197">
-      <c r="A197" s="21"/>
+      <c r="A197" s="20"/>
       <c r="B197" s="16"/>
       <c r="C197" s="16"/>
       <c r="D197" s="16"/>
@@ -6483,7 +6502,7 @@
       <c r="N197" s="19"/>
     </row>
     <row r="198">
-      <c r="A198" s="21"/>
+      <c r="A198" s="20"/>
       <c r="B198" s="16"/>
       <c r="C198" s="16"/>
       <c r="D198" s="16"/>
@@ -6505,7 +6524,7 @@
       <c r="N198" s="19"/>
     </row>
     <row r="199">
-      <c r="A199" s="21"/>
+      <c r="A199" s="20"/>
       <c r="B199" s="16"/>
       <c r="C199" s="16"/>
       <c r="D199" s="16"/>
@@ -6527,7 +6546,7 @@
       <c r="N199" s="19"/>
     </row>
     <row r="200">
-      <c r="A200" s="21"/>
+      <c r="A200" s="20"/>
       <c r="B200" s="16"/>
       <c r="C200" s="16"/>
       <c r="D200" s="16"/>
@@ -6549,7 +6568,7 @@
       <c r="N200" s="19"/>
     </row>
     <row r="201">
-      <c r="A201" s="21"/>
+      <c r="A201" s="20"/>
       <c r="B201" s="16"/>
       <c r="C201" s="16"/>
       <c r="D201" s="16"/>
@@ -6571,7 +6590,7 @@
       <c r="N201" s="19"/>
     </row>
     <row r="202">
-      <c r="A202" s="21"/>
+      <c r="A202" s="20"/>
       <c r="B202" s="16"/>
       <c r="C202" s="16"/>
       <c r="D202" s="16"/>
@@ -6593,7 +6612,7 @@
       <c r="N202" s="19"/>
     </row>
     <row r="203">
-      <c r="A203" s="21"/>
+      <c r="A203" s="20"/>
       <c r="B203" s="16"/>
       <c r="C203" s="16"/>
       <c r="D203" s="16"/>
@@ -6615,7 +6634,7 @@
       <c r="N203" s="19"/>
     </row>
     <row r="204">
-      <c r="A204" s="21"/>
+      <c r="A204" s="20"/>
       <c r="B204" s="16"/>
       <c r="C204" s="16"/>
       <c r="D204" s="16"/>
@@ -6637,7 +6656,7 @@
       <c r="N204" s="19"/>
     </row>
     <row r="205">
-      <c r="A205" s="21"/>
+      <c r="A205" s="20"/>
       <c r="B205" s="16"/>
       <c r="C205" s="16"/>
       <c r="D205" s="16"/>
@@ -6659,7 +6678,7 @@
       <c r="N205" s="19"/>
     </row>
     <row r="206">
-      <c r="A206" s="21"/>
+      <c r="A206" s="20"/>
       <c r="B206" s="16"/>
       <c r="C206" s="16"/>
       <c r="D206" s="16"/>
@@ -6681,7 +6700,7 @@
       <c r="N206" s="19"/>
     </row>
     <row r="207">
-      <c r="A207" s="21"/>
+      <c r="A207" s="20"/>
       <c r="B207" s="16"/>
       <c r="C207" s="16"/>
       <c r="D207" s="16"/>
@@ -6703,7 +6722,7 @@
       <c r="N207" s="19"/>
     </row>
     <row r="208">
-      <c r="A208" s="21"/>
+      <c r="A208" s="20"/>
       <c r="B208" s="16"/>
       <c r="C208" s="16"/>
       <c r="D208" s="16"/>
@@ -6725,7 +6744,7 @@
       <c r="N208" s="19"/>
     </row>
     <row r="209">
-      <c r="A209" s="21"/>
+      <c r="A209" s="20"/>
       <c r="B209" s="16"/>
       <c r="C209" s="16"/>
       <c r="D209" s="16"/>
@@ -6747,7 +6766,7 @@
       <c r="N209" s="19"/>
     </row>
     <row r="210">
-      <c r="A210" s="21"/>
+      <c r="A210" s="20"/>
       <c r="B210" s="16"/>
       <c r="C210" s="16"/>
       <c r="D210" s="16"/>
@@ -6769,7 +6788,7 @@
       <c r="N210" s="19"/>
     </row>
     <row r="211">
-      <c r="A211" s="21"/>
+      <c r="A211" s="20"/>
       <c r="B211" s="16"/>
       <c r="C211" s="16"/>
       <c r="D211" s="16"/>
@@ -6791,7 +6810,7 @@
       <c r="N211" s="19"/>
     </row>
     <row r="212">
-      <c r="A212" s="21"/>
+      <c r="A212" s="20"/>
       <c r="B212" s="16"/>
       <c r="C212" s="16"/>
       <c r="D212" s="16"/>
@@ -6813,7 +6832,7 @@
       <c r="N212" s="19"/>
     </row>
     <row r="213">
-      <c r="A213" s="21"/>
+      <c r="A213" s="20"/>
       <c r="B213" s="16"/>
       <c r="C213" s="16"/>
       <c r="D213" s="16"/>
@@ -6835,7 +6854,7 @@
       <c r="N213" s="19"/>
     </row>
     <row r="214">
-      <c r="A214" s="21"/>
+      <c r="A214" s="20"/>
       <c r="B214" s="16"/>
       <c r="C214" s="16"/>
       <c r="D214" s="16"/>
@@ -6857,7 +6876,7 @@
       <c r="N214" s="19"/>
     </row>
     <row r="215">
-      <c r="A215" s="21"/>
+      <c r="A215" s="20"/>
       <c r="B215" s="16"/>
       <c r="C215" s="16"/>
       <c r="D215" s="16"/>
@@ -6879,7 +6898,7 @@
       <c r="N215" s="19"/>
     </row>
     <row r="216">
-      <c r="A216" s="21"/>
+      <c r="A216" s="20"/>
       <c r="B216" s="16"/>
       <c r="C216" s="16"/>
       <c r="D216" s="16"/>
@@ -6901,7 +6920,7 @@
       <c r="N216" s="19"/>
     </row>
     <row r="217">
-      <c r="A217" s="21"/>
+      <c r="A217" s="20"/>
       <c r="B217" s="16"/>
       <c r="C217" s="16"/>
       <c r="D217" s="16"/>
@@ -6923,7 +6942,7 @@
       <c r="N217" s="19"/>
     </row>
     <row r="218">
-      <c r="A218" s="21"/>
+      <c r="A218" s="20"/>
       <c r="B218" s="16"/>
       <c r="C218" s="16"/>
       <c r="D218" s="16"/>
@@ -6945,7 +6964,7 @@
       <c r="N218" s="19"/>
     </row>
     <row r="219">
-      <c r="A219" s="21"/>
+      <c r="A219" s="20"/>
       <c r="B219" s="16"/>
       <c r="C219" s="16"/>
       <c r="D219" s="16"/>
@@ -6967,7 +6986,7 @@
       <c r="N219" s="19"/>
     </row>
     <row r="220">
-      <c r="A220" s="21"/>
+      <c r="A220" s="20"/>
       <c r="B220" s="16"/>
       <c r="C220" s="16"/>
       <c r="D220" s="16"/>
@@ -6989,7 +7008,7 @@
       <c r="N220" s="19"/>
     </row>
     <row r="221">
-      <c r="A221" s="21"/>
+      <c r="A221" s="20"/>
       <c r="B221" s="16"/>
       <c r="C221" s="16"/>
       <c r="D221" s="16"/>
@@ -7011,7 +7030,7 @@
       <c r="N221" s="19"/>
     </row>
     <row r="222">
-      <c r="A222" s="21"/>
+      <c r="A222" s="20"/>
       <c r="B222" s="16"/>
       <c r="C222" s="16"/>
       <c r="D222" s="16"/>
@@ -7033,7 +7052,7 @@
       <c r="N222" s="19"/>
     </row>
     <row r="223">
-      <c r="A223" s="21"/>
+      <c r="A223" s="20"/>
       <c r="B223" s="16"/>
       <c r="C223" s="16"/>
       <c r="D223" s="16"/>
@@ -7055,7 +7074,7 @@
       <c r="N223" s="19"/>
     </row>
     <row r="224">
-      <c r="A224" s="21"/>
+      <c r="A224" s="20"/>
       <c r="B224" s="16"/>
       <c r="C224" s="16"/>
       <c r="D224" s="16"/>
@@ -7077,7 +7096,7 @@
       <c r="N224" s="19"/>
     </row>
     <row r="225">
-      <c r="A225" s="21"/>
+      <c r="A225" s="20"/>
       <c r="B225" s="16"/>
       <c r="C225" s="16"/>
       <c r="D225" s="16"/>
@@ -7099,7 +7118,7 @@
       <c r="N225" s="19"/>
     </row>
     <row r="226">
-      <c r="A226" s="21"/>
+      <c r="A226" s="20"/>
       <c r="B226" s="16"/>
       <c r="C226" s="16"/>
       <c r="D226" s="16"/>
@@ -7121,7 +7140,7 @@
       <c r="N226" s="19"/>
     </row>
     <row r="227">
-      <c r="A227" s="21"/>
+      <c r="A227" s="20"/>
       <c r="B227" s="16"/>
       <c r="C227" s="16"/>
       <c r="D227" s="16"/>
@@ -7143,7 +7162,7 @@
       <c r="N227" s="19"/>
     </row>
     <row r="228">
-      <c r="A228" s="21"/>
+      <c r="A228" s="20"/>
       <c r="B228" s="16"/>
       <c r="C228" s="16"/>
       <c r="D228" s="16"/>
@@ -7165,7 +7184,7 @@
       <c r="N228" s="19"/>
     </row>
     <row r="229">
-      <c r="A229" s="21"/>
+      <c r="A229" s="20"/>
       <c r="B229" s="16"/>
       <c r="C229" s="16"/>
       <c r="D229" s="16"/>
@@ -7187,7 +7206,7 @@
       <c r="N229" s="19"/>
     </row>
     <row r="230">
-      <c r="A230" s="21"/>
+      <c r="A230" s="20"/>
       <c r="B230" s="16"/>
       <c r="C230" s="16"/>
       <c r="D230" s="16"/>
@@ -7209,7 +7228,7 @@
       <c r="N230" s="19"/>
     </row>
     <row r="231">
-      <c r="A231" s="21"/>
+      <c r="A231" s="20"/>
       <c r="B231" s="16"/>
       <c r="C231" s="16"/>
       <c r="D231" s="16"/>
@@ -7231,7 +7250,7 @@
       <c r="N231" s="19"/>
     </row>
     <row r="232">
-      <c r="A232" s="21"/>
+      <c r="A232" s="20"/>
       <c r="B232" s="16"/>
       <c r="C232" s="16"/>
       <c r="D232" s="16"/>
@@ -7253,7 +7272,7 @@
       <c r="N232" s="19"/>
     </row>
     <row r="233">
-      <c r="A233" s="21"/>
+      <c r="A233" s="20"/>
       <c r="B233" s="16"/>
       <c r="C233" s="16"/>
       <c r="D233" s="16"/>
@@ -7275,7 +7294,7 @@
       <c r="N233" s="19"/>
     </row>
     <row r="234">
-      <c r="A234" s="21"/>
+      <c r="A234" s="20"/>
       <c r="B234" s="16"/>
       <c r="C234" s="16"/>
       <c r="D234" s="16"/>
@@ -7297,7 +7316,7 @@
       <c r="N234" s="19"/>
     </row>
     <row r="235">
-      <c r="A235" s="21"/>
+      <c r="A235" s="20"/>
       <c r="B235" s="16"/>
       <c r="C235" s="16"/>
       <c r="D235" s="16"/>
@@ -7319,7 +7338,7 @@
       <c r="N235" s="19"/>
     </row>
     <row r="236">
-      <c r="A236" s="21"/>
+      <c r="A236" s="20"/>
       <c r="B236" s="16"/>
       <c r="C236" s="16"/>
       <c r="D236" s="16"/>
@@ -7341,7 +7360,7 @@
       <c r="N236" s="19"/>
     </row>
     <row r="237">
-      <c r="A237" s="21"/>
+      <c r="A237" s="20"/>
       <c r="B237" s="16"/>
       <c r="C237" s="16"/>
       <c r="D237" s="16"/>
@@ -7363,7 +7382,7 @@
       <c r="N237" s="19"/>
     </row>
     <row r="238">
-      <c r="A238" s="21"/>
+      <c r="A238" s="20"/>
       <c r="B238" s="16"/>
       <c r="C238" s="16"/>
       <c r="D238" s="16"/>
@@ -7385,7 +7404,7 @@
       <c r="N238" s="19"/>
     </row>
     <row r="239">
-      <c r="A239" s="21"/>
+      <c r="A239" s="20"/>
       <c r="B239" s="16"/>
       <c r="C239" s="16"/>
       <c r="D239" s="16"/>
@@ -7407,7 +7426,7 @@
       <c r="N239" s="19"/>
     </row>
     <row r="240">
-      <c r="A240" s="21"/>
+      <c r="A240" s="20"/>
       <c r="B240" s="16"/>
       <c r="C240" s="16"/>
       <c r="D240" s="16"/>
@@ -7429,7 +7448,7 @@
       <c r="N240" s="19"/>
     </row>
     <row r="241">
-      <c r="A241" s="21"/>
+      <c r="A241" s="20"/>
       <c r="B241" s="16"/>
       <c r="C241" s="16"/>
       <c r="D241" s="16"/>
@@ -7451,7 +7470,7 @@
       <c r="N241" s="19"/>
     </row>
     <row r="242">
-      <c r="A242" s="21"/>
+      <c r="A242" s="20"/>
       <c r="B242" s="16"/>
       <c r="C242" s="16"/>
       <c r="D242" s="16"/>
@@ -7473,7 +7492,7 @@
       <c r="N242" s="19"/>
     </row>
     <row r="243">
-      <c r="A243" s="21"/>
+      <c r="A243" s="20"/>
       <c r="B243" s="16"/>
       <c r="C243" s="16"/>
       <c r="D243" s="16"/>
@@ -7495,7 +7514,7 @@
       <c r="N243" s="19"/>
     </row>
     <row r="244">
-      <c r="A244" s="21"/>
+      <c r="A244" s="20"/>
       <c r="B244" s="16"/>
       <c r="C244" s="16"/>
       <c r="D244" s="16"/>
@@ -7517,7 +7536,7 @@
       <c r="N244" s="19"/>
     </row>
     <row r="245">
-      <c r="A245" s="21"/>
+      <c r="A245" s="20"/>
       <c r="B245" s="16"/>
       <c r="C245" s="16"/>
       <c r="D245" s="16"/>
@@ -7539,7 +7558,7 @@
       <c r="N245" s="19"/>
     </row>
     <row r="246">
-      <c r="A246" s="21"/>
+      <c r="A246" s="20"/>
       <c r="B246" s="16"/>
       <c r="C246" s="16"/>
       <c r="D246" s="16"/>
@@ -7561,7 +7580,7 @@
       <c r="N246" s="19"/>
     </row>
     <row r="247">
-      <c r="A247" s="21"/>
+      <c r="A247" s="20"/>
       <c r="B247" s="16"/>
       <c r="C247" s="16"/>
       <c r="D247" s="16"/>
@@ -7583,7 +7602,7 @@
       <c r="N247" s="19"/>
     </row>
     <row r="248">
-      <c r="A248" s="21"/>
+      <c r="A248" s="20"/>
       <c r="B248" s="16"/>
       <c r="C248" s="16"/>
       <c r="D248" s="16"/>
@@ -7605,7 +7624,7 @@
       <c r="N248" s="19"/>
     </row>
     <row r="249">
-      <c r="A249" s="21"/>
+      <c r="A249" s="20"/>
       <c r="B249" s="16"/>
       <c r="C249" s="16"/>
       <c r="D249" s="16"/>
@@ -7627,7 +7646,7 @@
       <c r="N249" s="19"/>
     </row>
     <row r="250">
-      <c r="A250" s="21"/>
+      <c r="A250" s="20"/>
       <c r="B250" s="16"/>
       <c r="C250" s="16"/>
       <c r="D250" s="16"/>
@@ -7649,7 +7668,7 @@
       <c r="N250" s="19"/>
     </row>
     <row r="251">
-      <c r="A251" s="21"/>
+      <c r="A251" s="20"/>
       <c r="B251" s="16"/>
       <c r="C251" s="16"/>
       <c r="D251" s="16"/>
@@ -7671,7 +7690,7 @@
       <c r="N251" s="19"/>
     </row>
     <row r="252">
-      <c r="A252" s="21"/>
+      <c r="A252" s="20"/>
       <c r="B252" s="16"/>
       <c r="C252" s="16"/>
       <c r="D252" s="16"/>
@@ -7693,7 +7712,7 @@
       <c r="N252" s="19"/>
     </row>
     <row r="253">
-      <c r="A253" s="21"/>
+      <c r="A253" s="20"/>
       <c r="B253" s="16"/>
       <c r="C253" s="16"/>
       <c r="D253" s="16"/>
@@ -7715,7 +7734,7 @@
       <c r="N253" s="19"/>
     </row>
     <row r="254">
-      <c r="A254" s="21"/>
+      <c r="A254" s="20"/>
       <c r="B254" s="16"/>
       <c r="C254" s="16"/>
       <c r="D254" s="16"/>
@@ -7737,7 +7756,7 @@
       <c r="N254" s="19"/>
     </row>
     <row r="255">
-      <c r="A255" s="21"/>
+      <c r="A255" s="20"/>
       <c r="B255" s="16"/>
       <c r="C255" s="16"/>
       <c r="D255" s="16"/>
@@ -7759,7 +7778,7 @@
       <c r="N255" s="19"/>
     </row>
     <row r="256">
-      <c r="A256" s="21"/>
+      <c r="A256" s="20"/>
       <c r="B256" s="16"/>
       <c r="C256" s="16"/>
       <c r="D256" s="16"/>
@@ -7781,7 +7800,7 @@
       <c r="N256" s="19"/>
     </row>
     <row r="257">
-      <c r="A257" s="21"/>
+      <c r="A257" s="20"/>
       <c r="B257" s="16"/>
       <c r="C257" s="16"/>
       <c r="D257" s="16"/>
@@ -7803,7 +7822,7 @@
       <c r="N257" s="19"/>
     </row>
     <row r="258">
-      <c r="A258" s="21"/>
+      <c r="A258" s="20"/>
       <c r="B258" s="16"/>
       <c r="C258" s="16"/>
       <c r="D258" s="16"/>
@@ -7825,7 +7844,7 @@
       <c r="N258" s="19"/>
     </row>
     <row r="259">
-      <c r="A259" s="21"/>
+      <c r="A259" s="20"/>
       <c r="B259" s="16"/>
       <c r="C259" s="16"/>
       <c r="D259" s="16"/>
@@ -7847,7 +7866,7 @@
       <c r="N259" s="19"/>
     </row>
     <row r="260">
-      <c r="A260" s="21"/>
+      <c r="A260" s="20"/>
       <c r="B260" s="16"/>
       <c r="C260" s="16"/>
       <c r="D260" s="16"/>
@@ -7869,7 +7888,7 @@
       <c r="N260" s="19"/>
     </row>
     <row r="261">
-      <c r="A261" s="21"/>
+      <c r="A261" s="20"/>
       <c r="B261" s="16"/>
       <c r="C261" s="16"/>
       <c r="D261" s="16"/>
@@ -7891,7 +7910,7 @@
       <c r="N261" s="19"/>
     </row>
     <row r="262">
-      <c r="A262" s="21"/>
+      <c r="A262" s="20"/>
       <c r="B262" s="16"/>
       <c r="C262" s="16"/>
       <c r="D262" s="16"/>
@@ -7913,7 +7932,7 @@
       <c r="N262" s="19"/>
     </row>
     <row r="263">
-      <c r="A263" s="21"/>
+      <c r="A263" s="20"/>
       <c r="B263" s="16"/>
       <c r="C263" s="16"/>
       <c r="D263" s="16"/>
@@ -7935,7 +7954,7 @@
       <c r="N263" s="19"/>
     </row>
     <row r="264">
-      <c r="A264" s="21"/>
+      <c r="A264" s="20"/>
       <c r="B264" s="16"/>
       <c r="C264" s="16"/>
       <c r="D264" s="16"/>
@@ -7957,7 +7976,7 @@
       <c r="N264" s="19"/>
     </row>
     <row r="265">
-      <c r="A265" s="21"/>
+      <c r="A265" s="20"/>
       <c r="B265" s="16"/>
       <c r="C265" s="16"/>
       <c r="D265" s="16"/>
@@ -7979,7 +7998,7 @@
       <c r="N265" s="19"/>
     </row>
     <row r="266">
-      <c r="A266" s="21"/>
+      <c r="A266" s="20"/>
       <c r="B266" s="16"/>
       <c r="C266" s="16"/>
       <c r="D266" s="16"/>
@@ -8001,7 +8020,7 @@
       <c r="N266" s="19"/>
     </row>
     <row r="267">
-      <c r="A267" s="21"/>
+      <c r="A267" s="20"/>
       <c r="B267" s="16"/>
       <c r="C267" s="16"/>
       <c r="D267" s="16"/>
@@ -8023,7 +8042,7 @@
       <c r="N267" s="19"/>
     </row>
     <row r="268">
-      <c r="A268" s="21"/>
+      <c r="A268" s="20"/>
       <c r="B268" s="16"/>
       <c r="C268" s="16"/>
       <c r="D268" s="16"/>
@@ -8045,7 +8064,7 @@
       <c r="N268" s="19"/>
     </row>
     <row r="269">
-      <c r="A269" s="21"/>
+      <c r="A269" s="20"/>
       <c r="B269" s="16"/>
       <c r="C269" s="16"/>
       <c r="D269" s="16"/>
@@ -8067,7 +8086,7 @@
       <c r="N269" s="19"/>
     </row>
     <row r="270">
-      <c r="A270" s="21"/>
+      <c r="A270" s="20"/>
       <c r="B270" s="16"/>
       <c r="C270" s="16"/>
       <c r="D270" s="16"/>
@@ -8089,7 +8108,7 @@
       <c r="N270" s="19"/>
     </row>
     <row r="271">
-      <c r="A271" s="21"/>
+      <c r="A271" s="20"/>
       <c r="B271" s="16"/>
       <c r="C271" s="16"/>
       <c r="D271" s="16"/>
@@ -8111,7 +8130,7 @@
       <c r="N271" s="19"/>
     </row>
     <row r="272">
-      <c r="A272" s="21"/>
+      <c r="A272" s="20"/>
       <c r="B272" s="16"/>
       <c r="C272" s="16"/>
       <c r="D272" s="16"/>
@@ -8133,7 +8152,7 @@
       <c r="N272" s="19"/>
     </row>
     <row r="273">
-      <c r="A273" s="21"/>
+      <c r="A273" s="20"/>
       <c r="B273" s="16"/>
       <c r="C273" s="16"/>
       <c r="D273" s="16"/>
@@ -8155,7 +8174,7 @@
       <c r="N273" s="19"/>
     </row>
     <row r="274">
-      <c r="A274" s="21"/>
+      <c r="A274" s="20"/>
       <c r="B274" s="16"/>
       <c r="C274" s="16"/>
       <c r="D274" s="16"/>
@@ -8177,7 +8196,7 @@
       <c r="N274" s="19"/>
     </row>
     <row r="275">
-      <c r="A275" s="21"/>
+      <c r="A275" s="20"/>
       <c r="B275" s="16"/>
       <c r="C275" s="16"/>
       <c r="D275" s="16"/>
@@ -8199,7 +8218,7 @@
       <c r="N275" s="19"/>
     </row>
     <row r="276">
-      <c r="A276" s="21"/>
+      <c r="A276" s="20"/>
       <c r="B276" s="16"/>
       <c r="C276" s="16"/>
       <c r="D276" s="16"/>
@@ -8221,7 +8240,7 @@
       <c r="N276" s="19"/>
     </row>
     <row r="277">
-      <c r="A277" s="21"/>
+      <c r="A277" s="20"/>
       <c r="B277" s="16"/>
       <c r="C277" s="16"/>
       <c r="D277" s="16"/>
@@ -8243,7 +8262,7 @@
       <c r="N277" s="19"/>
     </row>
     <row r="278">
-      <c r="A278" s="21"/>
+      <c r="A278" s="20"/>
       <c r="B278" s="16"/>
       <c r="C278" s="16"/>
       <c r="D278" s="16"/>
@@ -8265,7 +8284,7 @@
       <c r="N278" s="19"/>
     </row>
     <row r="279">
-      <c r="A279" s="21"/>
+      <c r="A279" s="20"/>
       <c r="B279" s="16"/>
       <c r="C279" s="16"/>
       <c r="D279" s="16"/>
@@ -8287,7 +8306,7 @@
       <c r="N279" s="19"/>
     </row>
     <row r="280">
-      <c r="A280" s="21"/>
+      <c r="A280" s="20"/>
       <c r="B280" s="16"/>
       <c r="C280" s="16"/>
       <c r="D280" s="16"/>
@@ -8309,7 +8328,7 @@
       <c r="N280" s="19"/>
     </row>
     <row r="281">
-      <c r="A281" s="21"/>
+      <c r="A281" s="20"/>
       <c r="B281" s="16"/>
       <c r="C281" s="16"/>
       <c r="D281" s="16"/>
@@ -8331,7 +8350,7 @@
       <c r="N281" s="19"/>
     </row>
     <row r="282">
-      <c r="A282" s="21"/>
+      <c r="A282" s="20"/>
       <c r="B282" s="16"/>
       <c r="C282" s="16"/>
       <c r="D282" s="16"/>
@@ -8353,7 +8372,7 @@
       <c r="N282" s="19"/>
     </row>
     <row r="283">
-      <c r="A283" s="21"/>
+      <c r="A283" s="20"/>
       <c r="B283" s="16"/>
       <c r="C283" s="16"/>
       <c r="D283" s="16"/>
@@ -8375,7 +8394,7 @@
       <c r="N283" s="19"/>
     </row>
     <row r="284">
-      <c r="A284" s="21"/>
+      <c r="A284" s="20"/>
       <c r="B284" s="16"/>
       <c r="C284" s="16"/>
       <c r="D284" s="16"/>
@@ -8397,7 +8416,7 @@
       <c r="N284" s="19"/>
     </row>
     <row r="285">
-      <c r="A285" s="21"/>
+      <c r="A285" s="20"/>
       <c r="B285" s="16"/>
       <c r="C285" s="16"/>
       <c r="D285" s="16"/>
@@ -8419,7 +8438,7 @@
       <c r="N285" s="19"/>
     </row>
     <row r="286">
-      <c r="A286" s="21"/>
+      <c r="A286" s="20"/>
       <c r="B286" s="16"/>
       <c r="C286" s="16"/>
       <c r="D286" s="16"/>
@@ -8441,7 +8460,7 @@
       <c r="N286" s="19"/>
     </row>
     <row r="287">
-      <c r="A287" s="21"/>
+      <c r="A287" s="20"/>
       <c r="B287" s="16"/>
       <c r="C287" s="16"/>
       <c r="D287" s="16"/>
@@ -8463,7 +8482,7 @@
       <c r="N287" s="19"/>
     </row>
     <row r="288">
-      <c r="A288" s="21"/>
+      <c r="A288" s="20"/>
       <c r="B288" s="16"/>
       <c r="C288" s="16"/>
       <c r="D288" s="16"/>
@@ -8485,7 +8504,7 @@
       <c r="N288" s="19"/>
     </row>
     <row r="289">
-      <c r="A289" s="21"/>
+      <c r="A289" s="20"/>
       <c r="B289" s="16"/>
       <c r="C289" s="16"/>
       <c r="D289" s="16"/>
@@ -8507,7 +8526,7 @@
       <c r="N289" s="19"/>
     </row>
     <row r="290">
-      <c r="A290" s="21"/>
+      <c r="A290" s="20"/>
       <c r="B290" s="16"/>
       <c r="C290" s="16"/>
       <c r="D290" s="16"/>
@@ -8529,7 +8548,7 @@
       <c r="N290" s="19"/>
     </row>
     <row r="291">
-      <c r="A291" s="21"/>
+      <c r="A291" s="20"/>
       <c r="B291" s="16"/>
       <c r="C291" s="16"/>
       <c r="D291" s="16"/>
@@ -8551,7 +8570,7 @@
       <c r="N291" s="19"/>
     </row>
     <row r="292">
-      <c r="A292" s="21"/>
+      <c r="A292" s="20"/>
       <c r="B292" s="16"/>
       <c r="C292" s="16"/>
       <c r="D292" s="16"/>
@@ -8573,7 +8592,7 @@
       <c r="N292" s="19"/>
     </row>
     <row r="293">
-      <c r="A293" s="21"/>
+      <c r="A293" s="20"/>
       <c r="B293" s="16"/>
       <c r="C293" s="16"/>
       <c r="D293" s="16"/>
@@ -8595,7 +8614,7 @@
       <c r="N293" s="19"/>
     </row>
     <row r="294">
-      <c r="A294" s="21"/>
+      <c r="A294" s="20"/>
       <c r="B294" s="16"/>
       <c r="C294" s="16"/>
       <c r="D294" s="16"/>
@@ -8617,7 +8636,7 @@
       <c r="N294" s="19"/>
     </row>
     <row r="295">
-      <c r="A295" s="21"/>
+      <c r="A295" s="20"/>
       <c r="B295" s="16"/>
       <c r="C295" s="16"/>
       <c r="D295" s="16"/>
@@ -8639,7 +8658,7 @@
       <c r="N295" s="19"/>
     </row>
     <row r="296">
-      <c r="A296" s="21"/>
+      <c r="A296" s="20"/>
       <c r="B296" s="16"/>
       <c r="C296" s="16"/>
       <c r="D296" s="16"/>
@@ -8661,7 +8680,7 @@
       <c r="N296" s="19"/>
     </row>
     <row r="297">
-      <c r="A297" s="21"/>
+      <c r="A297" s="20"/>
       <c r="B297" s="16"/>
       <c r="C297" s="16"/>
       <c r="D297" s="16"/>
@@ -8683,7 +8702,7 @@
       <c r="N297" s="19"/>
     </row>
     <row r="298">
-      <c r="A298" s="21"/>
+      <c r="A298" s="20"/>
       <c r="B298" s="16"/>
       <c r="C298" s="16"/>
       <c r="D298" s="16"/>
@@ -8705,7 +8724,7 @@
       <c r="N298" s="19"/>
     </row>
     <row r="299">
-      <c r="A299" s="21"/>
+      <c r="A299" s="20"/>
       <c r="B299" s="16"/>
       <c r="C299" s="16"/>
       <c r="D299" s="16"/>
@@ -8727,7 +8746,7 @@
       <c r="N299" s="19"/>
     </row>
     <row r="300">
-      <c r="A300" s="21"/>
+      <c r="A300" s="20"/>
       <c r="B300" s="16"/>
       <c r="C300" s="16"/>
       <c r="D300" s="16"/>
@@ -8749,7 +8768,7 @@
       <c r="N300" s="19"/>
     </row>
     <row r="301">
-      <c r="A301" s="21"/>
+      <c r="A301" s="20"/>
       <c r="B301" s="16"/>
       <c r="C301" s="16"/>
       <c r="D301" s="16"/>
@@ -8771,7 +8790,7 @@
       <c r="N301" s="19"/>
     </row>
     <row r="302">
-      <c r="A302" s="21"/>
+      <c r="A302" s="20"/>
       <c r="B302" s="16"/>
       <c r="C302" s="16"/>
       <c r="D302" s="16"/>
@@ -8793,7 +8812,7 @@
       <c r="N302" s="19"/>
     </row>
     <row r="303">
-      <c r="A303" s="21"/>
+      <c r="A303" s="20"/>
       <c r="B303" s="16"/>
       <c r="C303" s="16"/>
       <c r="D303" s="16"/>
@@ -8815,7 +8834,7 @@
       <c r="N303" s="19"/>
     </row>
     <row r="304">
-      <c r="A304" s="21"/>
+      <c r="A304" s="20"/>
       <c r="B304" s="16"/>
       <c r="C304" s="16"/>
       <c r="D304" s="16"/>
@@ -8837,7 +8856,7 @@
       <c r="N304" s="19"/>
     </row>
     <row r="305">
-      <c r="A305" s="21"/>
+      <c r="A305" s="20"/>
       <c r="B305" s="16"/>
       <c r="C305" s="16"/>
       <c r="D305" s="16"/>
@@ -8859,7 +8878,7 @@
       <c r="N305" s="19"/>
     </row>
     <row r="306">
-      <c r="A306" s="21"/>
+      <c r="A306" s="20"/>
       <c r="B306" s="16"/>
       <c r="C306" s="16"/>
       <c r="D306" s="16"/>
@@ -8881,7 +8900,7 @@
       <c r="N306" s="19"/>
     </row>
     <row r="307">
-      <c r="A307" s="21"/>
+      <c r="A307" s="20"/>
       <c r="B307" s="16"/>
       <c r="C307" s="16"/>
       <c r="D307" s="16"/>
@@ -8903,7 +8922,7 @@
       <c r="N307" s="19"/>
     </row>
     <row r="308">
-      <c r="A308" s="21"/>
+      <c r="A308" s="20"/>
       <c r="B308" s="16"/>
       <c r="C308" s="16"/>
       <c r="D308" s="16"/>
@@ -8925,7 +8944,7 @@
       <c r="N308" s="19"/>
     </row>
     <row r="309">
-      <c r="A309" s="21"/>
+      <c r="A309" s="20"/>
       <c r="B309" s="16"/>
       <c r="C309" s="16"/>
       <c r="D309" s="16"/>
@@ -8947,7 +8966,7 @@
       <c r="N309" s="19"/>
     </row>
     <row r="310">
-      <c r="A310" s="21"/>
+      <c r="A310" s="20"/>
       <c r="B310" s="16"/>
       <c r="C310" s="16"/>
       <c r="D310" s="16"/>
@@ -8969,7 +8988,7 @@
       <c r="N310" s="19"/>
     </row>
     <row r="311">
-      <c r="A311" s="21"/>
+      <c r="A311" s="20"/>
       <c r="B311" s="16"/>
       <c r="C311" s="16"/>
       <c r="D311" s="16"/>
@@ -8991,7 +9010,7 @@
       <c r="N311" s="19"/>
     </row>
     <row r="312">
-      <c r="A312" s="21"/>
+      <c r="A312" s="20"/>
       <c r="B312" s="16"/>
       <c r="C312" s="16"/>
       <c r="D312" s="16"/>
@@ -9013,7 +9032,7 @@
       <c r="N312" s="19"/>
     </row>
     <row r="313">
-      <c r="A313" s="21"/>
+      <c r="A313" s="20"/>
       <c r="B313" s="16"/>
       <c r="C313" s="16"/>
       <c r="D313" s="16"/>
@@ -9035,7 +9054,7 @@
       <c r="N313" s="19"/>
     </row>
     <row r="314">
-      <c r="A314" s="21"/>
+      <c r="A314" s="20"/>
       <c r="B314" s="16"/>
       <c r="C314" s="16"/>
       <c r="D314" s="16"/>
@@ -9057,7 +9076,7 @@
       <c r="N314" s="19"/>
     </row>
     <row r="315">
-      <c r="A315" s="21"/>
+      <c r="A315" s="20"/>
       <c r="B315" s="16"/>
       <c r="C315" s="16"/>
       <c r="D315" s="16"/>
@@ -9079,7 +9098,7 @@
       <c r="N315" s="19"/>
     </row>
     <row r="316">
-      <c r="A316" s="21"/>
+      <c r="A316" s="20"/>
       <c r="B316" s="16"/>
       <c r="C316" s="16"/>
       <c r="D316" s="16"/>
@@ -9101,7 +9120,7 @@
       <c r="N316" s="19"/>
     </row>
     <row r="317">
-      <c r="A317" s="21"/>
+      <c r="A317" s="20"/>
       <c r="B317" s="16"/>
       <c r="C317" s="16"/>
       <c r="D317" s="16"/>
@@ -9123,7 +9142,7 @@
       <c r="N317" s="19"/>
     </row>
     <row r="318">
-      <c r="A318" s="21"/>
+      <c r="A318" s="20"/>
       <c r="B318" s="16"/>
       <c r="C318" s="16"/>
       <c r="D318" s="16"/>
@@ -9145,7 +9164,7 @@
       <c r="N318" s="19"/>
     </row>
     <row r="319">
-      <c r="A319" s="21"/>
+      <c r="A319" s="20"/>
       <c r="B319" s="16"/>
       <c r="C319" s="16"/>
       <c r="D319" s="16"/>
@@ -9167,7 +9186,7 @@
       <c r="N319" s="19"/>
     </row>
     <row r="320">
-      <c r="A320" s="21"/>
+      <c r="A320" s="20"/>
       <c r="B320" s="16"/>
       <c r="C320" s="16"/>
       <c r="D320" s="16"/>
@@ -9189,7 +9208,7 @@
       <c r="N320" s="19"/>
     </row>
     <row r="321">
-      <c r="A321" s="21"/>
+      <c r="A321" s="20"/>
       <c r="B321" s="16"/>
       <c r="C321" s="16"/>
       <c r="D321" s="16"/>
@@ -9211,7 +9230,7 @@
       <c r="N321" s="19"/>
     </row>
     <row r="322">
-      <c r="A322" s="21"/>
+      <c r="A322" s="20"/>
       <c r="B322" s="16"/>
       <c r="C322" s="16"/>
       <c r="D322" s="16"/>
@@ -9233,7 +9252,7 @@
       <c r="N322" s="19"/>
     </row>
     <row r="323">
-      <c r="A323" s="21"/>
+      <c r="A323" s="20"/>
       <c r="B323" s="16"/>
       <c r="C323" s="16"/>
       <c r="D323" s="16"/>
@@ -9255,7 +9274,7 @@
       <c r="N323" s="19"/>
     </row>
     <row r="324">
-      <c r="A324" s="21"/>
+      <c r="A324" s="20"/>
       <c r="B324" s="16"/>
       <c r="C324" s="16"/>
       <c r="D324" s="16"/>
@@ -9277,7 +9296,7 @@
       <c r="N324" s="19"/>
     </row>
     <row r="325">
-      <c r="A325" s="21"/>
+      <c r="A325" s="20"/>
       <c r="B325" s="16"/>
       <c r="C325" s="16"/>
       <c r="D325" s="16"/>
@@ -9299,7 +9318,7 @@
       <c r="N325" s="19"/>
     </row>
     <row r="326">
-      <c r="A326" s="21"/>
+      <c r="A326" s="20"/>
       <c r="B326" s="16"/>
       <c r="C326" s="16"/>
       <c r="D326" s="16"/>
@@ -9321,7 +9340,7 @@
       <c r="N326" s="19"/>
     </row>
     <row r="327">
-      <c r="A327" s="21"/>
+      <c r="A327" s="20"/>
       <c r="B327" s="16"/>
       <c r="C327" s="16"/>
       <c r="D327" s="16"/>
@@ -9343,7 +9362,7 @@
       <c r="N327" s="19"/>
     </row>
     <row r="328">
-      <c r="A328" s="21"/>
+      <c r="A328" s="20"/>
       <c r="B328" s="16"/>
       <c r="C328" s="16"/>
       <c r="D328" s="16"/>
@@ -9365,7 +9384,7 @@
       <c r="N328" s="19"/>
     </row>
     <row r="329">
-      <c r="A329" s="21"/>
+      <c r="A329" s="20"/>
       <c r="B329" s="16"/>
       <c r="C329" s="16"/>
       <c r="D329" s="16"/>
@@ -9387,7 +9406,7 @@
       <c r="N329" s="19"/>
     </row>
     <row r="330">
-      <c r="A330" s="21"/>
+      <c r="A330" s="20"/>
       <c r="B330" s="16"/>
       <c r="C330" s="16"/>
       <c r="D330" s="16"/>
@@ -9409,7 +9428,7 @@
       <c r="N330" s="19"/>
     </row>
     <row r="331">
-      <c r="A331" s="21"/>
+      <c r="A331" s="20"/>
       <c r="B331" s="16"/>
       <c r="C331" s="16"/>
       <c r="D331" s="16"/>
@@ -9431,7 +9450,7 @@
       <c r="N331" s="19"/>
     </row>
     <row r="332">
-      <c r="A332" s="21"/>
+      <c r="A332" s="20"/>
       <c r="B332" s="16"/>
       <c r="C332" s="16"/>
       <c r="D332" s="16"/>
@@ -9453,7 +9472,7 @@
       <c r="N332" s="19"/>
     </row>
     <row r="333">
-      <c r="A333" s="21"/>
+      <c r="A333" s="20"/>
       <c r="B333" s="16"/>
       <c r="C333" s="16"/>
       <c r="D333" s="16"/>
@@ -9475,7 +9494,7 @@
       <c r="N333" s="19"/>
     </row>
     <row r="334">
-      <c r="A334" s="21"/>
+      <c r="A334" s="20"/>
       <c r="B334" s="16"/>
       <c r="C334" s="16"/>
       <c r="D334" s="16"/>
@@ -9497,7 +9516,7 @@
       <c r="N334" s="19"/>
     </row>
     <row r="335">
-      <c r="A335" s="21"/>
+      <c r="A335" s="20"/>
       <c r="B335" s="16"/>
       <c r="C335" s="16"/>
       <c r="D335" s="16"/>
@@ -9519,7 +9538,7 @@
       <c r="N335" s="19"/>
     </row>
     <row r="336">
-      <c r="A336" s="21"/>
+      <c r="A336" s="20"/>
       <c r="B336" s="16"/>
       <c r="C336" s="16"/>
       <c r="D336" s="16"/>
@@ -9541,7 +9560,7 @@
       <c r="N336" s="19"/>
     </row>
     <row r="337">
-      <c r="A337" s="21"/>
+      <c r="A337" s="20"/>
       <c r="B337" s="16"/>
       <c r="C337" s="16"/>
       <c r="D337" s="16"/>
@@ -9563,7 +9582,7 @@
       <c r="N337" s="19"/>
     </row>
     <row r="338">
-      <c r="A338" s="21"/>
+      <c r="A338" s="20"/>
       <c r="B338" s="16"/>
       <c r="C338" s="16"/>
       <c r="D338" s="16"/>
@@ -9585,7 +9604,7 @@
       <c r="N338" s="19"/>
     </row>
     <row r="339">
-      <c r="A339" s="21"/>
+      <c r="A339" s="20"/>
       <c r="B339" s="16"/>
       <c r="C339" s="16"/>
       <c r="D339" s="16"/>
@@ -9607,7 +9626,7 @@
       <c r="N339" s="19"/>
     </row>
     <row r="340">
-      <c r="A340" s="21"/>
+      <c r="A340" s="20"/>
       <c r="B340" s="16"/>
       <c r="C340" s="16"/>
       <c r="D340" s="16"/>
@@ -9629,7 +9648,7 @@
       <c r="N340" s="19"/>
     </row>
     <row r="341">
-      <c r="A341" s="21"/>
+      <c r="A341" s="20"/>
       <c r="B341" s="16"/>
       <c r="C341" s="16"/>
       <c r="D341" s="16"/>
@@ -9651,7 +9670,7 @@
       <c r="N341" s="19"/>
     </row>
     <row r="342">
-      <c r="A342" s="21"/>
+      <c r="A342" s="20"/>
       <c r="B342" s="16"/>
       <c r="C342" s="16"/>
       <c r="D342" s="16"/>
@@ -9673,7 +9692,7 @@
       <c r="N342" s="19"/>
     </row>
     <row r="343">
-      <c r="A343" s="21"/>
+      <c r="A343" s="20"/>
       <c r="B343" s="16"/>
       <c r="C343" s="16"/>
       <c r="D343" s="16"/>
@@ -9695,7 +9714,7 @@
       <c r="N343" s="19"/>
     </row>
     <row r="344">
-      <c r="A344" s="21"/>
+      <c r="A344" s="20"/>
       <c r="B344" s="16"/>
       <c r="C344" s="16"/>
       <c r="D344" s="16"/>
@@ -9717,7 +9736,7 @@
       <c r="N344" s="19"/>
     </row>
     <row r="345">
-      <c r="A345" s="21"/>
+      <c r="A345" s="20"/>
       <c r="B345" s="16"/>
       <c r="C345" s="16"/>
       <c r="D345" s="16"/>
@@ -9739,7 +9758,7 @@
       <c r="N345" s="19"/>
     </row>
     <row r="346">
-      <c r="A346" s="21"/>
+      <c r="A346" s="20"/>
       <c r="B346" s="16"/>
       <c r="C346" s="16"/>
       <c r="D346" s="16"/>
@@ -9761,7 +9780,7 @@
       <c r="N346" s="19"/>
     </row>
     <row r="347">
-      <c r="A347" s="21"/>
+      <c r="A347" s="20"/>
       <c r="B347" s="16"/>
       <c r="C347" s="16"/>
       <c r="D347" s="16"/>
@@ -9783,7 +9802,7 @@
       <c r="N347" s="19"/>
     </row>
     <row r="348">
-      <c r="A348" s="21"/>
+      <c r="A348" s="20"/>
       <c r="B348" s="16"/>
       <c r="C348" s="16"/>
       <c r="D348" s="16"/>
@@ -9805,7 +9824,7 @@
       <c r="N348" s="19"/>
     </row>
     <row r="349">
-      <c r="A349" s="21"/>
+      <c r="A349" s="20"/>
       <c r="B349" s="16"/>
       <c r="C349" s="16"/>
       <c r="D349" s="16"/>
@@ -9827,7 +9846,7 @@
       <c r="N349" s="19"/>
     </row>
     <row r="350">
-      <c r="A350" s="21"/>
+      <c r="A350" s="20"/>
       <c r="B350" s="16"/>
       <c r="C350" s="16"/>
       <c r="D350" s="16"/>
@@ -9849,7 +9868,7 @@
       <c r="N350" s="19"/>
     </row>
     <row r="351">
-      <c r="A351" s="21"/>
+      <c r="A351" s="20"/>
       <c r="B351" s="16"/>
       <c r="C351" s="16"/>
       <c r="D351" s="16"/>
@@ -9871,7 +9890,7 @@
       <c r="N351" s="19"/>
     </row>
     <row r="352">
-      <c r="A352" s="21"/>
+      <c r="A352" s="20"/>
       <c r="B352" s="16"/>
       <c r="C352" s="16"/>
       <c r="D352" s="16"/>
@@ -9893,7 +9912,7 @@
       <c r="N352" s="19"/>
     </row>
     <row r="353">
-      <c r="A353" s="21"/>
+      <c r="A353" s="20"/>
       <c r="B353" s="16"/>
       <c r="C353" s="16"/>
       <c r="D353" s="16"/>
@@ -9915,7 +9934,7 @@
       <c r="N353" s="19"/>
     </row>
     <row r="354">
-      <c r="A354" s="21"/>
+      <c r="A354" s="20"/>
       <c r="B354" s="16"/>
       <c r="C354" s="16"/>
       <c r="D354" s="16"/>
@@ -9937,7 +9956,7 @@
       <c r="N354" s="19"/>
     </row>
     <row r="355">
-      <c r="A355" s="21"/>
+      <c r="A355" s="20"/>
       <c r="B355" s="16"/>
       <c r="C355" s="16"/>
       <c r="D355" s="16"/>
@@ -9959,7 +9978,7 @@
       <c r="N355" s="19"/>
     </row>
     <row r="356">
-      <c r="A356" s="21"/>
+      <c r="A356" s="20"/>
       <c r="B356" s="16"/>
       <c r="C356" s="16"/>
       <c r="D356" s="16"/>
@@ -9981,7 +10000,7 @@
       <c r="N356" s="19"/>
     </row>
     <row r="357">
-      <c r="A357" s="21"/>
+      <c r="A357" s="20"/>
       <c r="B357" s="16"/>
       <c r="C357" s="16"/>
       <c r="D357" s="16"/>
@@ -10003,7 +10022,7 @@
       <c r="N357" s="19"/>
     </row>
     <row r="358">
-      <c r="A358" s="21"/>
+      <c r="A358" s="20"/>
       <c r="B358" s="16"/>
       <c r="C358" s="16"/>
       <c r="D358" s="16"/>
@@ -10025,7 +10044,7 @@
       <c r="N358" s="19"/>
     </row>
     <row r="359">
-      <c r="A359" s="21"/>
+      <c r="A359" s="20"/>
       <c r="B359" s="16"/>
       <c r="C359" s="16"/>
       <c r="D359" s="16"/>
@@ -10047,7 +10066,7 @@
       <c r="N359" s="19"/>
     </row>
     <row r="360">
-      <c r="A360" s="21"/>
+      <c r="A360" s="20"/>
       <c r="B360" s="16"/>
       <c r="C360" s="16"/>
       <c r="D360" s="16"/>
@@ -10069,7 +10088,7 @@
       <c r="N360" s="19"/>
     </row>
     <row r="361">
-      <c r="A361" s="21"/>
+      <c r="A361" s="20"/>
       <c r="B361" s="16"/>
       <c r="C361" s="16"/>
       <c r="D361" s="16"/>
@@ -10091,7 +10110,7 @@
       <c r="N361" s="19"/>
     </row>
     <row r="362">
-      <c r="A362" s="21"/>
+      <c r="A362" s="20"/>
       <c r="B362" s="16"/>
       <c r="C362" s="16"/>
       <c r="D362" s="16"/>
@@ -10113,7 +10132,7 @@
       <c r="N362" s="19"/>
     </row>
     <row r="363">
-      <c r="A363" s="21"/>
+      <c r="A363" s="20"/>
       <c r="B363" s="16"/>
       <c r="C363" s="16"/>
       <c r="D363" s="16"/>
@@ -10135,7 +10154,7 @@
       <c r="N363" s="19"/>
     </row>
     <row r="364">
-      <c r="A364" s="21"/>
+      <c r="A364" s="20"/>
       <c r="B364" s="16"/>
       <c r="C364" s="16"/>
       <c r="D364" s="16"/>
@@ -10157,7 +10176,7 @@
       <c r="N364" s="19"/>
     </row>
     <row r="365">
-      <c r="A365" s="21"/>
+      <c r="A365" s="20"/>
       <c r="B365" s="16"/>
       <c r="C365" s="16"/>
       <c r="D365" s="16"/>
@@ -10179,7 +10198,7 @@
       <c r="N365" s="19"/>
     </row>
     <row r="366">
-      <c r="A366" s="21"/>
+      <c r="A366" s="20"/>
       <c r="B366" s="16"/>
       <c r="C366" s="16"/>
       <c r="D366" s="16"/>
@@ -10201,7 +10220,7 @@
       <c r="N366" s="19"/>
     </row>
     <row r="367">
-      <c r="A367" s="21"/>
+      <c r="A367" s="20"/>
       <c r="B367" s="16"/>
       <c r="C367" s="16"/>
       <c r="D367" s="16"/>
@@ -10223,7 +10242,7 @@
       <c r="N367" s="19"/>
     </row>
     <row r="368">
-      <c r="A368" s="21"/>
+      <c r="A368" s="20"/>
       <c r="B368" s="16"/>
       <c r="C368" s="16"/>
       <c r="D368" s="16"/>
@@ -10245,7 +10264,7 @@
       <c r="N368" s="19"/>
     </row>
     <row r="369">
-      <c r="A369" s="21"/>
+      <c r="A369" s="20"/>
       <c r="B369" s="16"/>
       <c r="C369" s="16"/>
       <c r="D369" s="16"/>
@@ -10267,7 +10286,7 @@
       <c r="N369" s="19"/>
     </row>
     <row r="370">
-      <c r="A370" s="21"/>
+      <c r="A370" s="20"/>
       <c r="B370" s="16"/>
       <c r="C370" s="16"/>
       <c r="D370" s="16"/>
@@ -10289,7 +10308,7 @@
       <c r="N370" s="19"/>
     </row>
     <row r="371">
-      <c r="A371" s="21"/>
+      <c r="A371" s="20"/>
       <c r="B371" s="16"/>
       <c r="C371" s="16"/>
       <c r="D371" s="16"/>
@@ -10311,7 +10330,7 @@
       <c r="N371" s="19"/>
     </row>
     <row r="372">
-      <c r="A372" s="21"/>
+      <c r="A372" s="20"/>
       <c r="B372" s="16"/>
       <c r="C372" s="16"/>
       <c r="D372" s="16"/>
@@ -10333,7 +10352,7 @@
       <c r="N372" s="19"/>
     </row>
     <row r="373">
-      <c r="A373" s="21"/>
+      <c r="A373" s="20"/>
       <c r="B373" s="16"/>
       <c r="C373" s="16"/>
       <c r="D373" s="16"/>
@@ -10355,7 +10374,7 @@
       <c r="N373" s="19"/>
     </row>
     <row r="374">
-      <c r="A374" s="21"/>
+      <c r="A374" s="20"/>
       <c r="B374" s="16"/>
       <c r="C374" s="16"/>
       <c r="D374" s="16"/>
@@ -10377,7 +10396,7 @@
       <c r="N374" s="19"/>
     </row>
     <row r="375">
-      <c r="A375" s="21"/>
+      <c r="A375" s="20"/>
       <c r="B375" s="16"/>
       <c r="C375" s="16"/>
       <c r="D375" s="16"/>
@@ -10399,7 +10418,7 @@
       <c r="N375" s="19"/>
     </row>
     <row r="376">
-      <c r="A376" s="21"/>
+      <c r="A376" s="20"/>
       <c r="B376" s="16"/>
       <c r="C376" s="16"/>
       <c r="D376" s="16"/>
@@ -10421,7 +10440,7 @@
       <c r="N376" s="19"/>
     </row>
     <row r="377">
-      <c r="A377" s="21"/>
+      <c r="A377" s="20"/>
       <c r="B377" s="16"/>
       <c r="C377" s="16"/>
       <c r="D377" s="16"/>
@@ -10443,7 +10462,7 @@
       <c r="N377" s="19"/>
     </row>
     <row r="378">
-      <c r="A378" s="21"/>
+      <c r="A378" s="20"/>
       <c r="B378" s="16"/>
       <c r="C378" s="16"/>
       <c r="D378" s="16"/>
@@ -10465,7 +10484,7 @@
       <c r="N378" s="19"/>
     </row>
     <row r="379">
-      <c r="A379" s="21"/>
+      <c r="A379" s="20"/>
       <c r="B379" s="16"/>
       <c r="C379" s="16"/>
       <c r="D379" s="16"/>
@@ -10487,7 +10506,7 @@
       <c r="N379" s="19"/>
     </row>
     <row r="380">
-      <c r="A380" s="21"/>
+      <c r="A380" s="20"/>
       <c r="B380" s="16"/>
       <c r="C380" s="16"/>
       <c r="D380" s="16"/>
@@ -10509,7 +10528,7 @@
       <c r="N380" s="19"/>
     </row>
     <row r="381">
-      <c r="A381" s="21"/>
+      <c r="A381" s="20"/>
       <c r="B381" s="16"/>
       <c r="C381" s="16"/>
       <c r="D381" s="16"/>
@@ -10531,7 +10550,7 @@
       <c r="N381" s="19"/>
     </row>
     <row r="382">
-      <c r="A382" s="21"/>
+      <c r="A382" s="20"/>
       <c r="B382" s="16"/>
       <c r="C382" s="16"/>
       <c r="D382" s="16"/>
@@ -10553,7 +10572,7 @@
       <c r="N382" s="19"/>
     </row>
     <row r="383">
-      <c r="A383" s="21"/>
+      <c r="A383" s="20"/>
       <c r="B383" s="16"/>
       <c r="C383" s="16"/>
       <c r="D383" s="16"/>
@@ -10575,7 +10594,7 @@
       <c r="N383" s="19"/>
     </row>
     <row r="384">
-      <c r="A384" s="21"/>
+      <c r="A384" s="20"/>
       <c r="B384" s="16"/>
       <c r="C384" s="16"/>
       <c r="D384" s="16"/>
@@ -10597,7 +10616,7 @@
       <c r="N384" s="19"/>
     </row>
     <row r="385">
-      <c r="A385" s="21"/>
+      <c r="A385" s="20"/>
       <c r="B385" s="16"/>
       <c r="C385" s="16"/>
       <c r="D385" s="16"/>
@@ -10619,7 +10638,7 @@
       <c r="N385" s="19"/>
     </row>
     <row r="386">
-      <c r="A386" s="21"/>
+      <c r="A386" s="20"/>
       <c r="B386" s="16"/>
       <c r="C386" s="16"/>
       <c r="D386" s="16"/>
@@ -10641,7 +10660,7 @@
       <c r="N386" s="19"/>
     </row>
     <row r="387">
-      <c r="A387" s="21"/>
+      <c r="A387" s="20"/>
       <c r="B387" s="16"/>
       <c r="C387" s="16"/>
       <c r="D387" s="16"/>
@@ -10663,7 +10682,7 @@
       <c r="N387" s="19"/>
     </row>
     <row r="388">
-      <c r="A388" s="21"/>
+      <c r="A388" s="20"/>
       <c r="B388" s="16"/>
       <c r="C388" s="16"/>
       <c r="D388" s="16"/>
@@ -10685,7 +10704,7 @@
       <c r="N388" s="19"/>
     </row>
     <row r="389">
-      <c r="A389" s="21"/>
+      <c r="A389" s="20"/>
       <c r="B389" s="16"/>
       <c r="C389" s="16"/>
       <c r="D389" s="16"/>
@@ -10707,7 +10726,7 @@
       <c r="N389" s="19"/>
     </row>
     <row r="390">
-      <c r="A390" s="21"/>
+      <c r="A390" s="20"/>
       <c r="B390" s="16"/>
       <c r="C390" s="16"/>
       <c r="D390" s="16"/>
@@ -10729,7 +10748,7 @@
       <c r="N390" s="19"/>
     </row>
     <row r="391">
-      <c r="A391" s="21"/>
+      <c r="A391" s="20"/>
       <c r="B391" s="16"/>
       <c r="C391" s="16"/>
       <c r="D391" s="16"/>
@@ -10751,7 +10770,7 @@
       <c r="N391" s="19"/>
     </row>
     <row r="392">
-      <c r="A392" s="21"/>
+      <c r="A392" s="20"/>
       <c r="B392" s="16"/>
       <c r="C392" s="16"/>
       <c r="D392" s="16"/>
@@ -10773,7 +10792,7 @@
       <c r="N392" s="19"/>
     </row>
     <row r="393">
-      <c r="A393" s="21"/>
+      <c r="A393" s="20"/>
       <c r="B393" s="16"/>
       <c r="C393" s="16"/>
       <c r="D393" s="16"/>
@@ -10795,7 +10814,7 @@
       <c r="N393" s="19"/>
     </row>
     <row r="394">
-      <c r="A394" s="21"/>
+      <c r="A394" s="20"/>
       <c r="B394" s="16"/>
       <c r="C394" s="16"/>
       <c r="D394" s="16"/>
@@ -10817,7 +10836,7 @@
       <c r="N394" s="19"/>
     </row>
     <row r="395">
-      <c r="A395" s="21"/>
+      <c r="A395" s="20"/>
       <c r="B395" s="16"/>
       <c r="C395" s="16"/>
       <c r="D395" s="16"/>
@@ -10839,7 +10858,7 @@
       <c r="N395" s="19"/>
     </row>
     <row r="396">
-      <c r="A396" s="21"/>
+      <c r="A396" s="20"/>
       <c r="B396" s="16"/>
       <c r="C396" s="16"/>
       <c r="D396" s="16"/>
@@ -10861,7 +10880,7 @@
       <c r="N396" s="19"/>
     </row>
     <row r="397">
-      <c r="A397" s="21"/>
+      <c r="A397" s="20"/>
       <c r="B397" s="16"/>
       <c r="C397" s="16"/>
       <c r="D397" s="16"/>
@@ -10883,7 +10902,7 @@
       <c r="N397" s="19"/>
     </row>
     <row r="398">
-      <c r="A398" s="21"/>
+      <c r="A398" s="20"/>
       <c r="B398" s="16"/>
       <c r="C398" s="16"/>
       <c r="D398" s="16"/>
@@ -10905,7 +10924,7 @@
       <c r="N398" s="19"/>
     </row>
     <row r="399">
-      <c r="A399" s="21"/>
+      <c r="A399" s="20"/>
       <c r="B399" s="16"/>
       <c r="C399" s="16"/>
       <c r="D399" s="16"/>
@@ -10927,7 +10946,7 @@
       <c r="N399" s="19"/>
     </row>
     <row r="400">
-      <c r="A400" s="21"/>
+      <c r="A400" s="20"/>
       <c r="B400" s="16"/>
       <c r="C400" s="16"/>
       <c r="D400" s="16"/>
@@ -10949,7 +10968,7 @@
       <c r="N400" s="19"/>
     </row>
     <row r="401">
-      <c r="A401" s="21"/>
+      <c r="A401" s="20"/>
       <c r="B401" s="16"/>
       <c r="C401" s="16"/>
       <c r="D401" s="16"/>
@@ -10987,7 +11006,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="lessThan" id="{3CFDA9BF-1AE6-4106-806C-8135A2570AA1}">
+          <x14:cfRule type="cellIs" priority="2" operator="lessThan" id="{F581D4D6-8E09-46A5-8DF1-21F84AD7DC70}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -11008,7 +11027,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3" disablePrompts="0">
-        <x14:dataValidation xr:uid="{91F4F13C-ECBA-4170-BBDF-A502D754F8D9}" type="list" allowBlank="1" error="Please choose a value from the dropdown list." errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's overall feeling" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{23BC7110-18C9-457E-86AD-A298003C59C0}" type="list" allowBlank="1" error="Please choose a value from the dropdown list." errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's overall feeling" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Excellent,Good,Neutral,Low,Stressed"</xm:f>
           </x14:formula1>
@@ -11017,7 +11036,7 @@
           </x14:formula2>
           <xm:sqref>K6:K401</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{EBC7801D-984A-4C9A-A170-5281A59ECDC2}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's satisfaction level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{14A2B412-18FA-490A-9043-70CB53E63A27}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's satisfaction level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</xm:f>
           </x14:formula1>
@@ -11026,7 +11045,7 @@
           </x14:formula2>
           <xm:sqref>L6:L51 L56:L401 L52 L53 L54 L55</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{22C882DC-E02F-49FE-984C-39D607219A87}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's energy level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{4D1673E5-3A8C-46D2-8D7C-0D0E5FB835C0}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" prompt="Select today's energy level" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"High,Medium,Low"</xm:f>
           </x14:formula1>
